--- a/tame_output/ON/bt/strategyON_20240926.xlsx
+++ b/tame_output/ON/bt/strategyON_20240926.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.6%</t>
+          <t>-574.0%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-48.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.6%</t>
+          <t>-319.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-65.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>134.4%</t>
+          <t>134.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>141.0%</t>
+          <t>142.0%</t>
         </is>
       </c>
     </row>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.86325021509095</v>
+        <v>3.872163648396344</v>
       </c>
       <c r="C2098" t="n">
         <v>4.925948693046007</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.140416996950414</v>
+        <v>-4.124772746419541</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.269425469952094</v>
+        <v>3.275683170164442</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.574368173633686</v>
+        <v>1.590012424164559</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.870569597226219</v>
+        <v>5.879956147544743</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240926.xlsx
+++ b/tame_output/ON/bt/strategyON_20240926.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>181.0%</t>
+          <t>177.6%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.4%</t>
+          <t>421.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-574.0%</t>
+          <t>-575.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-52.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.4%</t>
+          <t>-320.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-65.0%</t>
+          <t>-66.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>134.8%</t>
+          <t>133.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>121.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>142.0%</t>
+          <t>137.8%</t>
         </is>
       </c>
     </row>
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.057119799856059</v>
+        <v>3.023796232579679</v>
       </c>
       <c r="D1905" t="n">
         <v>-6.735319701416286</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3626354949757968</v>
+        <v>0.329311927699417</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.5137064616439256</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.748895922869704</v>
+        <v>2.715572355593324</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.059934860543696</v>
+        <v>3.026611293267316</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.563458485851384</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4341950418893945</v>
+        <v>0.4008714746130146</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.3418452460790228</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.854827712896283</v>
+        <v>2.821504145619903</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.072841201767355</v>
+        <v>3.039517634490975</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.478493819122065</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4810872498047809</v>
+        <v>0.447763682528401</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2568805793497032</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.918712854157533</v>
+        <v>2.885389286881153</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.944865272168136</v>
+        <v>2.911541704891756</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.584083808895169</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3108753242963203</v>
+        <v>0.2775517570199404</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3624705691228076</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.727382930694452</v>
+        <v>2.694059363418072</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.993409614045222</v>
+        <v>2.960086046768843</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.515849224269742</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3867135000235775</v>
+        <v>0.3533899327471977</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3440552462502716</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.78697646629506</v>
+        <v>2.75365289901868</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>2.843465238130436</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.367909182862142</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3292687079482102</v>
+        <v>0.2959451406718303</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.323734330341714</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.682548207201787</v>
+        <v>2.649224639925408</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>2.834751251876957</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.314939660608154</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3417425305963278</v>
+        <v>0.3084189633199479</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.705615934300702</v>
+        <v>2.672292367024323</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>2.827790639781864</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.149151464647863</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4010971968853507</v>
+        <v>0.3677736296089709</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.698655322205609</v>
+        <v>2.665331754929229</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>2.842252994163007</v>
       </c>
       <c r="D1913" t="n">
         <v>-6.115788258169094</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4289048338580015</v>
+        <v>0.3955812665816216</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.713117676586752</v>
+        <v>2.679794109310373</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>2.836785114622202</v>
       </c>
       <c r="D1914" t="n">
         <v>-6.007529121046573</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4667406091662052</v>
+        <v>0.4334170418898253</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2707648080877251</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.707649797045947</v>
+        <v>2.674326229769568</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>2.834283208632779</v>
       </c>
       <c r="D1915" t="n">
         <v>-5.884237986229442</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5135551571036343</v>
+        <v>0.4802315898272544</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1474736732705946</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.779122571946802</v>
+        <v>2.745799004670423</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>2.841984186870104</v>
       </c>
       <c r="D1916" t="n">
         <v>-5.831541119098151</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5423348821934759</v>
+        <v>0.5090113149170961</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.09477680613930345</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.818441670462903</v>
+        <v>2.785118103186523</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>2.837764895217155</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.587775677114706</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6356217673339044</v>
+        <v>0.6022982000575245</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.09477680613930345</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.814222378809953</v>
+        <v>2.780898811533573</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>2.839889209137171</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.498000004738234</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6736563502045092</v>
+        <v>0.6403327829281293</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.853306359678555</v>
+        <v>2.819982792402175</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>2.832631284120873</v>
       </c>
       <c r="D1919" t="n">
         <v>-5.248149610789159</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7663385827678413</v>
+        <v>0.7330150154914614</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.846048434662257</v>
+        <v>2.812724867385878</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>2.836230407641522</v>
       </c>
       <c r="D1920" t="n">
         <v>-5.072257518321727</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8402945432754629</v>
+        <v>0.8069709759990831</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.03317736122499343</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.849647558182906</v>
+        <v>2.816323990906526</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>2.849557913696076</v>
       </c>
       <c r="D1921" t="n">
         <v>-4.900811055299264</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9222006345390019</v>
+        <v>0.8888770672626221</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1382691017974697</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.965842942050938</v>
+        <v>2.932519374774558</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>2.848578391312373</v>
       </c>
       <c r="D1922" t="n">
         <v>-4.820788768190143</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9532300269989473</v>
+        <v>0.9199064597225675</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2182913889065907</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.012876791932707</v>
+        <v>2.979553224656327</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>2.85327319236669</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.757153025956208</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9833791249468384</v>
+        <v>0.9500555576704586</v>
       </c>
       <c r="F1923" t="n">
         <v>0.2819271311405252</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.055753038327385</v>
+        <v>3.022429471051005</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>2.834467451150485</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.663455707739813</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.002052311017192</v>
+        <v>0.9687287437408121</v>
       </c>
       <c r="F1924" t="n">
         <v>0.2819271311405252</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.036947297111181</v>
+        <v>3.003623729834801</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>2.836210527775363</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.673958330805102</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9995943384159538</v>
+        <v>0.9662707711395739</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2714245080752363</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.032388799896885</v>
+        <v>2.999065232620505</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>2.840139841610183</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.561472070136228</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.048518156518324</v>
+        <v>1.015194589241944</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2714245080752363</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036318113731705</v>
+        <v>3.002994546455325</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>2.840818425527523</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.543758383258362</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.05628221518681</v>
+        <v>1.02295864791043</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2746058369721531</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.038905494987195</v>
+        <v>3.005581927710815</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>2.837816496747517</v>
       </c>
       <c r="D1928" t="n">
         <v>-4.420284111945344</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.102669994932011</v>
+        <v>1.069346427655631</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2746058369721531</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.035903566207188</v>
+        <v>3.002579998930809</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>2.839395533758131</v>
       </c>
       <c r="D1929" t="n">
         <v>-4.200263313908334</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.192257351157429</v>
+        <v>1.158933783881049</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4158256820401334</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.122214510258591</v>
+        <v>3.088890942982211</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>2.855289716559954</v>
       </c>
       <c r="D1930" t="n">
         <v>-4.067395624845056</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.261298609584564</v>
+        <v>1.227975042308184</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4158256820401334</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138108693060414</v>
+        <v>3.104785125784034</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>2.856435561000256</v>
       </c>
       <c r="D1931" t="n">
         <v>-3.947222541480557</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.310513687370665</v>
+        <v>1.277190120094285</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5359987654046323</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.211358387519415</v>
+        <v>3.178034820243036</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>2.866523663561696</v>
       </c>
       <c r="D1932" t="n">
         <v>-3.81196918015058</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.374703134464096</v>
+        <v>1.341379567187716</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6712521267346094</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.302598506878842</v>
+        <v>3.269274939602462</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>2.852561154963122</v>
       </c>
       <c r="D1933" t="n">
         <v>-3.871844007508273</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.336790694922444</v>
+        <v>1.303467127646065</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6113772993769173</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.252711101865652</v>
+        <v>3.219387534589272</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>2.86785032419733</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.752023776597435</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.400007956520988</v>
+        <v>1.366684389244608</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6113772993769173</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.268000271099861</v>
+        <v>3.234676703823481</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>2.775494523519772</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.754493483059241</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.306664273258707</v>
+        <v>1.273340705982327</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6089075929151111</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174162646545219</v>
+        <v>3.140839079268839</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>2.694756385005073</v>
       </c>
       <c r="D1936" t="n">
         <v>-3.822863669383251</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.198578060214404</v>
+        <v>1.165254492938025</v>
       </c>
       <c r="F1936" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.098989927452249</v>
+        <v>3.065666360175869</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.685193093636964</v>
       </c>
       <c r="D1937" t="n">
         <v>-3.934735949009402</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144265856995835</v>
+        <v>1.110942289719456</v>
       </c>
       <c r="F1937" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.08942663608414</v>
+        <v>3.05610306880776</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.685091185837372</v>
+        <v>2.651767618560992</v>
       </c>
       <c r="D1938" t="n">
         <v>-3.918761283523134</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.11723024811437</v>
+        <v>1.08390668083799</v>
       </c>
       <c r="F1938" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.056001161008167</v>
+        <v>3.022677593731788</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.689658417829159</v>
+        <v>2.65633485055278</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.743287023730665</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.191987184023146</v>
+        <v>1.158663616746766</v>
       </c>
       <c r="F1939" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.060568392999955</v>
+        <v>3.027244825723575</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.665400446590366</v>
+        <v>2.632076879313987</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.73536264914575</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.170898962618318</v>
+        <v>1.137575395341939</v>
       </c>
       <c r="F1940" t="n">
         <v>0.618183291951326</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.036310421761162</v>
+        <v>3.002986854484782</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.593938759991816</v>
+        <v>2.560615192715436</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.729084446575901</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.101948557047708</v>
+        <v>1.068624989771328</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.968615656704522</v>
+        <v>2.935292089428142</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.604111146423949</v>
+        <v>2.570787579147569</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.669231827372178</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.136061991161329</v>
+        <v>1.102738423884949</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.978788043136654</v>
+        <v>2.945464475860274</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.599057416997809</v>
+        <v>2.565733849721429</v>
       </c>
       <c r="D1943" t="n">
         <v>-3.582988364345801</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.165505646945741</v>
+        <v>1.132182079669361</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6244614945211751</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.973734313710514</v>
+        <v>2.940410746434134</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.590833192442334</v>
+        <v>2.557509625165955</v>
       </c>
       <c r="D1944" t="n">
         <v>-3.628295183744781</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.139158694630674</v>
+        <v>1.105835127354294</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5836513315119443</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.941023991349501</v>
+        <v>2.907700424073121</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.591385065475436</v>
+        <v>2.558061498199056</v>
       </c>
       <c r="D1945" t="n">
         <v>-3.657328288447082</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.128097325782855</v>
+        <v>1.094773758506475</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5836513315119443</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.941575864382603</v>
+        <v>2.908252297106223</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.520657757366802</v>
+        <v>2.487334190090422</v>
       </c>
       <c r="D1946" t="n">
         <v>-3.564517806996223</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.094494210254565</v>
+        <v>1.061170642978185</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6764618129628036</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.926534845144484</v>
+        <v>2.893211277868104</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.522531233291402</v>
+        <v>2.489207666015023</v>
       </c>
       <c r="D1947" t="n">
         <v>-3.608907276325651</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.078611898447394</v>
+        <v>1.045288331171014</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6320723436333759</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.901774639471428</v>
+        <v>2.868451072195048</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.517606941803125</v>
+        <v>2.484283374526746</v>
       </c>
       <c r="D1948" t="n">
         <v>-3.588403582440153</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.081889084513316</v>
+        <v>1.048565517236936</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6525760375188733</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.90915256431445</v>
+        <v>2.87582899703807</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.523098237633793</v>
+        <v>2.489774670357413</v>
       </c>
       <c r="D1949" t="n">
         <v>-3.628327677022726</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.071410742510954</v>
+        <v>1.038087175234575</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6525760375188733</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.914643860145117</v>
+        <v>2.881320292868737</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.534595439402332</v>
+        <v>2.501271872125952</v>
       </c>
       <c r="D1950" t="n">
         <v>-3.656108074924079</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.071795785118952</v>
+        <v>1.038472217842572</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6247956396175203</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.909472823172844</v>
+        <v>2.876149255896464</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.372951159402985</v>
+        <v>2.339627592126605</v>
       </c>
       <c r="D1951" t="n">
         <v>-3.774488747654217</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8627992360275503</v>
+        <v>0.8294756687511704</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.707497831882912</v>
+        <v>2.674174264606532</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.493100820122191</v>
+        <v>2.459777252845811</v>
       </c>
       <c r="D1952" t="n">
         <v>-3.883102826097548</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9395032653694235</v>
+        <v>0.9061796980930437</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.827647492602118</v>
+        <v>2.794323925325738</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.507613846224514</v>
+        <v>2.474290278948134</v>
       </c>
       <c r="D1953" t="n">
         <v>-3.847693787849405</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9681799067710035</v>
+        <v>0.9348563394946237</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5575777874665441</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.842160518704441</v>
+        <v>2.808836951428061</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.505033287566882</v>
+        <v>2.471709720290503</v>
       </c>
       <c r="D1954" t="n">
         <v>-3.856154956504867</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9622148806511879</v>
+        <v>0.928891313374808</v>
       </c>
       <c r="F1954" t="n">
         <v>0.549116618811083</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834503258853533</v>
+        <v>2.801179691577153</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.501762316412185</v>
+        <v>2.468438749135805</v>
       </c>
       <c r="D1955" t="n">
         <v>-3.6790386264697</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.029790441510557</v>
+        <v>0.9964668742341767</v>
       </c>
       <c r="F1955" t="n">
         <v>0.549116618811083</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831232287698835</v>
+        <v>2.797908720422455</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.502445708174098</v>
+        <v>2.469122140897718</v>
       </c>
       <c r="D1956" t="n">
         <v>-3.724130871303246</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.012436935339051</v>
+        <v>0.9791133680626716</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4872205756416932</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794778053559114</v>
+        <v>2.761454486282734</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.496232683480512</v>
+        <v>2.462909116204132</v>
       </c>
       <c r="D1957" t="n">
         <v>-3.544755450064478</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.077974079140973</v>
+        <v>1.044650511864593</v>
       </c>
       <c r="F1957" t="n">
         <v>0.6439973338124119</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.88263108376796</v>
+        <v>2.84930751649158</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.477040138812102</v>
+        <v>2.443716571535722</v>
       </c>
       <c r="D1958" t="n">
         <v>-3.589769663585085</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.04077584906432</v>
+        <v>1.00745228178794</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6136484384978073</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845229201910787</v>
+        <v>2.811905634634407</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.482731701151048</v>
+        <v>2.449408133874668</v>
       </c>
       <c r="D1959" t="n">
         <v>-3.85677417385752</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9396656072942917</v>
+        <v>0.9063420400179119</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4192854004548587</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734302941423963</v>
+        <v>2.700979374147583</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.481935623047549</v>
+        <v>2.448612055771169</v>
       </c>
       <c r="D1960" t="n">
         <v>-3.957971955294693</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.898390416615924</v>
+        <v>0.8650668493395441</v>
       </c>
       <c r="F1960" t="n">
         <v>0.3508765869095395</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692461575193273</v>
+        <v>2.659138007916893</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.479535584601866</v>
+        <v>2.446212017325486</v>
       </c>
       <c r="D1961" t="n">
         <v>-3.95146098868038</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8985947648159658</v>
+        <v>0.8652711975395859</v>
       </c>
       <c r="F1961" t="n">
         <v>0.3508765869095395</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.69006153674759</v>
+        <v>2.65673796947121</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.476060303810111</v>
+        <v>2.442736736533731</v>
       </c>
       <c r="D1962" t="n">
         <v>-3.932422860973083</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9027347351071295</v>
+        <v>0.8694111678307497</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2926929755783449</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651676089157118</v>
+        <v>2.618352521880738</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.595354705444301</v>
+        <v>2.562031138167921</v>
       </c>
       <c r="D1963" t="n">
         <v>-3.984938663247903</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001022815831392</v>
+        <v>0.9676992485550122</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2926929755783449</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.770970490791308</v>
+        <v>2.737646923514928</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.596188034430435</v>
+        <v>2.562864467154055</v>
       </c>
       <c r="D1964" t="n">
         <v>-3.988346974682483</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.000492820243694</v>
+        <v>0.9671692529673137</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3252095445877223</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.791313761183068</v>
+        <v>2.757990193906688</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.602196564827361</v>
+        <v>2.568872997550981</v>
       </c>
       <c r="D1965" t="n">
         <v>-3.968990838788636</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014243804998158</v>
+        <v>0.9809202377217785</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3252095445877223</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.797322291579994</v>
+        <v>2.763998724303614</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.50014678610456</v>
+        <v>2.46682321882818</v>
       </c>
       <c r="D1966" t="n">
         <v>-3.821247868553634</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9712912143693586</v>
+        <v>0.9379676470929788</v>
       </c>
       <c r="F1966" t="n">
         <v>0.4930169018226055</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.795956927198123</v>
+        <v>2.762633359921744</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.502940407636041</v>
+        <v>2.469616840359661</v>
       </c>
       <c r="D1967" t="n">
         <v>-3.905069089828332</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9405563473909604</v>
+        <v>0.9072327801145805</v>
       </c>
       <c r="F1967" t="n">
         <v>0.4930169018226055</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.798750548729604</v>
+        <v>2.765426981453225</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.503602756027699</v>
+        <v>2.47027918875132</v>
       </c>
       <c r="D1968" t="n">
         <v>-3.898916383775547</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9436797782037325</v>
+        <v>0.9103562109273526</v>
       </c>
       <c r="F1968" t="n">
         <v>0.4991696078753898</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.803104520752933</v>
+        <v>2.769780953476554</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.46935966549143</v>
       </c>
       <c r="D1969" t="n">
         <v>-3.915725681926049</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9360365356836422</v>
+        <v>0.9027129684072623</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4823603097248881</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.792099418602743</v>
+        <v>2.758775851326363</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.535695219288251</v>
       </c>
       <c r="D1970" t="n">
         <v>-3.853427683149927</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027291288990912</v>
+        <v>0.993967721714532</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5276545739993301</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.885611530964229</v>
+        <v>2.852287963687849</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.337987221002378</v>
       </c>
       <c r="D1971" t="n">
         <v>-3.651637485484769</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9102993697711022</v>
+        <v>0.8769758024947223</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7256727661684845</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.806714447979849</v>
+        <v>2.773390880703469</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.408277453324553</v>
       </c>
       <c r="D1972" t="n">
         <v>-3.702524198170964</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9602349170187994</v>
+        <v>0.9269113497424195</v>
       </c>
       <c r="F1972" t="n">
         <v>0.67478605348229</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.846472652690307</v>
+        <v>2.813149085413927</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.422905189440597</v>
       </c>
       <c r="D1973" t="n">
         <v>-3.615913455521156</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009506950194766</v>
+        <v>0.9761833829183861</v>
       </c>
       <c r="F1973" t="n">
         <v>0.7534117846874483</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.908275827529446</v>
+        <v>2.874952260253066</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.421441170265268</v>
       </c>
       <c r="D1974" t="n">
         <v>-3.676122753526441</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9839592118173239</v>
+        <v>0.9506356445409441</v>
       </c>
       <c r="F1974" t="n">
         <v>0.6932024866821638</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.870686229550947</v>
+        <v>2.837362662274567</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.419932788305197</v>
       </c>
       <c r="D1975" t="n">
         <v>-3.626936104842089</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002125489330993</v>
+        <v>0.9688019220546131</v>
       </c>
       <c r="F1975" t="n">
         <v>0.6932024866821638</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.869177847590875</v>
+        <v>2.835854280314495</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.419795655740633</v>
       </c>
       <c r="D1976" t="n">
         <v>-3.582562973203521</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019737609421857</v>
+        <v>0.9864140421454768</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7375756183207324</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.895664594009453</v>
+        <v>2.862341026733073</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.414189449879224</v>
       </c>
       <c r="D1977" t="n">
         <v>-3.54783165188502</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.028023932087847</v>
+        <v>0.9947003648114676</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7375756183207324</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.890058388148043</v>
+        <v>2.856734820871663</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.420571206907028</v>
       </c>
       <c r="D1978" t="n">
         <v>-3.500175921323964</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.053467981340074</v>
+        <v>1.020144414063695</v>
       </c>
       <c r="F1978" t="n">
         <v>0.785231348881788</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.925033583512481</v>
+        <v>2.891710016236101</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.425463580281753</v>
       </c>
       <c r="D1979" t="n">
         <v>-3.39965776282521</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.098567618114301</v>
+        <v>1.065244050837921</v>
       </c>
       <c r="F1979" t="n">
         <v>0.8857495073805426</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.990236851986459</v>
+        <v>2.956913284710079</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.412218252757625</v>
       </c>
       <c r="D1980" t="n">
         <v>-3.383752433392857</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.091684422363114</v>
+        <v>1.058360855086734</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8066368466713036</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.929523928036788</v>
+        <v>2.896200360760408</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.416315955368254</v>
       </c>
       <c r="D1981" t="n">
         <v>-3.338914031784459</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.113717485617102</v>
+        <v>1.080393918340722</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8111802796161731</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.936347690414338</v>
+        <v>2.903024123137958</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.420476894999332</v>
       </c>
       <c r="D1982" t="n">
         <v>-3.358412488026467</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.110079042751377</v>
+        <v>1.076755475474997</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7630956383362688</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.911657845277473</v>
+        <v>2.878334278001093</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.426356497527169</v>
       </c>
       <c r="D1983" t="n">
         <v>-3.314209650940567</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.133639780113574</v>
+        <v>1.100316212837194</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8072984754221693</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.944059150056851</v>
+        <v>2.910735582780471</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.424766497996417</v>
       </c>
       <c r="D1984" t="n">
         <v>-3.321769316777614</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.129025914248003</v>
+        <v>1.095702346971623</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8621018794319886</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.97535119293199</v>
+        <v>2.94202762565561</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.476014263179456</v>
       </c>
       <c r="D1985" t="n">
         <v>-3.163477899238341</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.243590246446751</v>
+        <v>1.210266679170372</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8621018794319886</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.026598958115029</v>
+        <v>2.99327539083865</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.474454967773709</v>
       </c>
       <c r="D1986" t="n">
         <v>-2.955835895603865</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.325087752494795</v>
+        <v>1.291764185218415</v>
       </c>
       <c r="F1986" t="n">
         <v>1.069743883066465</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.149624864889968</v>
+        <v>3.116301297613588</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.469403196011979</v>
       </c>
       <c r="D1987" t="n">
         <v>-2.904803802881337</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.340448817822076</v>
+        <v>1.307125250545697</v>
       </c>
       <c r="F1987" t="n">
         <v>1.120775975788993</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.175192348761755</v>
+        <v>3.141868781485375</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.486590600104684</v>
       </c>
       <c r="D1988" t="n">
         <v>-2.839579621754131</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.383725894365664</v>
+        <v>1.350402327089284</v>
       </c>
       <c r="F1988" t="n">
         <v>1.186000156916198</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.231514261530783</v>
+        <v>3.198190694254404</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.482551572403965</v>
       </c>
       <c r="D1989" t="n">
         <v>-2.802152601682998</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.394657674693397</v>
+        <v>1.361334107417018</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19125169494538</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.230626156647573</v>
+        <v>3.197302589371193</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.483808364735205</v>
       </c>
       <c r="D1990" t="n">
         <v>-2.800794616709452</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.396457661014056</v>
+        <v>1.363134093737676</v>
       </c>
       <c r="F1990" t="n">
         <v>1.265589820483199</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.276485824301504</v>
+        <v>3.243162257025125</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.644366135756416</v>
       </c>
       <c r="D1991" t="n">
         <v>-2.772381353609568</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.56838073727522</v>
+        <v>1.53505716999884</v>
       </c>
       <c r="F1991" t="n">
         <v>1.20661425773677</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.401658257674858</v>
+        <v>3.368334690398478</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>2.764479044974233</v>
       </c>
       <c r="D1992" t="n">
         <v>-2.697599092584556</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.718406550903042</v>
+        <v>1.685082983626663</v>
       </c>
       <c r="F1992" t="n">
         <v>1.281396518761783</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.566640523507683</v>
+        <v>3.533316956231303</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>2.756187020988092</v>
       </c>
       <c r="D1993" t="n">
         <v>-2.671515008320748</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.720548160622425</v>
+        <v>1.687224593346045</v>
       </c>
       <c r="F1993" t="n">
         <v>1.281396518761783</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.558348499521542</v>
+        <v>3.525024932245162</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>2.754380216571871</v>
       </c>
       <c r="D1994" t="n">
         <v>-2.583637095211627</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.753892521449852</v>
+        <v>1.720568954173473</v>
       </c>
       <c r="F1994" t="n">
         <v>1.397322161185134</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.626097080559332</v>
+        <v>3.592773513282952</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>2.771934622298663</v>
       </c>
       <c r="D1995" t="n">
         <v>-2.574744633818344</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.775003911733957</v>
+        <v>1.741680344457577</v>
       </c>
       <c r="F1995" t="n">
         <v>1.397322161185134</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.643651486286123</v>
+        <v>3.610327919009743</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>2.763789669703247</v>
       </c>
       <c r="D1996" t="n">
         <v>-2.743220750788222</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.69946851235059</v>
+        <v>1.66614494507421</v>
       </c>
       <c r="F1996" t="n">
         <v>1.369374325468553</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.618737832260758</v>
+        <v>3.585414264984379</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>2.745059366891109</v>
       </c>
       <c r="D1997" t="n">
         <v>-2.296964558158782</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.859240686590228</v>
+        <v>1.825917119313848</v>
       </c>
       <c r="F1997" t="n">
         <v>1.27465565579892</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.543176327646841</v>
+        <v>3.509852760370461</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>2.735723389388013</v>
       </c>
       <c r="D1998" t="n">
         <v>-2.27424345447563</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.858993150560393</v>
+        <v>1.825669583284013</v>
       </c>
       <c r="F1998" t="n">
         <v>1.27465565579892</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533840350143745</v>
+        <v>3.500516782867365</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>2.894629515239182</v>
       </c>
       <c r="D1999" t="n">
         <v>-2.403445267769672</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.966218551093945</v>
+        <v>1.932894983817565</v>
       </c>
       <c r="F1999" t="n">
         <v>1.145453842504878</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.615225388018489</v>
+        <v>3.581901820742109</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>2.931707337732829</v>
       </c>
       <c r="D2000" t="n">
         <v>-2.429319666243698</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.992946614197981</v>
+        <v>1.959623046921601</v>
       </c>
       <c r="F2000" t="n">
         <v>1.190365451216619</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.67925017573918</v>
+        <v>3.6459266084628</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>2.928382693722374</v>
       </c>
       <c r="D2001" t="n">
         <v>-2.422264976028524</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.992443846273596</v>
+        <v>1.959120278997216</v>
       </c>
       <c r="F2001" t="n">
         <v>1.197420141431793</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.68015834585783</v>
+        <v>3.64683477858145</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>2.938388847367115</v>
       </c>
       <c r="D2002" t="n">
         <v>-2.395313751702036</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.013230489648933</v>
+        <v>1.979906922372553</v>
       </c>
       <c r="F2002" t="n">
         <v>1.212300487459512</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.699092707119203</v>
+        <v>3.665769139842823</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.122491979512075</v>
       </c>
       <c r="D2003" t="n">
         <v>-2.416857979532824</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.188715930661578</v>
+        <v>2.155392363385198</v>
       </c>
       <c r="F2003" t="n">
         <v>1.212300487459512</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.883195839264162</v>
+        <v>3.849872271987782</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.114608674415068</v>
       </c>
       <c r="D2004" t="n">
         <v>-2.439266097337696</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.171869378442622</v>
+        <v>2.138545811166242</v>
       </c>
       <c r="F2004" t="n">
         <v>1.212300487459512</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.875312534167155</v>
+        <v>3.841988966890776</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.116662673964706</v>
       </c>
       <c r="D2005" t="n">
         <v>-2.467490332915296</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.162633683761219</v>
+        <v>2.129310116484839</v>
       </c>
       <c r="F2005" t="n">
         <v>1.230277239910821</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.888152585187578</v>
+        <v>3.854829017911198</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.172916391686553</v>
       </c>
       <c r="D2006" t="n">
         <v>-2.476931258803826</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.215111031127655</v>
+        <v>2.181787463851275</v>
       </c>
       <c r="F2006" t="n">
         <v>1.352704357454212</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01786257343546</v>
+        <v>3.98453900615908</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.175807486231854</v>
       </c>
       <c r="D2007" t="n">
         <v>-2.5658078899723</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.182451473205566</v>
+        <v>2.149127905929186</v>
       </c>
       <c r="F2007" t="n">
         <v>1.263827726285738</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.967427689279677</v>
+        <v>3.934104122003297</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.173919299125629</v>
       </c>
       <c r="D2008" t="n">
         <v>-2.642137867573206</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.150031295058978</v>
+        <v>2.116707727782599</v>
       </c>
       <c r="F2008" t="n">
         <v>1.263827726285738</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.965539502173452</v>
+        <v>3.932215934897072</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.168739528728491</v>
       </c>
       <c r="D2009" t="n">
         <v>-2.797094652973335</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.082868810501789</v>
+        <v>2.049545243225409</v>
       </c>
       <c r="F2009" t="n">
         <v>1.108870940885609</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.867385660536237</v>
+        <v>3.834062093259857</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.167173538938644</v>
       </c>
       <c r="D2010" t="n">
         <v>-2.95866307850059</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.016675450501039</v>
+        <v>1.983351883224659</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9820880170877296</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.789749916467661</v>
+        <v>3.756426349191281</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.180246945804562</v>
       </c>
       <c r="D2011" t="n">
         <v>-3.06696374037071</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.98642859261891</v>
+        <v>1.953105025342531</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9820880170877296</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.80282332333358</v>
+        <v>3.7694997560572</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.172252142587502</v>
       </c>
       <c r="D2012" t="n">
         <v>-3.084767712091454</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.971312200713553</v>
+        <v>1.937988633437173</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9115533941825285</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.752507746373399</v>
+        <v>3.719184179097019</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.170776183714504</v>
       </c>
       <c r="D2013" t="n">
         <v>-3.112668499200927</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.958675926996765</v>
+        <v>1.925352359720385</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8769564700395936</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.73027363301464</v>
+        <v>3.69695006573826</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.167540627691703</v>
       </c>
       <c r="D2014" t="n">
         <v>-3.23519460190382</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.906429929892806</v>
+        <v>1.873106362616427</v>
       </c>
       <c r="F2014" t="n">
         <v>0.7544303673366998</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.653522415370103</v>
+        <v>3.620198848093723</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.234246587282207</v>
       </c>
       <c r="D2015" t="n">
         <v>-3.465709098089409</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.880930091009075</v>
+        <v>1.847606523732695</v>
       </c>
       <c r="F2015" t="n">
         <v>0.523915871151111</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.581919677249253</v>
+        <v>3.548596109972873</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.374558306284054</v>
       </c>
       <c r="D2016" t="n">
         <v>-3.814454183313853</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.881743775921144</v>
+        <v>1.848420208644765</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.656982623899762</v>
+        <v>3.623659056623382</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.443538575429693</v>
       </c>
       <c r="D2017" t="n">
         <v>-3.968440601089993</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.889129477956328</v>
+        <v>1.855805910679948</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.725962893045402</v>
+        <v>3.692639325769022</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.429589777549814</v>
       </c>
       <c r="D2018" t="n">
         <v>-4.173040035953002</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.793340906131246</v>
+        <v>1.760017338854866</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.712014095165522</v>
+        <v>3.678690527889143</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.441460266605228</v>
       </c>
       <c r="D2019" t="n">
         <v>-4.425515189960726</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.70422133358357</v>
+        <v>1.67089776630719</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.723884584220936</v>
+        <v>3.690561016944557</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.442670801124172</v>
       </c>
       <c r="D2020" t="n">
         <v>-4.718410946440138</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.588273565510748</v>
+        <v>1.554949998234369</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4151679172322132</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.72509511873988</v>
+        <v>3.6917715514635</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.446792543351493</v>
       </c>
       <c r="D2021" t="n">
         <v>-4.905075074574946</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.517729656484147</v>
+        <v>1.484406089207767</v>
       </c>
       <c r="F2021" t="n">
         <v>0.3884289464076534</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.713173478472465</v>
+        <v>3.679849911196086</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.441870396087683</v>
       </c>
       <c r="D2022" t="n">
         <v>-5.051095761488908</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.454399234454751</v>
+        <v>1.421075667178371</v>
       </c>
       <c r="F2022" t="n">
         <v>0.3793458546137964</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.702801476132341</v>
+        <v>3.669477908855961</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.604074452786727</v>
       </c>
       <c r="D2023" t="n">
         <v>-5.142809770598493</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.579917687509961</v>
+        <v>1.546594120233582</v>
       </c>
       <c r="F2023" t="n">
         <v>0.3793458546137964</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.865005532831385</v>
+        <v>3.831681965555005</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.598921090750541</v>
       </c>
       <c r="D2024" t="n">
         <v>-5.174461429658463</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.562103661849788</v>
+        <v>1.528780094573408</v>
       </c>
       <c r="F2024" t="n">
         <v>0.3741773973693562</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.856751096448535</v>
+        <v>3.823427529172155</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.609150508319032</v>
       </c>
       <c r="D2025" t="n">
         <v>-5.243527484231399</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.544706657589105</v>
+        <v>1.511383090312725</v>
       </c>
       <c r="F2025" t="n">
         <v>0.3118065198757461</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.82955798752086</v>
+        <v>3.79623442024448</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.618076146774935</v>
       </c>
       <c r="D2026" t="n">
         <v>-5.345503606479807</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.512841847145644</v>
+        <v>1.479518279869264</v>
       </c>
       <c r="F2026" t="n">
         <v>0.2098303976273386</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.777297952627718</v>
+        <v>3.743974385351338</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.61022903401911</v>
       </c>
       <c r="D2027" t="n">
         <v>-5.235497323002585</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.548997247780708</v>
+        <v>1.515673680504328</v>
       </c>
       <c r="F2027" t="n">
         <v>0.2330349695446138</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.783373583022259</v>
+        <v>3.750050015745879</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.614479044741084</v>
       </c>
       <c r="D2028" t="n">
         <v>-5.092437747261659</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.610471088799053</v>
+        <v>1.577147521522673</v>
       </c>
       <c r="F2028" t="n">
         <v>0.2410483961345931</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.79243164969822</v>
+        <v>3.75910808242184</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.62173992762362</v>
       </c>
       <c r="D2029" t="n">
         <v>-4.790991021789822</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.738310661870324</v>
+        <v>1.704987094593944</v>
       </c>
       <c r="F2029" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.980560567863859</v>
+        <v>3.947237000587479</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.622711105376331</v>
       </c>
       <c r="D2030" t="n">
         <v>-4.815581266025005</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.729445741928961</v>
+        <v>1.696122174652581</v>
       </c>
       <c r="F2030" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.98153174561657</v>
+        <v>3.94820817834019</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.623554009756087</v>
       </c>
       <c r="D2031" t="n">
         <v>-4.764542890018485</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.750703996711324</v>
+        <v>1.717380429434944</v>
       </c>
       <c r="F2031" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.982374649996325</v>
+        <v>3.949051082719945</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.642592108630232</v>
       </c>
       <c r="D2032" t="n">
         <v>-4.723403595151854</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.786197813532122</v>
+        <v>1.752874246255742</v>
       </c>
       <c r="F2032" t="n">
         <v>0.5836344164730611</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.026096325790449</v>
+        <v>3.992772758514069</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.458776104754167</v>
       </c>
       <c r="D2033" t="n">
         <v>-4.626768683133214</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.641035774463513</v>
+        <v>1.607712207187133</v>
       </c>
       <c r="F2033" t="n">
         <v>0.6802693284917011</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.900261269125567</v>
+        <v>3.866937701849187</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.462278148828131</v>
       </c>
       <c r="D2034" t="n">
         <v>-4.557730672184746</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.672153022916864</v>
+        <v>1.638829455640484</v>
       </c>
       <c r="F2034" t="n">
         <v>0.7493073394401691</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.945186119768612</v>
+        <v>3.911862552492233</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.446704967904213</v>
       </c>
       <c r="D2035" t="n">
         <v>-4.393234337993785</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.722378375669331</v>
+        <v>1.689054808392951</v>
       </c>
       <c r="F2035" t="n">
         <v>0.913803673631131</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.028310739359272</v>
+        <v>3.994987172082892</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.445892678340643</v>
       </c>
       <c r="D2036" t="n">
         <v>-4.316135736451912</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.75240552672251</v>
+        <v>1.71908195944613</v>
       </c>
       <c r="F2036" t="n">
         <v>0.913803673631131</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.027498449795702</v>
+        <v>3.994174882519322</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.455761457465715</v>
       </c>
       <c r="D2037" t="n">
         <v>-4.326520931341801</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.758120227891627</v>
+        <v>1.724796660615247</v>
       </c>
       <c r="F2037" t="n">
         <v>0.9034184787412417</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.03113611198684</v>
+        <v>3.99781254471046</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.526598463242141</v>
       </c>
       <c r="D2038" t="n">
         <v>-4.345109090064026</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.821521970179162</v>
+        <v>1.788198402902782</v>
       </c>
       <c r="F2038" t="n">
         <v>0.8848303200190164</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.09082022252993</v>
+        <v>4.057496655253551</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.523467474060439</v>
       </c>
       <c r="D2039" t="n">
         <v>-4.345407636760062</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.818271562319046</v>
+        <v>1.784947995042666</v>
       </c>
       <c r="F2039" t="n">
         <v>0.8845317733229805</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.087510105330607</v>
+        <v>4.054186538054227</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.52799836899983</v>
       </c>
       <c r="D2040" t="n">
         <v>-4.244584503069635</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.863131710734609</v>
+        <v>1.829808143458229</v>
       </c>
       <c r="F2040" t="n">
         <v>0.8969959888073343</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.099519529560611</v>
+        <v>4.066195962284231</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.528127622478374</v>
       </c>
       <c r="D2041" t="n">
         <v>-4.053803142317227</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.939573508514115</v>
+        <v>1.906249941237735</v>
       </c>
       <c r="F2041" t="n">
         <v>1.087777349559742</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.214117599490599</v>
+        <v>4.180794032214219</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.50796446821597</v>
       </c>
       <c r="D2042" t="n">
         <v>-3.946839784467805</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.96219569739148</v>
+        <v>1.9288721301151</v>
       </c>
       <c r="F2042" t="n">
         <v>1.146241957519543</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229033210004077</v>
+        <v>4.195709642727697</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.542931404828029</v>
       </c>
       <c r="D2043" t="n">
         <v>-3.891509196566043</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.019294869164243</v>
+        <v>1.985971301887863</v>
       </c>
       <c r="F2043" t="n">
         <v>1.201572545421305</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.263874932080812</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.536617972729466</v>
       </c>
       <c r="D2044" t="n">
         <v>-3.87945506965308</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.017803087830866</v>
+        <v>1.984479520554486</v>
       </c>
       <c r="F2044" t="n">
         <v>1.213626672334268</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.264793976130028</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.538498602913602</v>
       </c>
       <c r="D2045" t="n">
         <v>-3.920610189221301</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.003221670187714</v>
+        <v>1.969898102911334</v>
       </c>
       <c r="F2045" t="n">
         <v>1.172471552766047</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.241981534573231</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.551349628791485</v>
       </c>
       <c r="D2046" t="n">
         <v>-3.852561626529771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>2.009968553865829</v>
       </c>
       <c r="F2046" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.295661698066031</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.571552298965079</v>
       </c>
       <c r="D2047" t="n">
         <v>-4.084162019699273</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.937531066771622</v>
       </c>
       <c r="F2047" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.315864368239625</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.555158535031961</v>
       </c>
       <c r="D2048" t="n">
         <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.901116684626816</v>
       </c>
       <c r="F2048" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.299470604306507</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.515410448625428</v>
       </c>
       <c r="D2049" t="n">
         <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.791325865189705</v>
       </c>
       <c r="F2049" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.259722517899974</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.522433067622368</v>
       </c>
       <c r="D2050" t="n">
         <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.876788545558854</v>
       </c>
       <c r="F2050" t="n">
         <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.384405228955227</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.621604067195272</v>
       </c>
       <c r="D2051" t="n">
         <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.037169701977072</v>
       </c>
       <c r="F2051" t="n">
         <v>1.589645661001384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.575391463796103</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.809070292103565</v>
       </c>
       <c r="D2052" t="n">
         <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.213313001336057</v>
       </c>
       <c r="F2052" t="n">
         <v>1.589645661001384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.762857688704395</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.778473243457647</v>
       </c>
       <c r="D2053" t="n">
         <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.116078662644731</v>
       </c>
       <c r="F2053" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.632304704990364</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.782149646119365</v>
       </c>
       <c r="D2054" t="n">
         <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.128969382651074</v>
       </c>
       <c r="F2054" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.635981107652082</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.77976770124286</v>
       </c>
       <c r="D2055" t="n">
         <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.138285829956848</v>
       </c>
       <c r="F2055" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.633599162775577</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.777060940400495</v>
       </c>
       <c r="D2056" t="n">
         <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.092808849963343</v>
       </c>
       <c r="F2056" t="n">
         <v>1.31612688801001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.566737073206502</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.77848974254373</v>
       </c>
       <c r="D2057" t="n">
         <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.036230228703678</v>
       </c>
       <c r="F2057" t="n">
         <v>1.171108329502762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.481154740245387</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.878420981801483</v>
       </c>
       <c r="D2058" t="n">
         <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.088824761647544</v>
       </c>
       <c r="F2058" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.587497602640874</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.876206678927422</v>
       </c>
       <c r="D2059" t="n">
         <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.066046289845199</v>
       </c>
       <c r="F2059" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.585283299766813</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.876109807001711</v>
       </c>
       <c r="D2060" t="n">
         <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.034181637436388</v>
       </c>
       <c r="F2060" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.585186427841102</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.876103700559754</v>
       </c>
       <c r="D2061" t="n">
         <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>1.995990331827544</v>
       </c>
       <c r="F2061" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.585180321399145</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.874200097122364</v>
       </c>
       <c r="D2062" t="n">
         <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.019837092730441</v>
       </c>
       <c r="F2062" t="n">
         <v>1.246170278916367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.621902264472185</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.879933914870091</v>
       </c>
       <c r="D2063" t="n">
         <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>2.00342324562529</v>
       </c>
       <c r="F2063" t="n">
         <v>1.246170278916367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.627636082219912</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.879472278213024</v>
       </c>
       <c r="D2064" t="n">
         <v>-4.708604079325242</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.028997789445559</v>
+        <v>1.995674222169179</v>
       </c>
       <c r="F2064" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645434150485719</v>
+        <v>4.612110583209339</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.899346671063342</v>
       </c>
       <c r="D2065" t="n">
         <v>-4.620397245177664</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.084154915954909</v>
+        <v>2.050831348678529</v>
       </c>
       <c r="F2065" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665308543336037</v>
+        <v>4.631984976059657</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.88304737158807</v>
       </c>
       <c r="D2066" t="n">
         <v>-4.514362249972354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.11026961456176</v>
+        <v>2.07694604728538</v>
       </c>
       <c r="F2066" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.649009243860765</v>
+        <v>4.615685676584385</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.885478321052116</v>
       </c>
       <c r="D2067" t="n">
         <v>-4.331150586839259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.185985229279044</v>
+        <v>2.152661662002664</v>
       </c>
       <c r="F2067" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.65144019332481</v>
+        <v>4.618116626048431</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.884593074176385</v>
+        <v>3.851269506900006</v>
       </c>
       <c r="D2068" t="n">
         <v>-4.259429139825408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.180464993932474</v>
+        <v>2.147141426656095</v>
       </c>
       <c r="F2068" t="n">
         <v>1.292785288674375</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.660264247381011</v>
+        <v>4.626940680104632</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.831508820097557</v>
+        <v>3.798185252821177</v>
       </c>
       <c r="D2069" t="n">
         <v>-4.237056114217702</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.136329950096728</v>
+        <v>2.103006382820348</v>
       </c>
       <c r="F2069" t="n">
         <v>1.304041039787277</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.613933443969923</v>
+        <v>4.580609876693543</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.016707024982912</v>
+        <v>3.983383457706533</v>
       </c>
       <c r="D2070" t="n">
         <v>-4.270072410128447</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.308321636617785</v>
+        <v>2.274998069341406</v>
       </c>
       <c r="F2070" t="n">
         <v>1.234603663120525</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.757469222855227</v>
+        <v>4.724145655578848</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.008628250811161</v>
+        <v>3.975304683534782</v>
       </c>
       <c r="D2071" t="n">
         <v>-4.258544774478838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.304853916705878</v>
+        <v>2.271530349429499</v>
       </c>
       <c r="F2071" t="n">
         <v>1.293604321321888</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.784790843604294</v>
+        <v>4.751467276327915</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>3.978972796056571</v>
       </c>
       <c r="D2072" t="n">
         <v>-4.355886275821207</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.269585428690719</v>
+        <v>2.23626186141434</v>
       </c>
       <c r="F2072" t="n">
         <v>1.249184139156399</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.761806846826789</v>
+        <v>4.72848327955041</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>3.980223878249409</v>
       </c>
       <c r="D2073" t="n">
         <v>-4.441742305161173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.236494099147571</v>
+        <v>2.203170531871192</v>
       </c>
       <c r="F2073" t="n">
         <v>1.206808069930264</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.737632287483946</v>
+        <v>4.704308720207568</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>3.962643080069911</v>
       </c>
       <c r="D2074" t="n">
         <v>-4.450579102577293</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.215378582001625</v>
+        <v>2.182055014725246</v>
       </c>
       <c r="F2074" t="n">
         <v>1.199365897288914</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.715586185719638</v>
+        <v>4.682262618443259</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>3.97280759111496</v>
       </c>
       <c r="D2075" t="n">
         <v>-4.541961665142751</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.188990068020491</v>
+        <v>2.155666500744112</v>
       </c>
       <c r="F2075" t="n">
         <v>1.162801012569569</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.70381176593308</v>
+        <v>4.670488198656702</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.074935848939228</v>
       </c>
       <c r="D2076" t="n">
         <v>-4.530254947155745</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.295801013039561</v>
+        <v>2.262477445763182</v>
       </c>
       <c r="F2076" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.812964054549552</v>
+        <v>4.779640487273173</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.077968187670633</v>
       </c>
       <c r="D2077" t="n">
         <v>-4.601167020898023</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.270468522274054</v>
+        <v>2.237144954997676</v>
       </c>
       <c r="F2077" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.815996393280956</v>
+        <v>4.782672826004578</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.290873020948691</v>
       </c>
       <c r="D2078" t="n">
         <v>-4.611483119064375</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.479246916285571</v>
+        <v>2.445923349009193</v>
       </c>
       <c r="F2078" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.028901226559015</v>
+        <v>4.995577659282636</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.290051687860781</v>
       </c>
       <c r="D2079" t="n">
         <v>-4.611389151047002</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.47846317040461</v>
+        <v>2.445139603128232</v>
       </c>
       <c r="F2079" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.028301810279495</v>
+        <v>4.994978243003117</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.284283673805135</v>
       </c>
       <c r="D2080" t="n">
         <v>-4.759755378703147</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.413348665286506</v>
+        <v>2.380025098010128</v>
       </c>
       <c r="F2080" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.022533796223849</v>
+        <v>4.989210228947471</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.284283673805135</v>
       </c>
       <c r="D2081" t="n">
         <v>-4.758806955585109</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.413728034533722</v>
+        <v>2.380404467257343</v>
       </c>
       <c r="F2081" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.022533796223849</v>
+        <v>4.989210228947471</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.297011281786227</v>
       </c>
       <c r="D2082" t="n">
         <v>-4.85907677354413</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.386347715331205</v>
+        <v>2.353024148054827</v>
       </c>
       <c r="F2082" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.035261404204941</v>
+        <v>5.001937836928563</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.298957280210614</v>
       </c>
       <c r="D2083" t="n">
         <v>-4.853084526755318</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.390690612471117</v>
+        <v>2.357367045194739</v>
       </c>
       <c r="F2083" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.037207402629329</v>
+        <v>5.00388383535295</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.292611416228383</v>
       </c>
       <c r="D2084" t="n">
         <v>-4.764526565624551</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.419767932941193</v>
+        <v>2.386444365664815</v>
       </c>
       <c r="F2084" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.030861538647097</v>
+        <v>4.997537971370719</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.291920093667379</v>
       </c>
       <c r="D2085" t="n">
         <v>-4.746767488121477</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.426180241381418</v>
+        <v>2.39285667410504</v>
       </c>
       <c r="F2085" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.030170216086093</v>
+        <v>4.996846648809715</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.304702279575966</v>
       </c>
       <c r="D2086" t="n">
         <v>-4.647137337072409</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.478814487709633</v>
+        <v>2.445490920433254</v>
       </c>
       <c r="F2086" t="n">
         <v>1.274507742952961</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.10273049262412</v>
+        <v>5.069406925347742</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.493856545074692</v>
       </c>
       <c r="D2087" t="n">
         <v>-4.69653684576142</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.648208949732754</v>
+        <v>2.614885382456376</v>
       </c>
       <c r="F2087" t="n">
         <v>1.284766576384706</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.298040058181893</v>
+        <v>5.264716490905515</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.481045218177554</v>
       </c>
       <c r="D2088" t="n">
         <v>-4.489852372119044</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.718071412292566</v>
+        <v>2.684747845016188</v>
       </c>
       <c r="F2088" t="n">
         <v>1.491451050027081</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.409239415470181</v>
+        <v>5.375915848193803</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.483046731831659</v>
       </c>
       <c r="D2089" t="n">
         <v>-4.52400926711657</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.706410167947661</v>
+        <v>2.673086600671283</v>
       </c>
       <c r="F2089" t="n">
         <v>1.407867280486269</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.361090667399798</v>
+        <v>5.32776710012342</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.836543845821327</v>
       </c>
       <c r="D2090" t="n">
         <v>-4.431419788055114</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.096943073561911</v>
+        <v>3.063619506285533</v>
       </c>
       <c r="F2090" t="n">
         <v>1.407867280486269</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.714587781389466</v>
+        <v>5.681264214113088</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.874430524664808</v>
+        <v>4.84110695738843</v>
       </c>
       <c r="D2091" t="n">
         <v>-4.491308415878664</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.077550733999594</v>
+        <v>3.044227166723216</v>
       </c>
       <c r="F2091" t="n">
         <v>1.393745365798804</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.710677744144091</v>
+        <v>5.677354176867713</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.924260465988335</v>
+        <v>4.890936898711957</v>
       </c>
       <c r="D2092" t="n">
         <v>-4.439092106082322</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.148267199241658</v>
+        <v>3.11494363196528</v>
       </c>
       <c r="F2092" t="n">
         <v>1.393745365798804</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.760507685467618</v>
+        <v>5.72718411819124</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.933074436198346</v>
+        <v>4.899750868921968</v>
       </c>
       <c r="D2093" t="n">
         <v>-4.407194588997077</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.169840176285768</v>
+        <v>3.13651660900939</v>
       </c>
       <c r="F2093" t="n">
         <v>1.42564288288405</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.788460165928776</v>
+        <v>5.755136598652398</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.928712020237543</v>
+        <v>4.895388452961165</v>
       </c>
       <c r="D2094" t="n">
         <v>-4.421949913197217</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.159575630644908</v>
+        <v>3.12625206336853</v>
       </c>
       <c r="F2094" t="n">
         <v>1.42564288288405</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.784097749967973</v>
+        <v>5.750774182691595</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.919636523653823</v>
+        <v>4.886312956377445</v>
       </c>
       <c r="D2095" t="n">
         <v>-4.372485289827305</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.170285983409153</v>
+        <v>3.136962416132775</v>
       </c>
       <c r="F2095" t="n">
         <v>1.475107506253962</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.804701027406201</v>
+        <v>5.771377460129822</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.916044191368758</v>
+        <v>4.88272062409238</v>
       </c>
       <c r="D2096" t="n">
         <v>-4.20937729767369</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.231936847985533</v>
+        <v>3.198613280709155</v>
       </c>
       <c r="F2096" t="n">
         <v>1.638215498407577</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.898973490413304</v>
+        <v>5.865649923136925</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.925091228059886</v>
+        <v>4.891767660783508</v>
       </c>
       <c r="D2097" t="n">
         <v>-4.076569672176523</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.294106934875528</v>
+        <v>3.26078336759915</v>
       </c>
       <c r="F2097" t="n">
         <v>1.638215498407577</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.908020527104432</v>
+        <v>5.874696959828054</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.872163648396344</v>
+        <v>3.840844385492103</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.925948693046007</v>
+        <v>4.892625125769629</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.124772746419541</v>
+        <v>-4.139277588651082</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.275683170164442</v>
+        <v>3.236557665995448</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.590012424164559</v>
+        <v>1.575507581933019</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.879956147544743</v>
+        <v>5.837929674929441</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240926.xlsx
+++ b/tame_output/ON/bt/strategyON_20240926.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>96.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>177.6%</t>
+          <t>181.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.9%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.5%</t>
+          <t>-573.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.6%</t>
+          <t>-48.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>359.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.2%</t>
+          <t>-322.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-64.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.0%</t>
+          <t>135.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>137.8%</t>
+          <t>142.5%</t>
         </is>
       </c>
     </row>
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.382748841269072</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.1932816125882724</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.300473542660733</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.379890222636664</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.557873258655615</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2487761587953732</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.475597960047277</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.289370792952255</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.792325352670105</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3497761613027648</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.475597960047277</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.282151628050659</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.896700083696551</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.3981982444873196</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.579972691073723</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.212854598660815</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-9.059213549395135</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.4620878409281972</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.67760612149241</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.15539033024816</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.185250342763425</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.5098088296463983</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.652354498682667</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.173235032563119</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.128178570867494</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.4829897852016249</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.652354498682667</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.177225368249521</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.269850412591614</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.5411337487900147</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.652354498682667</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.175750141350779</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.22025956816678</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.5062440008552089</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.602763654257834</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.220558058170552</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.071341233694923</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.4597278007131491</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.571514063522661</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.226256678964972</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.845496080975513</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.3598106665891767</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.529587387935497</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.260991757353479</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.720917424637921</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.3088400594980807</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.529587387935497</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.262130901909538</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.695880743069411</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.2961916127085691</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.504258300384761</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.279962128602087</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.62374756778153</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.2616046383547803</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.504258300384761</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.285695832840724</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.576075471757756</v>
+        <v>-8.552381175171883</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2522730623391358</v>
+        <v>-0.2427953437047865</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.432891907775113</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.304561828061122</v>
+        <v>2.318778406012647</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.482616437772531</v>
+        <v>-8.458922141186658</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2247729300579535</v>
+        <v>-0.2152952114236042</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.432891907775113</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.294678346748215</v>
+        <v>2.308894924699739</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.4719632562191</v>
+        <v>-8.448268959633227</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2223462179359545</v>
+        <v>-0.2128684993016052</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.432891907775113</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.292843786248842</v>
+        <v>2.307060364200366</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.374056217542609</v>
+        <v>-8.350361920956736</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1834837174388193</v>
+        <v>-0.17400599880447</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.388600454500431</v>
+        <v>-1.364906157914557</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.333334921191714</v>
+        <v>2.347551499143239</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.350102676566651</v>
+        <v>-8.326408379980778</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1732337949029423</v>
+        <v>-0.163756076268593</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.364646913524473</v>
+        <v>-1.340952616938599</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.348375551922782</v>
+        <v>2.362592129874307</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.086042738243854</v>
+        <v>-8.062348441657981</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08087013573557567</v>
+        <v>-0.07139241710122679</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.076892678615803</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.493551198754708</v>
+        <v>2.507767776706233</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.378963114739016</v>
+        <v>-7.355268818153143</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1991746800060588</v>
+        <v>0.2086523986404076</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.076892678615803</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.490764165094407</v>
+        <v>2.504980743045932</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.338778816372826</v>
+        <v>-7.315084519786953</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2155920232403763</v>
+        <v>0.2250697418747252</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.060402676835486</v>
+        <v>-1.036708380249612</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.529434945953487</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.175378945433463</v>
+        <v>-7.15168464884759</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2803187928368782</v>
+        <v>0.2897965114712271</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8970028058961237</v>
+        <v>-0.8733085093102497</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.626841689737862</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.017261566054688</v>
+        <v>-6.993567269468815</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3514901734262406</v>
+        <v>0.3609678920605899</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7388854265173482</v>
+        <v>-0.7151911299314743</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.715419968251455</v>
+        <v>2.729636546202979</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.867595175047173</v>
+        <v>-6.8439008784613</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4084645195162873</v>
+        <v>0.4179422381506366</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6459819352748123</v>
+        <v>-0.6222876386889383</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.768269852684018</v>
+        <v>2.782486430635542</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.023796232579679</v>
+        <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.735319701416286</v>
+        <v>-6.711625404830413</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.329311927699417</v>
+        <v>0.3721132136101457</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5137064616439256</v>
+        <v>-0.4900121650580517</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.715572355593324</v>
+        <v>2.763112500821229</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.026611293267316</v>
+        <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.563458485851384</v>
+        <v>-6.539764189265511</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4008714746130146</v>
+        <v>0.4436727605237438</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3418452460790228</v>
+        <v>-0.3181509494931488</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.821504145619903</v>
+        <v>2.869044290847807</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.039517634490975</v>
+        <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.478493819122065</v>
+        <v>-6.454799522536192</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.447763682528401</v>
+        <v>0.4905649684391302</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2568805793497032</v>
+        <v>-0.2331862827638292</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.885389286881153</v>
+        <v>2.932929432109058</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.911541704891756</v>
+        <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.584083808895169</v>
+        <v>-6.560389512309296</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2775517570199404</v>
+        <v>0.3203530429306696</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3624705691228076</v>
+        <v>-0.3387762725369336</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.694059363418072</v>
+        <v>2.741599508645976</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.960086046768843</v>
+        <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.515849224269742</v>
+        <v>-6.492154927683869</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3533899327471977</v>
+        <v>0.3961912186579268</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3440552462502716</v>
+        <v>-0.3203609496643976</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.75365289901868</v>
+        <v>2.801193044246584</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.843465238130436</v>
+        <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.367909182862142</v>
+        <v>-6.344214886276269</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2959451406718303</v>
+        <v>0.3387464265825595</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.323734330341714</v>
+        <v>-0.30004003375584</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.649224639925408</v>
+        <v>2.696764785153312</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.834751251876957</v>
+        <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.314939660608154</v>
+        <v>-6.291245364022281</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3084189633199479</v>
+        <v>0.3512202492306766</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.2470705115018512</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.672292367024323</v>
+        <v>2.719832512252227</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.827790639781864</v>
+        <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.149151464647863</v>
+        <v>-6.12545716806199</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3677736296089709</v>
+        <v>0.4105749155197</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.2470705115018512</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.665331754929229</v>
+        <v>2.712871900157134</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.842252994163007</v>
+        <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.115788258169094</v>
+        <v>-6.092093961583221</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3955812665816216</v>
+        <v>0.4383825524923504</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.2470705115018512</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.679794109310373</v>
+        <v>2.727334254538277</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.836785114622202</v>
+        <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.007529121046573</v>
+        <v>-5.9838348244607</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4334170418898253</v>
+        <v>0.4762183278005545</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.2470705115018512</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.674326229769568</v>
+        <v>2.721866374997472</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.834283208632779</v>
+        <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.884237986229442</v>
+        <v>-5.860543689643569</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4802315898272544</v>
+        <v>0.5230328757379836</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1474736732705946</v>
+        <v>-0.1237793766847207</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.745799004670423</v>
+        <v>2.793339149898327</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.841984186870104</v>
+        <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.831541119098151</v>
+        <v>-5.807846822512277</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5090113149170961</v>
+        <v>0.5518126008278252</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.09477680613930345</v>
+        <v>-0.07108250955342948</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.785118103186523</v>
+        <v>2.832658248414427</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.837764895217155</v>
+        <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.587775677114706</v>
+        <v>-5.564081380528833</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6022982000575245</v>
+        <v>0.6450994859682537</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.09477680613930345</v>
+        <v>-0.07108250955342948</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.780898811533573</v>
+        <v>2.828438956761477</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.839889209137171</v>
+        <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.498000004738234</v>
+        <v>-5.474305708152361</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6403327829281293</v>
+        <v>0.6831340688388585</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.009483064639119465</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.819982792402175</v>
+        <v>2.867522937630079</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.832631284120873</v>
+        <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.248149610789159</v>
+        <v>-5.224455314203286</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7330150154914614</v>
+        <v>0.7758163014021906</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.009483064639119465</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.812724867385878</v>
+        <v>2.860265012613782</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.836230407641522</v>
+        <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.072257518321727</v>
+        <v>-5.048563221735854</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8069709759990831</v>
+        <v>0.8497722619098123</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.009483064639119465</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.816323990906526</v>
+        <v>2.86386413613443</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.849557913696076</v>
+        <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.900811055299264</v>
+        <v>-4.877116758713391</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8888770672626221</v>
+        <v>0.9316783531733512</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1382691017974697</v>
+        <v>0.1619633983833437</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.932519374774558</v>
+        <v>2.980059520002462</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.848578391312373</v>
+        <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.820788768190143</v>
+        <v>-4.79709447160427</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9199064597225675</v>
+        <v>0.9627077456332964</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2182913889065907</v>
+        <v>0.2419856854924646</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.979553224656327</v>
+        <v>3.027093369884231</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.85327319236669</v>
+        <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.757153025956208</v>
+        <v>-4.733458729370335</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9500555576704586</v>
+        <v>0.9928568435811875</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2819271311405252</v>
+        <v>0.3056214277263992</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.022429471051005</v>
+        <v>3.06996961627891</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.834467451150485</v>
+        <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.663455707739813</v>
+        <v>-4.63976141115394</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9687287437408121</v>
+        <v>1.011530029651541</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2819271311405252</v>
+        <v>0.3056214277263992</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.003623729834801</v>
+        <v>3.051163875062705</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.836210527775363</v>
+        <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.673958330805102</v>
+        <v>-4.650264034219229</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9662707711395739</v>
+        <v>1.009072057050303</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2714245080752363</v>
+        <v>0.2951188046611103</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.999065232620505</v>
+        <v>3.046605377848409</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.840139841610183</v>
+        <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.561472070136228</v>
+        <v>-4.537777773550355</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.015194589241944</v>
+        <v>1.057995875152673</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2714245080752363</v>
+        <v>0.2951188046611103</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.002994546455325</v>
+        <v>3.050534691683229</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.840818425527523</v>
+        <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.543758383258362</v>
+        <v>-4.520064086672489</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.02295864791043</v>
+        <v>1.065759933821159</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2746058369721531</v>
+        <v>0.2983001335580271</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.005581927710815</v>
+        <v>3.05312207293872</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.837816496747517</v>
+        <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.420284111945344</v>
+        <v>-4.396589815359471</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.069346427655631</v>
+        <v>1.11214771356636</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2746058369721531</v>
+        <v>0.2983001335580271</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.002579998930809</v>
+        <v>3.050120144158713</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.839395533758131</v>
+        <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.200263313908334</v>
+        <v>-4.176569017322461</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.158933783881049</v>
+        <v>1.201735069791778</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4158256820401334</v>
+        <v>0.4395199786260073</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.088890942982211</v>
+        <v>3.136431088210115</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.855289716559954</v>
+        <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.067395624845056</v>
+        <v>-4.043701328259183</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.227975042308184</v>
+        <v>1.270776328218913</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4158256820401334</v>
+        <v>0.4395199786260073</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.104785125784034</v>
+        <v>3.152325271011938</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.856435561000256</v>
+        <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.947222541480557</v>
+        <v>-3.923528244894684</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.277190120094285</v>
+        <v>1.319991406005014</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5359987654046323</v>
+        <v>0.5596930619905063</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.178034820243036</v>
+        <v>3.22557496547094</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.866523663561696</v>
+        <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.81196918015058</v>
+        <v>-3.788274883564707</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.341379567187716</v>
+        <v>1.384180853098445</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6712521267346094</v>
+        <v>0.6949464233204834</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.269274939602462</v>
+        <v>3.316815084830366</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.852561154963122</v>
+        <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.871844007508273</v>
+        <v>-3.848149710922399</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.303467127646065</v>
+        <v>1.346268413556794</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6113772993769173</v>
+        <v>0.6350715959627913</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.219387534589272</v>
+        <v>3.266927679817177</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.86785032419733</v>
+        <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.752023776597435</v>
+        <v>-3.728329480011562</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.366684389244608</v>
+        <v>1.409485675155337</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6113772993769173</v>
+        <v>0.6350715959627913</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.234676703823481</v>
+        <v>3.282216849051385</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.775494523519772</v>
+        <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.754493483059241</v>
+        <v>-3.730799186473368</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.273340705982327</v>
+        <v>1.316141991893056</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6089075929151111</v>
+        <v>0.6326018895009851</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.140839079268839</v>
+        <v>3.188379224496743</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.694756385005073</v>
+        <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.822863669383251</v>
+        <v>-3.799169372797378</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.165254492938025</v>
+        <v>1.208055778848754</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6418775885372</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.065666360175869</v>
+        <v>3.113206505403773</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.685193093636964</v>
+        <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.934735949009402</v>
+        <v>-3.911041652423529</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.110942289719456</v>
+        <v>1.153743575630185</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6418775885372</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.05610306880776</v>
+        <v>3.103643214035665</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.651767618560992</v>
+        <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.918761283523134</v>
+        <v>-3.895066986937261</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.08390668083799</v>
+        <v>1.126707966748719</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6418775885372</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.022677593731788</v>
+        <v>3.070217738959692</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205895</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.65633485055278</v>
+        <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.743287023730665</v>
+        <v>-3.719592727144791</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.158663616746766</v>
+        <v>1.201464902657495</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6418775885372</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.027244825723575</v>
+        <v>3.074784970951479</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.632076879313987</v>
+        <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.73536264914575</v>
+        <v>-3.711668352559877</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.137575395341939</v>
+        <v>1.180376681252667</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.618183291951326</v>
+        <v>0.6418775885372</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.002986854484782</v>
+        <v>3.050526999712686</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.560615192715436</v>
+        <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.729084446575901</v>
+        <v>-3.705390149990028</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.068624989771328</v>
+        <v>1.111426275682057</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.648155791107049</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.935292089428142</v>
+        <v>2.982832234656046</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.570787579147569</v>
+        <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.669231827372178</v>
+        <v>-3.645537530786305</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.102738423884949</v>
+        <v>1.145539709795679</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.648155791107049</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.945464475860274</v>
+        <v>2.993004621088178</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.565733849721429</v>
+        <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.582988364345801</v>
+        <v>-3.559294067759928</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.132182079669361</v>
+        <v>1.17498336558009</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.648155791107049</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.940410746434134</v>
+        <v>2.987950891662039</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.557509625165955</v>
+        <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.628295183744781</v>
+        <v>-3.604600887158908</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.105835127354294</v>
+        <v>1.148636413265023</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5836513315119443</v>
+        <v>0.6073456280978182</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.907700424073121</v>
+        <v>2.955240569301026</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.558061498199056</v>
+        <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.657328288447082</v>
+        <v>-3.633633991861209</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.094773758506475</v>
+        <v>1.137575044417204</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5836513315119443</v>
+        <v>0.6073456280978182</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.908252297106223</v>
+        <v>2.955792442334127</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.487334190090422</v>
+        <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.564517806996223</v>
+        <v>-3.54082351041035</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.061170642978185</v>
+        <v>1.103971928888914</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6764618129628036</v>
+        <v>0.7001561095486776</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.893211277868104</v>
+        <v>2.940751423096009</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.489207666015023</v>
+        <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.608907276325651</v>
+        <v>-3.585212979739778</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.045288331171014</v>
+        <v>1.088089617081744</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6320723436333759</v>
+        <v>0.6557666402192499</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.868451072195048</v>
+        <v>2.915991217422953</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.484283374526746</v>
+        <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.588403582440153</v>
+        <v>-3.56470928585428</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.048565517236936</v>
+        <v>1.091366803147665</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6525760375188733</v>
+        <v>0.6762703341047472</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.87582899703807</v>
+        <v>2.923369142265974</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.489774670357413</v>
+        <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.628327677022726</v>
+        <v>-3.604633380436852</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.038087175234575</v>
+        <v>1.080888461145304</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6525760375188733</v>
+        <v>0.6762703341047472</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.881320292868737</v>
+        <v>2.928860438096641</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.501271872125952</v>
+        <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.656108074924079</v>
+        <v>-3.632413778338206</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.038472217842572</v>
+        <v>1.081273503753302</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6247956396175203</v>
+        <v>0.6484899362033942</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.876149255896464</v>
+        <v>2.923689401124369</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.339627592126605</v>
+        <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.774488747654217</v>
+        <v>-3.750794451068344</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8294756687511704</v>
+        <v>0.8722769546618996</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.581272084052418</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.674174264606532</v>
+        <v>2.721714409834436</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.459777252845811</v>
+        <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.883102826097548</v>
+        <v>-3.859408529511675</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9061796980930437</v>
+        <v>0.9489809840037726</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.581272084052418</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.794323925325738</v>
+        <v>2.841864070553642</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.474290278948134</v>
+        <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.847693787849405</v>
+        <v>-3.823999491263532</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9348563394946237</v>
+        <v>0.9776576254053528</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.581272084052418</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.808836951428061</v>
+        <v>2.856377096655965</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.471709720290503</v>
+        <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.856154956504867</v>
+        <v>-3.832460659918993</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.928891313374808</v>
+        <v>0.971692599285537</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.549116618811083</v>
+        <v>0.5728109153969569</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.801179691577153</v>
+        <v>2.848719836805057</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.468438749135805</v>
+        <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.6790386264697</v>
+        <v>-3.655344329883827</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9964668742341767</v>
+        <v>1.039268160144906</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.549116618811083</v>
+        <v>0.5728109153969569</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.797908720422455</v>
+        <v>2.845448865650359</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.469122140897718</v>
+        <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.724130871303246</v>
+        <v>-3.700436574717373</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9791133680626716</v>
+        <v>1.021914653973401</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4872205756416932</v>
+        <v>0.5109148722275672</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.761454486282734</v>
+        <v>2.808994631510638</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.462909116204132</v>
+        <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.544755450064478</v>
+        <v>-3.521061153478605</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.044650511864593</v>
+        <v>1.087451797775322</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6439973338124119</v>
+        <v>0.6676916303982858</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.84930751649158</v>
+        <v>2.896847661719484</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982224</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.443716571535722</v>
+        <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.589769663585085</v>
+        <v>-3.566075366999212</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.00745228178794</v>
+        <v>1.050253567698669</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6136484384978073</v>
+        <v>0.6373427350836812</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.811905634634407</v>
+        <v>2.859445779862311</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.449408133874668</v>
+        <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.85677417385752</v>
+        <v>-3.833079877271647</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9063420400179119</v>
+        <v>0.9491433259286408</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4192854004548587</v>
+        <v>0.4429796970407326</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.700979374147583</v>
+        <v>2.748519519375487</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.448612055771169</v>
+        <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.957971955294693</v>
+        <v>-3.93427765870882</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8650668493395441</v>
+        <v>0.9078681352502733</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3508765869095395</v>
+        <v>0.3745708834954135</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.659138007916893</v>
+        <v>2.706678153144797</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.446212017325486</v>
+        <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.95146098868038</v>
+        <v>-3.927766692094507</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8652711975395859</v>
+        <v>0.9080724834503151</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3508765869095395</v>
+        <v>0.3745708834954135</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.65673796947121</v>
+        <v>2.704278114699114</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.442736736533731</v>
+        <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.932422860973083</v>
+        <v>-3.90872856438721</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8694111678307497</v>
+        <v>0.9122124537414789</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2926929755783449</v>
+        <v>0.3163872721642189</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.618352521880738</v>
+        <v>2.665892667108642</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.562031138167921</v>
+        <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.984938663247903</v>
+        <v>-3.96124436666203</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9676992485550122</v>
+        <v>1.010500534465741</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2926929755783449</v>
+        <v>0.3163872721642189</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.737646923514928</v>
+        <v>2.785187068742833</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.562864467154055</v>
+        <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.988346974682483</v>
+        <v>-3.96465267809661</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9671692529673137</v>
+        <v>1.009970538878043</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3252095445877223</v>
+        <v>0.3489038411735963</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.757990193906688</v>
+        <v>2.805530339134592</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.568872997550981</v>
+        <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.968990838788636</v>
+        <v>-3.945296542202763</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9809202377217785</v>
+        <v>1.023721523632508</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3252095445877223</v>
+        <v>0.3489038411735963</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.763998724303614</v>
+        <v>2.811538869531518</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.46682321882818</v>
+        <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.821247868553634</v>
+        <v>-3.79755357196776</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9379676470929788</v>
+        <v>0.9807689330037079</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4930169018226055</v>
+        <v>0.5167111984084795</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.762633359921744</v>
+        <v>2.810173505149648</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.469616840359661</v>
+        <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.905069089828332</v>
+        <v>-3.881374793242458</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9072327801145805</v>
+        <v>0.9500340660253097</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4930169018226055</v>
+        <v>0.5167111984084795</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.765426981453225</v>
+        <v>2.812967126681129</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394725</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.47027918875132</v>
+        <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.898916383775547</v>
+        <v>-3.875222087189674</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9103562109273526</v>
+        <v>0.9531574968380818</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4991696078753898</v>
+        <v>0.5228639044612637</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.769780953476554</v>
+        <v>2.817321098704458</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.46935966549143</v>
+        <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.915725681926049</v>
+        <v>-3.892031385340176</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9027129684072623</v>
+        <v>0.9455142543179915</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4823603097248881</v>
+        <v>0.506054606310762</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.758775851326363</v>
+        <v>2.806315996554267</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.535695219288251</v>
+        <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.853427683149927</v>
+        <v>-3.829733386564054</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.993967721714532</v>
+        <v>1.036769007625261</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5276545739993301</v>
+        <v>0.5513488705852041</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.852287963687849</v>
+        <v>2.899828108915753</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.337987221002378</v>
+        <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.651637485484769</v>
+        <v>-3.627943188898896</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8769758024947223</v>
+        <v>0.9197770884054512</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7256727661684845</v>
+        <v>0.7493670627543585</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.773390880703469</v>
+        <v>2.820931025931373</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.408277453324553</v>
+        <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.702524198170964</v>
+        <v>-3.67882990158509</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9269113497424195</v>
+        <v>0.9697126356531487</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.67478605348229</v>
+        <v>0.698480350068164</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.813149085413927</v>
+        <v>2.860689230641832</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.422905189440597</v>
+        <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.615913455521156</v>
+        <v>-3.592219158935283</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9761833829183861</v>
+        <v>1.018984668829115</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7534117846874483</v>
+        <v>0.7771060812733223</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.874952260253066</v>
+        <v>2.92249240548097</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.421441170265268</v>
+        <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.676122753526441</v>
+        <v>-3.652428456940568</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9506356445409441</v>
+        <v>0.993436930451673</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.7168967832680377</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.837362662274567</v>
+        <v>2.884902807502471</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.419932788305197</v>
+        <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.626936104842089</v>
+        <v>-3.603241808256216</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9688019220546131</v>
+        <v>1.011603207965342</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.7168967832680377</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.835854280314495</v>
+        <v>2.8833944255424</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.419795655740633</v>
+        <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.582562973203521</v>
+        <v>-3.558868676617648</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9864140421454768</v>
+        <v>1.029215328056206</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.7612699149066063</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.862341026733073</v>
+        <v>2.909881171960977</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.414189449879224</v>
+        <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.54783165188502</v>
+        <v>-3.524137355299147</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9947003648114676</v>
+        <v>1.037501650722197</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.7612699149066063</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.856734820871663</v>
+        <v>2.904274966099567</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.420571206907028</v>
+        <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.500175921323964</v>
+        <v>-3.476481624738091</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.020144414063695</v>
+        <v>1.062945699974424</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.785231348881788</v>
+        <v>0.808925645467662</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.891710016236101</v>
+        <v>2.939250161464006</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.425463580281753</v>
+        <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.39965776282521</v>
+        <v>-3.375963466239337</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.065244050837921</v>
+        <v>1.10804533674865</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8857495073805426</v>
+        <v>0.9094438039664166</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.956913284710079</v>
+        <v>3.004453429937983</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.412218252757625</v>
+        <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.383752433392857</v>
+        <v>-3.360058136806984</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.058360855086734</v>
+        <v>1.101162140997463</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8066368466713036</v>
+        <v>0.8303311432571776</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.896200360760408</v>
+        <v>2.943740505988312</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.416315955368254</v>
+        <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.338914031784459</v>
+        <v>-3.315219735198586</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.080393918340722</v>
+        <v>1.123195204251451</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8111802796161731</v>
+        <v>0.8348745762020471</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.903024123137958</v>
+        <v>2.950564268365862</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.420476894999332</v>
+        <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.358412488026467</v>
+        <v>-3.334718191440594</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.076755475474997</v>
+        <v>1.119556761385726</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7630956383362688</v>
+        <v>0.7867899349221428</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.878334278001093</v>
+        <v>2.925874423228997</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.426356497527169</v>
+        <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.314209650940567</v>
+        <v>-3.290515354354694</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.100316212837194</v>
+        <v>1.143117498747923</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8072984754221693</v>
+        <v>0.8309927720080432</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.910735582780471</v>
+        <v>2.958275728008375</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.424766497996417</v>
+        <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.321769316777614</v>
+        <v>-3.298075020191741</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.095702346971623</v>
+        <v>1.138503632882352</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.8857961760178625</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.94202762565561</v>
+        <v>2.989567770883514</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.476014263179456</v>
+        <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.163477899238341</v>
+        <v>-3.139783602652468</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.210266679170372</v>
+        <v>1.253067965081101</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.8857961760178625</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.99327539083865</v>
+        <v>3.040815536066554</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.474454967773709</v>
+        <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.955835895603865</v>
+        <v>-2.932141599017992</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.291764185218415</v>
+        <v>1.334565471129144</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.069743883066465</v>
+        <v>1.093438179652339</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.116301297613588</v>
+        <v>3.163841442841492</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.469403196011979</v>
+        <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.904803802881337</v>
+        <v>-2.881109506295464</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.307125250545697</v>
+        <v>1.349926536456426</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.120775975788993</v>
+        <v>1.144470272374867</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.141868781485375</v>
+        <v>3.18940892671328</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.486590600104684</v>
+        <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.839579621754131</v>
+        <v>-2.815885325168258</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.350402327089284</v>
+        <v>1.393203613000013</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.186000156916198</v>
+        <v>1.209694453502072</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.198190694254404</v>
+        <v>3.245730839482308</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.482551572403965</v>
+        <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.802152601682998</v>
+        <v>-2.778458305097125</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.361334107417018</v>
+        <v>1.404135393327747</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.19125169494538</v>
+        <v>1.214945991531254</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.197302589371193</v>
+        <v>3.244842734599097</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.483808364735205</v>
+        <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.800794616709452</v>
+        <v>-2.777100320123579</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.363134093737676</v>
+        <v>1.405935379648405</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.265589820483199</v>
+        <v>1.289284117069073</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.243162257025125</v>
+        <v>3.290702402253029</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.644366135756416</v>
+        <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.772381353609568</v>
+        <v>-2.748687057023695</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.53505716999884</v>
+        <v>1.577858455909569</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.20661425773677</v>
+        <v>1.230308554322644</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.368334690398478</v>
+        <v>3.415874835626382</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.764479044974233</v>
+        <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.697599092584556</v>
+        <v>-2.673904795998683</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.685082983626663</v>
+        <v>1.727884269537392</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.281396518761783</v>
+        <v>1.305090815347657</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.533316956231303</v>
+        <v>3.580857101459207</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.756187020988092</v>
+        <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.671515008320748</v>
+        <v>-2.647820711734875</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.687224593346045</v>
+        <v>1.730025879256774</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.281396518761783</v>
+        <v>1.305090815347657</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.525024932245162</v>
+        <v>3.572565077473066</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.754380216571871</v>
+        <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.583637095211627</v>
+        <v>-2.559942798625754</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.720568954173473</v>
+        <v>1.763370240084202</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.397322161185134</v>
+        <v>1.421016457771008</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.592773513282952</v>
+        <v>3.640313658510856</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.771934622298663</v>
+        <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.574744633818344</v>
+        <v>-2.551050337232471</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.741680344457577</v>
+        <v>1.784481630368306</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.397322161185134</v>
+        <v>1.421016457771008</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.610327919009743</v>
+        <v>3.657868064237647</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.763789669703247</v>
+        <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.743220750788222</v>
+        <v>-2.719526454202349</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.66614494507421</v>
+        <v>1.708946230984939</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.369374325468553</v>
+        <v>1.393068622054427</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.585414264984379</v>
+        <v>3.632954410212283</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.745059366891109</v>
+        <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.296964558158782</v>
+        <v>-2.273270261572909</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.825917119313848</v>
+        <v>1.868718405224577</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.27465565579892</v>
+        <v>1.298349952384794</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.509852760370461</v>
+        <v>3.557392905598365</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.735723389388013</v>
+        <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.27424345447563</v>
+        <v>-2.250549157889757</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.825669583284013</v>
+        <v>1.868470869194742</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.27465565579892</v>
+        <v>1.298349952384794</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.500516782867365</v>
+        <v>3.54805692809527</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.894629515239182</v>
+        <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.403445267769672</v>
+        <v>-2.379750971183799</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.932894983817565</v>
+        <v>1.975696269728294</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.145453842504878</v>
+        <v>1.169148139090752</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.581901820742109</v>
+        <v>3.629441965970013</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.931707337732829</v>
+        <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.429319666243698</v>
+        <v>-2.405625369657825</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.959623046921601</v>
+        <v>2.002424332832331</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.190365451216619</v>
+        <v>1.214059747802493</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.6459266084628</v>
+        <v>3.693466753690704</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.928382693722374</v>
+        <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.422264976028524</v>
+        <v>-2.398570679442651</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.959120278997216</v>
+        <v>2.001921564907945</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.197420141431793</v>
+        <v>1.221114438017667</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.64683477858145</v>
+        <v>3.694374923809354</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.938388847367115</v>
+        <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.395313751702036</v>
+        <v>-2.371619455116163</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.979906922372553</v>
+        <v>2.022708208283282</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.212300487459512</v>
+        <v>1.235994784045386</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.665769139842823</v>
+        <v>3.713309285070727</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.122491979512075</v>
+        <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.416857979532824</v>
+        <v>-2.39316368294695</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.155392363385198</v>
+        <v>2.198193649295927</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.212300487459512</v>
+        <v>1.235994784045386</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.849872271987782</v>
+        <v>3.897412417215687</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.114608674415068</v>
+        <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.439266097337696</v>
+        <v>-2.415571800751823</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.138545811166242</v>
+        <v>2.181347097076971</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.212300487459512</v>
+        <v>1.235994784045386</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.841988966890776</v>
+        <v>3.88952911211868</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.116662673964706</v>
+        <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.467490332915296</v>
+        <v>-2.443796036329423</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.129310116484839</v>
+        <v>2.172111402395569</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.230277239910821</v>
+        <v>1.253971536496695</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.854829017911198</v>
+        <v>3.902369163139102</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.172916391686553</v>
+        <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.476931258803826</v>
+        <v>-2.453236962217953</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.181787463851275</v>
+        <v>2.224588749762003</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.352704357454212</v>
+        <v>1.376398654040086</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.98453900615908</v>
+        <v>4.032079151386984</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.175807486231854</v>
+        <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.5658078899723</v>
+        <v>-2.542113593386427</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.149127905929186</v>
+        <v>2.191929191839915</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.263827726285738</v>
+        <v>1.287522022871612</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.934104122003297</v>
+        <v>3.981644267231201</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.173919299125629</v>
+        <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.642137867573206</v>
+        <v>-2.618443570987333</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.116707727782599</v>
+        <v>2.159509013693328</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.263827726285738</v>
+        <v>1.287522022871612</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.932215934897072</v>
+        <v>3.979756080124976</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.168739528728491</v>
+        <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.797094652973335</v>
+        <v>-2.773400356387462</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.049545243225409</v>
+        <v>2.092346529136138</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.108870940885609</v>
+        <v>1.132565237471483</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.834062093259857</v>
+        <v>3.881602238487761</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.167173538938644</v>
+        <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.95866307850059</v>
+        <v>-2.934968781914717</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.983351883224659</v>
+        <v>2.026153169135389</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9820880170877296</v>
+        <v>1.005782313673603</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.756426349191281</v>
+        <v>3.803966494419186</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.180246945804562</v>
+        <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.06696374037071</v>
+        <v>-3.043269443784836</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.953105025342531</v>
+        <v>1.995906311253259</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9820880170877296</v>
+        <v>1.005782313673603</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.7694997560572</v>
+        <v>3.817039901285104</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.172252142587502</v>
+        <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.084767712091454</v>
+        <v>-3.061073415505581</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.937988633437173</v>
+        <v>1.980789919347901</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9115533941825285</v>
+        <v>0.9352476907684024</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.719184179097019</v>
+        <v>3.766724324324924</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.170776183714504</v>
+        <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.112668499200927</v>
+        <v>-3.088974202615054</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.925352359720385</v>
+        <v>1.968153645631115</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8769564700395936</v>
+        <v>0.9006507666254676</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.69695006573826</v>
+        <v>3.744490210966165</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.167540627691703</v>
+        <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.23519460190382</v>
+        <v>-3.211500305317947</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.873106362616427</v>
+        <v>1.915907648527156</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7544303673366998</v>
+        <v>0.7781246639225737</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.620198848093723</v>
+        <v>3.667738993321627</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.234246587282207</v>
+        <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.465709098089409</v>
+        <v>-3.442014801503536</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.847606523732695</v>
+        <v>1.890407809643424</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.523915871151111</v>
+        <v>0.547610167736985</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.548596109972873</v>
+        <v>3.596136255200778</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.374558306284054</v>
+        <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.814454183313853</v>
+        <v>-3.790759886727979</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.848420208644765</v>
+        <v>1.891221494555494</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4388622138180872</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.623659056623382</v>
+        <v>3.671199201851286</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.443538575429693</v>
+        <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.968440601089993</v>
+        <v>-3.94474630450412</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.855805910679948</v>
+        <v>1.898607196590677</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4388622138180872</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.692639325769022</v>
+        <v>3.740179470996926</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.429589777549814</v>
+        <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.173040035953002</v>
+        <v>-4.149345739367129</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.760017338854866</v>
+        <v>1.802818624765595</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4388622138180872</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.678690527889143</v>
+        <v>3.726230673117047</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.441460266605228</v>
+        <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.425515189960726</v>
+        <v>-4.401820893374853</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.67089776630719</v>
+        <v>1.713699052217919</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4388622138180872</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.690561016944557</v>
+        <v>3.738101162172461</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.442670801124172</v>
+        <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.718410946440138</v>
+        <v>-4.694716649854265</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.554949998234369</v>
+        <v>1.597751284145098</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.4388622138180872</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.6917715514635</v>
+        <v>3.739311696691404</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.446792543351493</v>
+        <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.905075074574946</v>
+        <v>-4.881380777989073</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.484406089207767</v>
+        <v>1.527207375118496</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3884289464076534</v>
+        <v>0.4121232429935273</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.679849911196086</v>
+        <v>3.72739005642399</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.441870396087683</v>
+        <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.051095761488908</v>
+        <v>-5.027401464903035</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.421075667178371</v>
+        <v>1.4638769530891</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.4030401511996703</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.669477908855961</v>
+        <v>3.717018054083865</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.604074452786727</v>
+        <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.142809770598493</v>
+        <v>-5.11911547401262</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.546594120233582</v>
+        <v>1.589395406144311</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.4030401511996703</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.831681965555005</v>
+        <v>3.879222110782909</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.598921090750541</v>
+        <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.174461429658463</v>
+        <v>-5.150767133072589</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.528780094573408</v>
+        <v>1.571581380484137</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3741773973693562</v>
+        <v>0.3978716939552301</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.823427529172155</v>
+        <v>3.870967674400059</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.609150508319032</v>
+        <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.243527484231399</v>
+        <v>-5.219833187645526</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.511383090312725</v>
+        <v>1.554184376223454</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3118065198757461</v>
+        <v>0.3355008164616201</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.79623442024448</v>
+        <v>3.843774565472384</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.618076146774935</v>
+        <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.345503606479807</v>
+        <v>-5.321809309893934</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.479518279869264</v>
+        <v>1.522319565779993</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2098303976273386</v>
+        <v>0.2335246942132125</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.743974385351338</v>
+        <v>3.791514530579242</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.61022903401911</v>
+        <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.235497323002585</v>
+        <v>-5.211803026416712</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.515673680504328</v>
+        <v>1.558474966415057</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2330349695446138</v>
+        <v>0.2567292661304877</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.750050015745879</v>
+        <v>3.797590160973783</v>
       </c>
     </row>
     <row r="2028">
@@ -48192,19 +48192,19 @@
         <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.614479044741084</v>
+        <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.092437747261659</v>
+        <v>-5.068743450675786</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.577147521522673</v>
+        <v>1.619948807433402</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2410483961345931</v>
+        <v>0.264742692720467</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.75910808242184</v>
+        <v>3.806648227649745</v>
       </c>
     </row>
     <row r="2029">
@@ -48215,19 +48215,19 @@
         <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.62173992762362</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.790991021789822</v>
+        <v>-4.767296725203948</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.704987094593944</v>
+        <v>1.747788380504673</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5661894181923043</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.947237000587479</v>
+        <v>3.994777145815383</v>
       </c>
     </row>
     <row r="2030">
@@ -48238,19 +48238,19 @@
         <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.622711105376331</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.815581266025005</v>
+        <v>-4.791886969439132</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.696122174652581</v>
+        <v>1.73892346056331</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5661894181923043</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.94820817834019</v>
+        <v>3.995748323568094</v>
       </c>
     </row>
     <row r="2031">
@@ -48261,19 +48261,19 @@
         <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.623554009756087</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.764542890018485</v>
+        <v>-4.740848593432612</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.717380429434944</v>
+        <v>1.760181715345674</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.5661894181923043</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.949051082719945</v>
+        <v>3.996591227947849</v>
       </c>
     </row>
     <row r="2032">
@@ -48284,19 +48284,19 @@
         <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.642592108630232</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.723403595151854</v>
+        <v>-4.699709298565981</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.752874246255742</v>
+        <v>1.795675532166471</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5836344164730611</v>
+        <v>0.6073287130589351</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.992772758514069</v>
+        <v>4.040312903741973</v>
       </c>
     </row>
     <row r="2033">
@@ -48307,19 +48307,19 @@
         <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.458776104754167</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.626768683133214</v>
+        <v>-4.603074386547341</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.607712207187133</v>
+        <v>1.650513493097862</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6802693284917011</v>
+        <v>0.703963625077575</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.866937701849187</v>
+        <v>3.914477847077092</v>
       </c>
     </row>
     <row r="2034">
@@ -48330,19 +48330,19 @@
         <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.462278148828131</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.557730672184746</v>
+        <v>-4.534036375598873</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.638829455640484</v>
+        <v>1.681630741551213</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7493073394401691</v>
+        <v>0.7730016360260431</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.911862552492233</v>
+        <v>3.959402697720137</v>
       </c>
     </row>
     <row r="2035">
@@ -48353,19 +48353,19 @@
         <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.446704967904213</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.393234337993785</v>
+        <v>-4.369540041407912</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.689054808392951</v>
+        <v>1.73185609430368</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.913803673631131</v>
+        <v>0.937497970217005</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.994987172082892</v>
+        <v>4.042527317310796</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.445892678340643</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.316135736451912</v>
+        <v>-4.292441439866039</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.71908195944613</v>
+        <v>1.761883245356859</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.913803673631131</v>
+        <v>0.937497970217005</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.994174882519322</v>
+        <v>4.041715027747226</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.455761457465715</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.326520931341801</v>
+        <v>-4.302826634755928</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.724796660615247</v>
+        <v>1.767597946525976</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9034184787412417</v>
+        <v>0.9271127753271157</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.99781254471046</v>
+        <v>4.045352689938365</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.526598463242141</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.345109090064026</v>
+        <v>-4.321414793478153</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.788198402902782</v>
+        <v>1.830999688813511</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8848303200190164</v>
+        <v>0.9085246166048904</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.057496655253551</v>
+        <v>4.105036800481455</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.523467474060439</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.345407636760062</v>
+        <v>-4.321713340174189</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.784947995042666</v>
+        <v>1.827749280953395</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8845317733229805</v>
+        <v>0.9082260699088545</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.054186538054227</v>
+        <v>4.101726683282132</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.52799836899983</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.244584503069635</v>
+        <v>-4.220890206483761</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.829808143458229</v>
+        <v>1.872609429368958</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8969959888073343</v>
+        <v>0.9206902853932083</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.066195962284231</v>
+        <v>4.113736107512135</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.528127622478374</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.053803142317227</v>
+        <v>-4.030108845731354</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.906249941237735</v>
+        <v>1.949051227148464</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.087777349559742</v>
+        <v>1.111471646145616</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.180794032214219</v>
+        <v>4.228334177442123</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.50796446821597</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.946839784467805</v>
+        <v>-3.923145487881932</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.9288721301151</v>
+        <v>1.971673416025829</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.146241957519543</v>
+        <v>1.169936254105417</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.195709642727697</v>
+        <v>4.243249787955601</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.542931404828029</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.891509196566043</v>
+        <v>-3.86781489998017</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.985971301887863</v>
+        <v>2.028772587798592</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.201572545421305</v>
+        <v>1.225266842007179</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.263874932080812</v>
+        <v>4.311415077308716</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.536617972729466</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.87945506965308</v>
+        <v>-3.855760773067207</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.984479520554486</v>
+        <v>2.027280806465216</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>1.237320968920142</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.264793976130028</v>
+        <v>4.312334121357932</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.538498602913602</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.920610189221301</v>
+        <v>-3.896915892635428</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.969898102911334</v>
+        <v>2.012699388822063</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>1.196165849351921</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.241981534573231</v>
+        <v>4.289521679801135</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.551349628791485</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-3.828867329943898</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.009968553865829</v>
+        <v>2.052769839776557</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.264214412043451</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.295661698066031</v>
+        <v>4.343201843293936</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.571552298965079</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.060467723113399</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.937531066771622</v>
+        <v>1.980332352682351</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.264214412043451</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.315864368239625</v>
+        <v>4.36340451346753</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.555158535031961</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.110519268642619</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.901116684626816</v>
+        <v>1.943917970537545</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.264214412043451</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.299470604306507</v>
+        <v>4.347010749534411</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.515410448625428</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.285626101219064</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.791325865189705</v>
+        <v>1.834127151100434</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.264214412043451</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.259722517899974</v>
+        <v>4.307262663127879</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.522433067622368</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.089525947788541</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.876788545558854</v>
+        <v>1.919589831469583</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.460314565473974</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.384405228955227</v>
+        <v>4.431945374183132</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.621604067195272</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-3.936500555675257</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.037169701977072</v>
+        <v>2.079970987887801</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.613339957587258</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.575391463796103</v>
+        <v>4.622931609024007</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.809070292103565</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-3.964807869548527</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.213313001336057</v>
+        <v>2.256114287246786</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.613339957587258</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.762857688704395</v>
+        <v>4.810397833932299</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.778473243457647</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.131401094662049</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.116078662644731</v>
+        <v>2.15887994855546</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.446746732473735</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.632304704990364</v>
+        <v>4.679844850218268</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.782149646119365</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.108365301300483</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.128969382651074</v>
+        <v>2.171770668561804</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.446746732473735</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.635981107652082</v>
+        <v>4.683521252879986</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.77976770124286</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.079119320844787</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.138285829956848</v>
+        <v>2.181087115867578</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.446746732473735</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.633599162775577</v>
+        <v>4.681139308003481</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.777060940400495</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.186044868722638</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.092808849963343</v>
+        <v>2.135610135874072</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.339821184595884</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.566737073206502</v>
+        <v>4.614277218434406</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.77848974254373</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.331063427229886</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.036230228703678</v>
+        <v>2.079031514614407</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.194802626088636</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.481154740245387</v>
+        <v>4.528694885473291</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.878420981801483</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.449405193014604</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.088824761647544</v>
+        <v>2.131626047558273</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.205488664651526</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.587497602640874</v>
+        <v>4.635037747868778</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.876206678927422</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.500815615335312</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.066046289845199</v>
+        <v>2.108847575755929</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.205488664651526</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.585283299766813</v>
+        <v>4.632823444994717</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.876109807001711</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.580235066543064</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.034181637436388</v>
+        <v>2.076982923347117</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.205488664651526</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.585186427841102</v>
+        <v>4.632726573069006</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.876103700559754</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.675698064460281</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.995990331827544</v>
+        <v>2.038791617738273</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.205488664651526</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.585180321399145</v>
+        <v>4.632720466627049</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.874200097122364</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.611322153609566</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.019837092730441</v>
+        <v>2.06263837864117</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.269864575502241</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.621902264472185</v>
+        <v>4.669442409700089</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.879933914870091</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.66669131574176</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.00342324562529</v>
+        <v>2.046224531536019</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.269864575502241</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.627636082219912</v>
+        <v>4.675176227447816</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.879472278213024</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.708604079325242</v>
+        <v>-4.684909782739369</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.995674222169179</v>
+        <v>2.038475508079908</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.221063841660525</v>
+        <v>1.244758138246399</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.612110583209339</v>
+        <v>4.659650728437243</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.899346671063342</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.620397245177664</v>
+        <v>-4.596702948591791</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.050831348678529</v>
+        <v>2.093632634589258</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.221063841660525</v>
+        <v>1.244758138246399</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.631984976059657</v>
+        <v>4.679525121287561</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.88304737158807</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.514362249972354</v>
+        <v>-4.490667953386481</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.07694604728538</v>
+        <v>2.119747333196109</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.221063841660525</v>
+        <v>1.244758138246399</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.615685676584385</v>
+        <v>4.663225821812289</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.885478321052116</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.331150586839259</v>
+        <v>-4.307456290253386</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.152661662002664</v>
+        <v>2.195462947913393</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.221063841660525</v>
+        <v>1.244758138246399</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.618116626048431</v>
+        <v>4.665656771276335</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.851269506900006</v>
+        <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.259429139825408</v>
+        <v>-4.235734843239535</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.147141426656095</v>
+        <v>2.189942712566823</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.292785288674375</v>
+        <v>1.316479585260249</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.626940680104632</v>
+        <v>4.674480825332535</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.798185252821177</v>
+        <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.237056114217702</v>
+        <v>-4.213361817631829</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.103006382820348</v>
+        <v>2.145807668731077</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.304041039787277</v>
+        <v>1.327735336373151</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.580609876693543</v>
+        <v>4.628150021921448</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.983383457706533</v>
+        <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.270072410128447</v>
+        <v>-4.246378113542574</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.274998069341406</v>
+        <v>2.317799355252134</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.234603663120525</v>
+        <v>1.258297959706399</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.724145655578848</v>
+        <v>4.771685800806752</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.975304683534782</v>
+        <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.258544774478838</v>
+        <v>-4.234850477892965</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.271530349429499</v>
+        <v>2.314331635340227</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.293604321321888</v>
+        <v>1.317298617907762</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.751467276327915</v>
+        <v>4.799007421555818</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.978972796056571</v>
+        <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.355886275821207</v>
+        <v>-4.332191979235334</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.23626186141434</v>
+        <v>2.279063147325068</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.249184139156399</v>
+        <v>1.272878435742273</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.72848327955041</v>
+        <v>4.776023424778314</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.980223878249409</v>
+        <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.441742305161173</v>
+        <v>-4.4180480085753</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.203170531871192</v>
+        <v>2.245971817781919</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.206808069930264</v>
+        <v>1.230502366516138</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.704308720207568</v>
+        <v>4.751848865435471</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.962643080069911</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.450579102577293</v>
+        <v>-4.42688480599142</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.182055014725246</v>
+        <v>2.224856300635974</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.199365897288914</v>
+        <v>1.223060193874788</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.682262618443259</v>
+        <v>4.729802763671162</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.97280759111496</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.541961665142751</v>
+        <v>-4.518267368556878</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.155666500744112</v>
+        <v>2.19846778665484</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.162801012569569</v>
+        <v>1.186495309155443</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.670488198656702</v>
+        <v>4.718028343884605</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.074935848939228</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.530254947155745</v>
+        <v>-4.506560650569872</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.262477445763182</v>
+        <v>2.305278731673909</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.174507730556575</v>
+        <v>1.198202027142449</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.779640487273173</v>
+        <v>4.827180632501076</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.077968187670633</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.601167020898023</v>
+        <v>-4.57747272431215</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.237144954997676</v>
+        <v>2.279946240908403</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.174507730556575</v>
+        <v>1.198202027142449</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.782672826004578</v>
+        <v>4.830212971232481</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.290873020948691</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.611483119064375</v>
+        <v>-4.587788822478502</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.445923349009193</v>
+        <v>2.488724634919921</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.174507730556575</v>
+        <v>1.198202027142449</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.995577659282636</v>
+        <v>5.043117804510539</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.290051687860781</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.611389151047002</v>
+        <v>-4.587694854461129</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.445139603128232</v>
+        <v>2.487940889038959</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.174877591903893</v>
+        <v>1.198571888489767</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.994978243003117</v>
+        <v>5.04251838823102</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.284283673805135</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.759755378703147</v>
+        <v>-4.736061082117274</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.380025098010128</v>
+        <v>2.422826383920855</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.174877591903893</v>
+        <v>1.198571888489767</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.989210228947471</v>
+        <v>5.036750374175373</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.284283673805135</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.758806955585109</v>
+        <v>-4.735112658999236</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.380404467257343</v>
+        <v>2.42320575316807</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.174877591903893</v>
+        <v>1.198571888489767</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.989210228947471</v>
+        <v>5.036750374175373</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.297011281786227</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.85907677354413</v>
+        <v>-4.835382476958257</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.353024148054827</v>
+        <v>2.395825433965554</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.174877591903893</v>
+        <v>1.198571888489767</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.001937836928563</v>
+        <v>5.049477982156466</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.298957280210614</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.853084526755318</v>
+        <v>-4.829390230169445</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.357367045194739</v>
+        <v>2.400168331105466</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.174877591903893</v>
+        <v>1.198571888489767</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.00388383535295</v>
+        <v>5.051423980580854</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.292611416228383</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.764526565624551</v>
+        <v>-4.740832269038678</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.386444365664815</v>
+        <v>2.429245651575542</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.174877591903893</v>
+        <v>1.198571888489767</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.997537971370719</v>
+        <v>5.045078116598622</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.291920093667379</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.746767488121477</v>
+        <v>-4.723073191535604</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.39285667410504</v>
+        <v>2.435657960015767</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.174877591903893</v>
+        <v>1.198571888489767</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.996846648809715</v>
+        <v>5.044386794037617</v>
       </c>
     </row>
     <row r="2086">
@@ -49526,19 +49526,19 @@
         <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.304702279575966</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.647137337072409</v>
+        <v>-4.623443040486536</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.445490920433254</v>
+        <v>2.488292206343981</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.274507742952961</v>
+        <v>1.298202039538835</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.069406925347742</v>
+        <v>5.116947070575645</v>
       </c>
     </row>
     <row r="2087">
@@ -49549,19 +49549,19 @@
         <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.493856545074692</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.69653684576142</v>
+        <v>-4.672842549175547</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.614885382456376</v>
+        <v>2.657686668367103</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.284766576384706</v>
+        <v>1.30846087297058</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.264716490905515</v>
+        <v>5.312256636133418</v>
       </c>
     </row>
     <row r="2088">
@@ -49572,19 +49572,19 @@
         <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.481045218177554</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.489852372119044</v>
+        <v>-4.466158075533171</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.684747845016188</v>
+        <v>2.727549130926916</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.491451050027081</v>
+        <v>1.515145346612955</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.375915848193803</v>
+        <v>5.423455993421705</v>
       </c>
     </row>
     <row r="2089">
@@ -49595,19 +49595,19 @@
         <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.483046731831659</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.52400926711657</v>
+        <v>-4.500314970530697</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.673086600671283</v>
+        <v>2.71588788658201</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.407867280486269</v>
+        <v>1.431561577072143</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.32776710012342</v>
+        <v>5.375307245351324</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.836543845821327</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.431419788055114</v>
+        <v>-4.407725491469241</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.063619506285533</v>
+        <v>3.106420792196261</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.407867280486269</v>
+        <v>1.431561577072143</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.681264214113088</v>
+        <v>5.728804359340991</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.84110695738843</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.491308415878664</v>
+        <v>-4.467614119292791</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.044227166723216</v>
+        <v>3.087028452633944</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.393745365798804</v>
+        <v>1.417439662384678</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.677354176867713</v>
+        <v>5.724894322095615</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.890936898711957</v>
+        <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.439092106082322</v>
+        <v>-4.415397809496449</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.11494363196528</v>
+        <v>3.157744917876008</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.393745365798804</v>
+        <v>1.417439662384678</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.72718411819124</v>
+        <v>5.774724263419142</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.899750868921968</v>
+        <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.407194588997077</v>
+        <v>-4.383500292411203</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.13651660900939</v>
+        <v>3.179317894920117</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.42564288288405</v>
+        <v>1.449337179469924</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.755136598652398</v>
+        <v>5.802676743880301</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.895388452961165</v>
+        <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.421949913197217</v>
+        <v>-4.398255616611344</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.12625206336853</v>
+        <v>3.169053349279258</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.42564288288405</v>
+        <v>1.449337179469924</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.750774182691595</v>
+        <v>5.798314327919497</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.886312956377445</v>
+        <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.372485289827305</v>
+        <v>-4.348790993241432</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.136962416132775</v>
+        <v>3.179763702043502</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.475107506253962</v>
+        <v>1.498801802839836</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.771377460129822</v>
+        <v>5.818917605357725</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.88272062409238</v>
+        <v>4.916044191368758</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.20937729767369</v>
+        <v>-4.185683001087817</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.198613280709155</v>
+        <v>3.241414566619883</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.638215498407577</v>
+        <v>1.661909794993451</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.865649923136925</v>
+        <v>5.913190068364829</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.891767660783508</v>
+        <v>4.925091228059886</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.076569672176523</v>
+        <v>-4.05287537559065</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.26078336759915</v>
+        <v>3.303584653509878</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.638215498407577</v>
+        <v>1.661909794993451</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.874696959828054</v>
+        <v>5.922237105055956</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.840844385492103</v>
+        <v>3.838889685205832</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.892625125769629</v>
+        <v>4.925948693046007</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.139277588651082</v>
+        <v>-4.115583292065208</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.236557665995448</v>
+        <v>3.279358951906176</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.575507581933019</v>
+        <v>1.599201878518893</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.837929674929441</v>
+        <v>5.885469820157343</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240926.xlsx
+++ b/tame_output/ON/bt/strategyON_20240926.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>55.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>119.1%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>194.4%</t>
+          <t>181.1%</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.4%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-576.7%</t>
+          <t>-575.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-56.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-319.3%</t>
+          <t>-320.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.31188830135569</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296836</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537428</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006536</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232414</v>
+        <v>3.747702660232417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.76631707943623</v>
+        <v>3.766317079436232</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.83937444738873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291811</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942101</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.685091185837372</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
@@ -46286,10 +46286,10 @@
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.668860948805666</v>
+        <v>-3.657328288447082</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.123484261639422</v>
+        <v>1.128097325782855</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5836513315119443</v>
@@ -46309,10 +46309,10 @@
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.576050467354806</v>
+        <v>-3.564517806996223</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.089881146111131</v>
+        <v>1.094494210254565</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6764618129628036</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.620439936684234</v>
+        <v>-3.608907276325651</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.073998834303961</v>
+        <v>1.078611898447394</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6320723436333759</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.599936242798737</v>
+        <v>-3.588403582440153</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.077276020369883</v>
+        <v>1.081889084513316</v>
       </c>
       <c r="F1948" t="n">
         <v>0.6525760375188733</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.639860337381308</v>
+        <v>-3.628327677022726</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.066797678367521</v>
+        <v>1.071410742510954</v>
       </c>
       <c r="F1949" t="n">
         <v>0.6525760375188733</v>
@@ -46401,10 +46401,10 @@
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.667640735282661</v>
+        <v>-3.656108074924079</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.067182720975519</v>
+        <v>1.071795785118952</v>
       </c>
       <c r="F1950" t="n">
         <v>0.6247956396175203</v>
@@ -46424,10 +46424,10 @@
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.7860214080128</v>
+        <v>-3.774488747654217</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8581861718841171</v>
+        <v>0.8627992360275503</v>
       </c>
       <c r="F1951" t="n">
         <v>0.5575777874665441</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.894635486456131</v>
+        <v>-3.883102826097548</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9348902012259903</v>
+        <v>0.9395032653694235</v>
       </c>
       <c r="F1952" t="n">
         <v>0.5575777874665441</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.859226448207988</v>
+        <v>-3.847693787849405</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9635668426275705</v>
+        <v>0.9681799067710035</v>
       </c>
       <c r="F1953" t="n">
         <v>0.5575777874665441</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.867687616863449</v>
+        <v>-3.856154956504867</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9576018165077547</v>
+        <v>0.9622148806511879</v>
       </c>
       <c r="F1954" t="n">
         <v>0.549116618811083</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532483</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.690571286828283</v>
+        <v>-3.6790386264697</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025177377367124</v>
+        <v>1.029790441510557</v>
       </c>
       <c r="F1955" t="n">
         <v>0.549116618811083</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413284487939</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.735663531661829</v>
+        <v>-3.724130871303246</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.007823871195618</v>
+        <v>1.012436935339051</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4872205756416932</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.556288110423061</v>
+        <v>-3.544755450064478</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.07336101499754</v>
+        <v>1.077974079140973</v>
       </c>
       <c r="F1957" t="n">
         <v>0.6439973338124119</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982224</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.601302323943667</v>
+        <v>-3.589769663585085</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036162784920887</v>
+        <v>1.04077584906432</v>
       </c>
       <c r="F1958" t="n">
         <v>0.6136484384978073</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.868306834216103</v>
+        <v>-3.85677417385752</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9350525431508585</v>
+        <v>0.9396656072942917</v>
       </c>
       <c r="F1959" t="n">
         <v>0.4192854004548587</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.969504615653276</v>
+        <v>-3.957971955294693</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8937773524724908</v>
+        <v>0.898390416615924</v>
       </c>
       <c r="F1960" t="n">
         <v>0.3508765869095395</v>
@@ -46654,10 +46654,10 @@
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.962993649038963</v>
+        <v>-3.95146098868038</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8939817006725326</v>
+        <v>0.8985947648159658</v>
       </c>
       <c r="F1961" t="n">
         <v>0.3508765869095395</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.943955521331666</v>
+        <v>-3.932422860973083</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8981216709636966</v>
+        <v>0.9027347351071295</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2926929755783449</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.996471323606486</v>
+        <v>-3.984938663247903</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9964097516879589</v>
+        <v>1.001022815831392</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2926929755783449</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.999879635041065</v>
+        <v>-3.988346974682483</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9958797561002606</v>
+        <v>1.000492820243694</v>
       </c>
       <c r="F1964" t="n">
         <v>0.3252095445877223</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.980523499147218</v>
+        <v>-3.968990838788636</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.009630740854725</v>
+        <v>1.014243804998158</v>
       </c>
       <c r="F1965" t="n">
         <v>0.3252095445877223</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.832780528912216</v>
+        <v>-3.821247868553634</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9666781502259256</v>
+        <v>0.9712912143693586</v>
       </c>
       <c r="F1966" t="n">
         <v>0.4930169018226055</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.916601750186914</v>
+        <v>-3.905069089828332</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9359432832475274</v>
+        <v>0.9405563473909604</v>
       </c>
       <c r="F1967" t="n">
         <v>0.4930169018226055</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394725</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.91044904413413</v>
+        <v>-3.898916383775547</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9390667140602995</v>
+        <v>0.9436797782037325</v>
       </c>
       <c r="F1968" t="n">
         <v>0.4991696078753898</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.927258342284631</v>
+        <v>-3.915725681926049</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9314234715402092</v>
+        <v>0.9360365356836422</v>
       </c>
       <c r="F1969" t="n">
         <v>0.4823603097248881</v>
@@ -46861,10 +46861,10 @@
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.86496034350851</v>
+        <v>-3.853427683149927</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.022678224847479</v>
+        <v>1.027291288990912</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5276545739993301</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.663170145843352</v>
+        <v>-3.651637485484769</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9056863056276689</v>
+        <v>0.9102993697711022</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7256727661684845</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.714056858529546</v>
+        <v>-3.702524198170964</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9556218528753664</v>
+        <v>0.9602349170187994</v>
       </c>
       <c r="F1972" t="n">
         <v>0.67478605348229</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.627446115879739</v>
+        <v>-3.615913455521156</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.004893886051333</v>
+        <v>1.009506950194766</v>
       </c>
       <c r="F1973" t="n">
         <v>0.7534117846874483</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.687655413885023</v>
+        <v>-3.676122753526441</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9793461476738907</v>
+        <v>0.9839592118173239</v>
       </c>
       <c r="F1974" t="n">
         <v>0.6932024866821638</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.638468765200672</v>
+        <v>-3.626936104842089</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9975124251875598</v>
+        <v>1.002125489330993</v>
       </c>
       <c r="F1975" t="n">
         <v>0.6932024866821638</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.594095633562103</v>
+        <v>-3.582562973203521</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.015124545278423</v>
+        <v>1.019737609421857</v>
       </c>
       <c r="F1976" t="n">
         <v>0.7375756183207324</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.559364312243603</v>
+        <v>-3.54783165188502</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.023410867944414</v>
+        <v>1.028023932087847</v>
       </c>
       <c r="F1977" t="n">
         <v>0.7375756183207324</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.511708581682547</v>
+        <v>-3.500175921323964</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.048854917196641</v>
+        <v>1.053467981340074</v>
       </c>
       <c r="F1978" t="n">
         <v>0.785231348881788</v>
@@ -47068,10 +47068,10 @@
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.411190423183792</v>
+        <v>-3.39965776282521</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.093954553970868</v>
+        <v>1.098567618114301</v>
       </c>
       <c r="F1979" t="n">
         <v>0.8857495073805426</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.39528509375144</v>
+        <v>-3.383752433392857</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.087071358219681</v>
+        <v>1.091684422363114</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8066368466713036</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.350446692143042</v>
+        <v>-3.338914031784459</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.109104421473669</v>
+        <v>1.113717485617102</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8111802796161731</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.36994514838505</v>
+        <v>-3.358412488026467</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.105465978607944</v>
+        <v>1.110079042751377</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7630956383362688</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.32574231129915</v>
+        <v>-3.314209650940567</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.129026715970141</v>
+        <v>1.133639780113574</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8072984754221693</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.333301977136196</v>
+        <v>-3.321769316777614</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.12441285010457</v>
+        <v>1.129025914248003</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8621018794319886</v>
@@ -47206,10 +47206,10 @@
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.175010559596924</v>
+        <v>-3.163477899238341</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.238977182303318</v>
+        <v>1.243590246446751</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8621018794319886</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.967368555962448</v>
+        <v>-2.955835895603865</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.320474688351362</v>
+        <v>1.325087752494795</v>
       </c>
       <c r="F1986" t="n">
         <v>1.069743883066465</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.91633646323992</v>
+        <v>-2.904803802881337</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.335835753678643</v>
+        <v>1.340448817822076</v>
       </c>
       <c r="F1987" t="n">
         <v>1.120775975788993</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.851112282112714</v>
+        <v>-2.839579621754131</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.37911283022223</v>
+        <v>1.383725894365664</v>
       </c>
       <c r="F1988" t="n">
         <v>1.186000156916198</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.81368526204158</v>
+        <v>-2.802152601682998</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.390044610549964</v>
+        <v>1.394657674693397</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19125169494538</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.812327277068035</v>
+        <v>-2.800794616709452</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.391844596870623</v>
+        <v>1.396457661014056</v>
       </c>
       <c r="F1990" t="n">
         <v>1.265589820483199</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.783914013968151</v>
+        <v>-2.772381353609568</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.563767673131787</v>
+        <v>1.56838073727522</v>
       </c>
       <c r="F1991" t="n">
         <v>1.20661425773677</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.709131752943139</v>
+        <v>-2.697599092584556</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.713793486759609</v>
+        <v>1.718406550903042</v>
       </c>
       <c r="F1992" t="n">
         <v>1.281396518761783</v>
@@ -47390,10 +47390,10 @@
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.683047668679331</v>
+        <v>-2.671515008320748</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.715935096478991</v>
+        <v>1.720548160622425</v>
       </c>
       <c r="F1993" t="n">
         <v>1.281396518761783</v>
@@ -47413,10 +47413,10 @@
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.59516975557021</v>
+        <v>-2.583637095211627</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.749279457306419</v>
+        <v>1.753892521449852</v>
       </c>
       <c r="F1994" t="n">
         <v>1.397322161185134</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.586277294176927</v>
+        <v>-2.574744633818344</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.770390847590524</v>
+        <v>1.775003911733957</v>
       </c>
       <c r="F1995" t="n">
         <v>1.397322161185134</v>
@@ -47459,10 +47459,10 @@
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.754753411146805</v>
+        <v>-2.743220750788222</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.694855448207157</v>
+        <v>1.69946851235059</v>
       </c>
       <c r="F1996" t="n">
         <v>1.369374325468553</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.308497218517365</v>
+        <v>-2.296964558158782</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.854627622446794</v>
+        <v>1.859240686590228</v>
       </c>
       <c r="F1997" t="n">
         <v>1.27465565579892</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.285776114834213</v>
+        <v>-2.27424345447563</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.85438008641696</v>
+        <v>1.858993150560393</v>
       </c>
       <c r="F1998" t="n">
         <v>1.27465565579892</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.414977928128255</v>
+        <v>-2.403445267769672</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.961605486950512</v>
+        <v>1.966218551093945</v>
       </c>
       <c r="F1999" t="n">
         <v>1.145453842504878</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.440852326602281</v>
+        <v>-2.429319666243698</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.988333550054548</v>
+        <v>1.992946614197981</v>
       </c>
       <c r="F2000" t="n">
         <v>1.190365451216619</v>
@@ -47574,10 +47574,10 @@
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.433797636387107</v>
+        <v>-2.422264976028524</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.987830782130163</v>
+        <v>1.992443846273596</v>
       </c>
       <c r="F2001" t="n">
         <v>1.197420141431793</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.406846412060619</v>
+        <v>-2.395313751702036</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.008617425505499</v>
+        <v>2.013230489648933</v>
       </c>
       <c r="F2002" t="n">
         <v>1.212300487459512</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.428390639891406</v>
+        <v>-2.416857979532824</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.184102866518145</v>
+        <v>2.188715930661578</v>
       </c>
       <c r="F2003" t="n">
         <v>1.212300487459512</v>
@@ -47643,10 +47643,10 @@
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.450798757696278</v>
+        <v>-2.439266097337696</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.167256314299189</v>
+        <v>2.171869378442622</v>
       </c>
       <c r="F2004" t="n">
         <v>1.212300487459512</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.719118627155033</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.479022993273879</v>
+        <v>-2.467490332915296</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.158020619617786</v>
+        <v>2.162633683761219</v>
       </c>
       <c r="F2005" t="n">
         <v>1.230277239910821</v>
@@ -47683,16 +47683,16 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.488463919162409</v>
+        <v>-2.476931258803826</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.210497966984221</v>
+        <v>2.215111031127655</v>
       </c>
       <c r="F2006" t="n">
         <v>1.352704357454212</v>
@@ -47706,16 +47706,16 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.577340550330883</v>
+        <v>-2.5658078899723</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.177838409062133</v>
+        <v>2.182451473205566</v>
       </c>
       <c r="F2007" t="n">
         <v>1.263827726285738</v>
@@ -47729,16 +47729,16 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347705</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.653670527931788</v>
+        <v>-2.642137867573206</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.145418230915546</v>
+        <v>2.150031295058978</v>
       </c>
       <c r="F2008" t="n">
         <v>1.263827726285738</v>
@@ -47752,16 +47752,16 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887751</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.808627313331918</v>
+        <v>-2.797094652973335</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.078255746358356</v>
+        <v>2.082868810501789</v>
       </c>
       <c r="F2009" t="n">
         <v>1.108870940885609</v>
@@ -47775,16 +47775,16 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.970195738859173</v>
+        <v>-2.95866307850059</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.012062386357607</v>
+        <v>2.016675450501039</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9820880170877296</v>
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.078496400729292</v>
+        <v>-3.06696374037071</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.981815528475477</v>
+        <v>1.98642859261891</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9820880170877296</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.749882691378386</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.096300372450036</v>
+        <v>-3.084767712091454</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.966699136570119</v>
+        <v>1.971312200713553</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9115533941825285</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.124201159559509</v>
+        <v>-3.112668499200927</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.954062862853332</v>
+        <v>1.958675926996765</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8769564700395936</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.246727262262403</v>
+        <v>-3.23519460190382</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.901816865749373</v>
+        <v>1.906429929892806</v>
       </c>
       <c r="F2014" t="n">
         <v>0.7544303673366998</v>
@@ -47896,10 +47896,10 @@
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.477241758447992</v>
+        <v>-3.465709098089409</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.876317026865642</v>
+        <v>1.880930091009075</v>
       </c>
       <c r="F2015" t="n">
         <v>0.523915871151111</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.825986843672435</v>
+        <v>-3.814454183313853</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.877130711777711</v>
+        <v>1.881743775921144</v>
       </c>
       <c r="F2016" t="n">
         <v>0.4151679172322132</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237092</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.979973261448576</v>
+        <v>-3.968440601089993</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.884516413812895</v>
+        <v>1.889129477956328</v>
       </c>
       <c r="F2017" t="n">
         <v>0.4151679172322132</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.184572696311585</v>
+        <v>-4.173040035953002</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.788727841987812</v>
+        <v>1.793340906131246</v>
       </c>
       <c r="F2018" t="n">
         <v>0.4151679172322132</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.437047850319309</v>
+        <v>-4.425515189960726</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.699608269440137</v>
+        <v>1.70422133358357</v>
       </c>
       <c r="F2019" t="n">
         <v>0.4151679172322132</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.729943606798721</v>
+        <v>-4.718410946440138</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.583660501367316</v>
+        <v>1.588273565510748</v>
       </c>
       <c r="F2020" t="n">
         <v>0.4151679172322132</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.916607734933529</v>
+        <v>-4.905075074574946</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.513116592340714</v>
+        <v>1.517729656484147</v>
       </c>
       <c r="F2021" t="n">
         <v>0.3884289464076534</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.652149152916201</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.062628421847491</v>
+        <v>-5.051095761488908</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.449786170311318</v>
+        <v>1.454399234454751</v>
       </c>
       <c r="F2022" t="n">
         <v>0.3793458546137964</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.154342430957076</v>
+        <v>-5.142809770598493</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.575304623366529</v>
+        <v>1.579917687509961</v>
       </c>
       <c r="F2023" t="n">
         <v>0.3793458546137964</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.185994090017045</v>
+        <v>-5.174461429658463</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.557490597706355</v>
+        <v>1.562103661849788</v>
       </c>
       <c r="F2024" t="n">
         <v>0.3741773973693562</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.255060144589982</v>
+        <v>-5.243527484231399</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.540093593445671</v>
+        <v>1.544706657589105</v>
       </c>
       <c r="F2025" t="n">
         <v>0.3118065198757461</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.783632867332693</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.35703626683839</v>
+        <v>-5.345503606479807</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.508228783002211</v>
+        <v>1.512841847145644</v>
       </c>
       <c r="F2026" t="n">
         <v>0.2098303976273386</v>
@@ -48166,16 +48166,16 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.79829678423181</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.247029983361168</v>
+        <v>-5.235497323002585</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.544384183637275</v>
+        <v>1.548997247780708</v>
       </c>
       <c r="F2027" t="n">
         <v>0.2330349695446138</v>
@@ -48189,16 +48189,16 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.785563924818516</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.103970407620242</v>
+        <v>-5.092437747261659</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.605858024655619</v>
+        <v>1.610471088799053</v>
       </c>
       <c r="F2028" t="n">
         <v>0.2410483961345931</v>
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.58222756271021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.802523682148404</v>
+        <v>-4.790991021789822</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.73369759772689</v>
+        <v>1.665474729680533</v>
       </c>
       <c r="F2029" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.980560567863859</v>
+        <v>3.907724635674068</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.583198740462921</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.827113926383588</v>
+        <v>-4.815581266025005</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.724832677785528</v>
+        <v>1.65660980973917</v>
       </c>
       <c r="F2030" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.98153174561657</v>
+        <v>3.908695813426779</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.584041644842676</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.776075550377068</v>
+        <v>-4.764542890018485</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.746090932567891</v>
+        <v>1.677868064521534</v>
       </c>
       <c r="F2031" t="n">
         <v>0.5424951216064303</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.982374649996325</v>
+        <v>3.909538717806535</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.603079743716822</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.734936255510437</v>
+        <v>-4.723403595151854</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.781584749388689</v>
+        <v>1.713361881342332</v>
       </c>
       <c r="F2032" t="n">
         <v>0.5836344164730611</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.026096325790449</v>
+        <v>3.953260393600659</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.419263739840756</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.638301343491797</v>
+        <v>-4.626768683133214</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.63642271032008</v>
+        <v>1.568199842273722</v>
       </c>
       <c r="F2033" t="n">
         <v>0.6802693284917011</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.900261269125567</v>
+        <v>3.827425336935777</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.42276578391472</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.569263332543329</v>
+        <v>-4.557730672184746</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.667539958773431</v>
+        <v>1.599317090727073</v>
       </c>
       <c r="F2034" t="n">
         <v>0.7493073394401691</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.945186119768612</v>
+        <v>3.872350187578822</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.407192602990802</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.404766998352367</v>
+        <v>-4.393234337993785</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.717765311525898</v>
+        <v>1.64954244347954</v>
       </c>
       <c r="F2035" t="n">
         <v>0.913803673631131</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.028310739359272</v>
+        <v>3.955474807169481</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.406380313427232</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.327668396810495</v>
+        <v>-4.316135736451912</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.747792462579077</v>
+        <v>1.679569594532719</v>
       </c>
       <c r="F2036" t="n">
         <v>0.913803673631131</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.027498449795702</v>
+        <v>3.954662517605911</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.416249092552305</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.338053591700384</v>
+        <v>-4.326520931341801</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.753507163748194</v>
+        <v>1.685284295701836</v>
       </c>
       <c r="F2037" t="n">
         <v>0.9034184787412417</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.03113611198684</v>
+        <v>3.95830017979705</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.48708609832873</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.356641750422609</v>
+        <v>-4.345109090064026</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.816908906035729</v>
+        <v>1.748686037989371</v>
       </c>
       <c r="F2038" t="n">
         <v>0.8848303200190164</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.09082022252993</v>
+        <v>4.01798429034014</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.483955109147028</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.356940297118645</v>
+        <v>-4.345407636760062</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.813658498175613</v>
+        <v>1.745435630129255</v>
       </c>
       <c r="F2039" t="n">
         <v>0.8845317733229805</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.087510105330607</v>
+        <v>4.014674173140817</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.48848600408642</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.256117163428217</v>
+        <v>-4.244584503069635</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.858518646591175</v>
+        <v>1.790295778544818</v>
       </c>
       <c r="F2040" t="n">
         <v>0.8969959888073343</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.099519529560611</v>
+        <v>4.026683597370821</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.488615257564963</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.06533580267581</v>
+        <v>-4.053803142317227</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.934960444370682</v>
+        <v>1.866737576324324</v>
       </c>
       <c r="F2041" t="n">
         <v>1.087777349559742</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.214117599490599</v>
+        <v>4.141281667300808</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.468452103302559</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.958372444826388</v>
+        <v>-3.946839784467805</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.957582633248047</v>
+        <v>1.889359765201689</v>
       </c>
       <c r="F2042" t="n">
         <v>1.146241957519543</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.229033210004077</v>
+        <v>4.156197277814286</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.503419039914618</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.903041856924626</v>
+        <v>-3.891509196566043</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.01468180502081</v>
+        <v>1.946458936974452</v>
       </c>
       <c r="F2043" t="n">
         <v>1.201572545421305</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.297198499357192</v>
+        <v>4.224362567167401</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.497105607816056</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.890987730011663</v>
+        <v>-3.87945506965308</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.013190023687433</v>
+        <v>1.944967155641075</v>
       </c>
       <c r="F2044" t="n">
         <v>1.213626672334268</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.225281611216617</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.498986238000191</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.932142849579884</v>
+        <v>-3.920610189221301</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.99860860604428</v>
+        <v>1.930385737997923</v>
       </c>
       <c r="F2045" t="n">
         <v>1.172471552766047</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.20246916965982</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.511837263878074</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.864094286888354</v>
+        <v>-3.852561626529771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.038679056998775</v>
+        <v>1.970456188952418</v>
       </c>
       <c r="F2046" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.256149333152621</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013427</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.532039934051668</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.095694680057855</v>
+        <v>-4.084162019699273</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.966241569904569</v>
+        <v>1.898018701858211</v>
       </c>
       <c r="F2047" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.276352003326215</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498964</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.51564617011855</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.145746225587075</v>
+        <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.929827187759763</v>
+        <v>1.861604319713405</v>
       </c>
       <c r="F2048" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.259958239393097</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.475898083712017</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.32085305816352</v>
+        <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.820036368322651</v>
+        <v>1.751813500276294</v>
       </c>
       <c r="F2049" t="n">
         <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.220210152986564</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.482920702708957</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.124752904732997</v>
+        <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.905499048691801</v>
+        <v>1.837276180645443</v>
       </c>
       <c r="F2050" t="n">
         <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.344892864041817</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.582091702281861</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.971727512619713</v>
+        <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.065880205110019</v>
+        <v>1.997657337063661</v>
       </c>
       <c r="F2051" t="n">
         <v>1.589645661001384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.535879098882692</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.769557927190154</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.000034826492983</v>
+        <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.242023504469003</v>
+        <v>2.173800636422646</v>
       </c>
       <c r="F2052" t="n">
         <v>1.589645661001384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.723345323790984</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.738960878544237</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.166628051606505</v>
+        <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.144789165777677</v>
+        <v>2.07656629773132</v>
       </c>
       <c r="F2053" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.592792340076953</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.742637281205954</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.143592258244939</v>
+        <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.157679885784021</v>
+        <v>2.089457017737664</v>
       </c>
       <c r="F2054" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.596468742738671</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.74025533632945</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.114346277789243</v>
+        <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.166996333089795</v>
+        <v>2.098773465043438</v>
       </c>
       <c r="F2055" t="n">
         <v>1.423052435887861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.594086797862166</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.737548575487085</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.221271825667094</v>
+        <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.12151935309629</v>
+        <v>2.053296485049932</v>
       </c>
       <c r="F2056" t="n">
         <v>1.31612688801001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.527224708293091</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.738977377630319</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.366290384174342</v>
+        <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.064940731836625</v>
+        <v>1.996717863790267</v>
       </c>
       <c r="F2057" t="n">
         <v>1.171108329502762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.441642375331976</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>3.838908616888072</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.48463214995906</v>
+        <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.117535264780491</v>
+        <v>2.049312396734133</v>
       </c>
       <c r="F2058" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.547985237727463</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>3.836694314014011</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.536042572279768</v>
+        <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.094756792978147</v>
+        <v>2.026533924931789</v>
       </c>
       <c r="F2059" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.545770934853402</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.704757949437331</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>3.8365974420883</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.615462023487519</v>
+        <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.062892140569335</v>
+        <v>1.994669272522978</v>
       </c>
       <c r="F2060" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.545674062927691</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>3.836591335646343</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.710925021404737</v>
+        <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.024700834960491</v>
+        <v>1.956477966914133</v>
       </c>
       <c r="F2061" t="n">
         <v>1.181794368065652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.545667956485734</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>3.834687732208954</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.646549110554022</v>
+        <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.048547595863387</v>
+        <v>1.98032472781703</v>
       </c>
       <c r="F2062" t="n">
         <v>1.246170278916367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.582389899558774</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353537</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>3.84042154995668</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.701918272686216</v>
+        <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.032133748758237</v>
+        <v>1.963910880711879</v>
       </c>
       <c r="F2063" t="n">
         <v>1.246170278916367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.588123717306501</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.73682287011328</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>3.839959913299613</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.720136739683825</v>
+        <v>-4.708604079325242</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.024384725302125</v>
+        <v>1.956161857255768</v>
       </c>
       <c r="F2064" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645434150485719</v>
+        <v>4.572598218295928</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113689</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>3.859834306149931</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.631929905536246</v>
+        <v>-4.620397245177664</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.079541851811475</v>
+        <v>2.011318983765118</v>
       </c>
       <c r="F2065" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665308543336037</v>
+        <v>4.592472611146246</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016435</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>3.843535006674659</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.525894910330937</v>
+        <v>-4.514362249972354</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.105656550418327</v>
+        <v>2.03743368237197</v>
       </c>
       <c r="F2066" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.649009243860765</v>
+        <v>4.576173311670974</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>3.845965956138705</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.342683247197842</v>
+        <v>-4.331150586839259</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.181372165135611</v>
+        <v>2.113149297089254</v>
       </c>
       <c r="F2067" t="n">
         <v>1.221063841660525</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.65144019332481</v>
+        <v>4.578604261135021</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863547</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.884593074176385</v>
+        <v>3.811757141986595</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.270961800183991</v>
+        <v>-4.259429139825408</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.175851929789041</v>
+        <v>2.107629061742684</v>
       </c>
       <c r="F2068" t="n">
         <v>1.292785288674375</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.660264247381011</v>
+        <v>4.587428315191221</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.831508820097557</v>
+        <v>3.758672887907767</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.248588774576285</v>
+        <v>-4.237056114217702</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.131716885953295</v>
+        <v>2.063494017906938</v>
       </c>
       <c r="F2069" t="n">
         <v>1.304041039787277</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.613933443969923</v>
+        <v>4.541097511780133</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.016707024982912</v>
+        <v>3.943871092793122</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.281605070487029</v>
+        <v>-4.270072410128447</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.303708572474352</v>
+        <v>2.235485704427996</v>
       </c>
       <c r="F2070" t="n">
         <v>1.234603663120525</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.757469222855227</v>
+        <v>4.684633290665437</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883677</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.008628250811161</v>
+        <v>3.935792318621371</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.270077434837421</v>
+        <v>-4.258544774478838</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.300240852562445</v>
+        <v>2.232017984516088</v>
       </c>
       <c r="F2071" t="n">
         <v>1.293604321321888</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.784790843604294</v>
+        <v>4.711954911414504</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236298</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>3.93946043114316</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.367418936179789</v>
+        <v>-4.355886275821207</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.264972364547286</v>
+        <v>2.196749496500929</v>
       </c>
       <c r="F2072" t="n">
         <v>1.249184139156399</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.761806846826789</v>
+        <v>4.688970914636999</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427685</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>3.940711513335998</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.453274965519756</v>
+        <v>-4.441742305161173</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.231881035004137</v>
+        <v>2.163658166957781</v>
       </c>
       <c r="F2073" t="n">
         <v>1.206808069930264</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.737632287483946</v>
+        <v>4.664796355294157</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610377</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>3.9231307151565</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.462111762935876</v>
+        <v>-4.450579102577293</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.210765517858191</v>
+        <v>2.142542649811835</v>
       </c>
       <c r="F2074" t="n">
         <v>1.199365897288914</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.715586185719638</v>
+        <v>4.642750253529848</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667455</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>3.933295226201549</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.553494325501334</v>
+        <v>-4.541961665142751</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.184377003877057</v>
+        <v>2.116154135830701</v>
       </c>
       <c r="F2075" t="n">
         <v>1.162801012569569</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.70381176593308</v>
+        <v>4.630975833743291</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889192</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.035423484025817</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.541787607514328</v>
+        <v>-4.530254947155745</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.291187948896127</v>
+        <v>2.222965080849771</v>
       </c>
       <c r="F2076" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.812964054549552</v>
+        <v>4.740128122359762</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409568</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.038455822757221</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.612699681256606</v>
+        <v>-4.601167020898023</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.265855458130621</v>
+        <v>2.197632590084264</v>
       </c>
       <c r="F2077" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.815996393280956</v>
+        <v>4.743160461091167</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.251360656035279</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.623015779422958</v>
+        <v>-4.611483119064375</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.474633852142138</v>
+        <v>2.406410984095781</v>
       </c>
       <c r="F2078" t="n">
         <v>1.174507730556575</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.028901226559015</v>
+        <v>4.956065294369225</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762288</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.250539322947369</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.622921811405585</v>
+        <v>-4.611389151047002</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.473850106261177</v>
+        <v>2.40562723821482</v>
       </c>
       <c r="F2079" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.028301810279495</v>
+        <v>4.955465878089705</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988019</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.244771308891723</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.77128803906173</v>
+        <v>-4.759755378703147</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.408735601143073</v>
+        <v>2.340512733096716</v>
       </c>
       <c r="F2080" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.022533796223849</v>
+        <v>4.949697864034059</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740917</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.244771308891723</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.770339615943691</v>
+        <v>-4.758806955585109</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.409114970390288</v>
+        <v>2.340892102343932</v>
       </c>
       <c r="F2081" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.022533796223849</v>
+        <v>4.949697864034059</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663621</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.257498916872815</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.870609433902713</v>
+        <v>-4.85907677354413</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.381734651187772</v>
+        <v>2.313511783141415</v>
       </c>
       <c r="F2082" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.035261404204941</v>
+        <v>4.962425472015151</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.259444915297203</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.864617187113901</v>
+        <v>-4.853084526755318</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.386077548327684</v>
+        <v>2.317854680281327</v>
       </c>
       <c r="F2083" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.037207402629329</v>
+        <v>4.964371470439539</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.253099051314972</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.776059225983134</v>
+        <v>-4.764526565624551</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.41515486879776</v>
+        <v>2.346932000751403</v>
       </c>
       <c r="F2084" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.030861538647097</v>
+        <v>4.958025606457308</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383085</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.252407728753967</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.75830014848006</v>
+        <v>-4.746767488121477</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.421567177237985</v>
+        <v>2.353344309191629</v>
       </c>
       <c r="F2085" t="n">
         <v>1.174877591903893</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.030170216086093</v>
+        <v>4.957334283896303</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720993</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.265189914662554</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.658669997430992</v>
+        <v>-4.647137337072409</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.474201423566199</v>
+        <v>2.405978555519843</v>
       </c>
       <c r="F2086" t="n">
         <v>1.274507742952961</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.10273049262412</v>
+        <v>5.029894560434331</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.45434418016128</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.708069506120003</v>
+        <v>-4.69653684576142</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.643595885589321</v>
+        <v>2.575373017542964</v>
       </c>
       <c r="F2087" t="n">
         <v>1.284766576384706</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.298040058181893</v>
+        <v>5.225204125992104</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.441532853264142</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.501385032477627</v>
+        <v>-4.489852372119044</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.713458348149134</v>
+        <v>2.645235480102777</v>
       </c>
       <c r="F2088" t="n">
         <v>1.491451050027081</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.409239415470181</v>
+        <v>5.336403483280391</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.740284389162543</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.443534366918247</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.535541927475153</v>
+        <v>-4.52400926711657</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.701797103804228</v>
+        <v>2.633574235757871</v>
       </c>
       <c r="F2089" t="n">
         <v>1.407867280486269</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.361090667399798</v>
+        <v>5.288254735210009</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.797031480907915</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.442952448413696</v>
+        <v>-4.431419788055114</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.092330009418478</v>
+        <v>3.024107141372121</v>
       </c>
       <c r="F2090" t="n">
         <v>1.407867280486269</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.714587781389466</v>
+        <v>5.641751849199676</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.874430524664808</v>
+        <v>4.801594592475018</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.502841076237247</v>
+        <v>-4.491308415878664</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.072937669856161</v>
+        <v>3.004714801809804</v>
       </c>
       <c r="F2091" t="n">
         <v>1.393745365798804</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.710677744144091</v>
+        <v>5.637841811954301</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103564</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.924260465988335</v>
+        <v>4.851424533798546</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.450624766440905</v>
+        <v>-4.439092106082322</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.143654135098226</v>
+        <v>3.075431267051869</v>
       </c>
       <c r="F2092" t="n">
         <v>1.393745365798804</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.760507685467618</v>
+        <v>5.687671753277828</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047745</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.933074436198346</v>
+        <v>4.860238504008557</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.418727249355659</v>
+        <v>-4.407194588997077</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.165227112142334</v>
+        <v>3.097004244095978</v>
       </c>
       <c r="F2093" t="n">
         <v>1.42564288288405</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.788460165928776</v>
+        <v>5.715624233738986</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650754</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.928712020237543</v>
+        <v>4.855876088047753</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.4334825735558</v>
+        <v>-4.421949913197217</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.154962566501475</v>
+        <v>3.086739698455118</v>
       </c>
       <c r="F2094" t="n">
         <v>1.42564288288405</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.784097749967973</v>
+        <v>5.711261817778183</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135747</v>
+        <v>3.845044666135749</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.919636523653823</v>
+        <v>4.846800591464033</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.384017950185888</v>
+        <v>-4.372485289827305</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.16567291926572</v>
+        <v>3.097450051219363</v>
       </c>
       <c r="F2095" t="n">
         <v>1.475107506253962</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.804701027406201</v>
+        <v>5.731865095216411</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.82593179047922</v>
+        <v>3.825931790479222</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.916044191368758</v>
+        <v>4.843208259178968</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.220909958032273</v>
+        <v>-4.20937729767369</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.227323783842101</v>
+        <v>3.159100915795744</v>
       </c>
       <c r="F2096" t="n">
         <v>1.638215498407577</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.898973490413304</v>
+        <v>5.826137558223514</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844245</v>
+        <v>3.847096478844239</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.925091228059886</v>
+        <v>4.852255295870096</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.088102332535106</v>
+        <v>-4.076569672176523</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.289493870732096</v>
+        <v>3.221271002685739</v>
       </c>
       <c r="F2097" t="n">
         <v>1.638215498407577</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.908020527104432</v>
+        <v>5.835184594914642</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790955</v>
+        <v>3.832425987790948</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.925948693046007</v>
+        <v>4.853112760856217</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.150810249009664</v>
+        <v>-4.139277588651082</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.265268169128394</v>
+        <v>3.197045301082037</v>
       </c>
       <c r="F2098" t="n">
         <v>1.575507581933019</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.871253242205819</v>
+        <v>5.798417310016029</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.909322783554432</v>
+        <v>3.83251510151092</v>
       </c>
       <c r="C2099" t="n">
-        <v>5.060510859631462</v>
+        <v>4.927761295252113</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.150810249009664</v>
+        <v>-4.139277588651082</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.265268169128394</v>
+        <v>3.197045301082037</v>
       </c>
       <c r="F2099" t="n">
         <v>1.575507581933019</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.05357465661783</v>
+        <v>4.920825092238481</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240926.xlsx
+++ b/tame_output/ON/bt/strategyON_20240926.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>112.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>181.1%</t>
+          <t>175.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-76.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-607.5%</t>
+          <t>-614.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>426.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.5%</t>
+          <t>-618.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-243.4%</t>
+          <t>-246.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-66.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>74.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-235.8%</t>
+          <t>-242.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-101.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-141.9%</t>
+          <t>-146.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,52 +1461,52 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>40.8%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.31188830135569</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.3634908492490375</v>
+        <v>0.2937328739283852</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.26761008749881</v>
+        <v>3.239706897370549</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.70757260984084</v>
+        <v>1.637814634520188</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.147113738017447</v>
+        <v>4.105258952825055</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2397963636932034</v>
+        <v>0.1700383883725511</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.253073377774018</v>
+        <v>3.225170187645757</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.70757260984084</v>
+        <v>1.637814634520188</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.182054822514989</v>
+        <v>4.140200037322598</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2448339544207899</v>
+        <v>0.1750759791001376</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.253665854250391</v>
+        <v>3.22576266412213</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.763217066107158</v>
+        <v>1.693459090786505</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.214018936460117</v>
+        <v>4.172164151267726</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.01236008028726682</v>
+        <v>-0.08211805560791913</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.129534621990905</v>
+        <v>3.101631431862645</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.506023031399101</v>
+        <v>1.436265056078448</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.03844889725902</v>
+        <v>3.996594112066629</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.07812747033667888</v>
+        <v>-0.1478854456573312</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.104245275101611</v>
+        <v>3.07634208497335</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.506023031399101</v>
+        <v>1.436265056078448</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.03946650638949</v>
+        <v>3.997611721197099</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3104983844983536</v>
+        <v>-0.3802563598190059</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.001924941424697</v>
+        <v>2.974021751296436</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.506023031399101</v>
+        <v>1.436265056078448</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.030094538377246</v>
+        <v>3.988239753184855</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.3922702849261053</v>
+        <v>-0.4620282602467576</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.959298907208834</v>
+        <v>2.931395717080573</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.533058604805237</v>
+        <v>1.463300629484585</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.036398608376166</v>
+        <v>3.994543823183775</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296836</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6545912063460799</v>
+        <v>-0.7243491816667322</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.859135855474547</v>
+        <v>2.831232665346286</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.533058604805237</v>
+        <v>1.463300629484585</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.041163925209869</v>
+        <v>3.999309140017477</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201484</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6432019696912785</v>
+        <v>-0.7129599450119308</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.861516346255708</v>
+        <v>2.833613156127447</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.544447841460039</v>
+        <v>1.474689866139387</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.045822263321989</v>
+        <v>4.003967478129598</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153003</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8956798641106845</v>
+        <v>-0.9654378394313368</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.758452079993008</v>
+        <v>2.730548889864747</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.291969947040633</v>
+        <v>1.222211971719981</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.89226241817541</v>
+        <v>3.850407632983018</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.185811530716116</v>
+        <v>-1.255569506036768</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.642265629949757</v>
+        <v>2.614362439821496</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.316051741780813</v>
+        <v>1.246293766460161</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.906577711618439</v>
+        <v>3.864722926426048</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.393815589069193</v>
+        <v>-1.463573564389846</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.563956151162452</v>
+        <v>2.536052961034191</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.316051741780813</v>
+        <v>1.246293766460161</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.911469856172364</v>
+        <v>3.869615070979973</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.525751975550816</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.534166243036052</v>
+        <v>2.506263052907791</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.253873330619843</v>
+        <v>1.18411535529919</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.86924426581377</v>
+        <v>3.827389480621379</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-1.891820702695468</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.38082305148464</v>
+        <v>2.352919861356379</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.88780460347519</v>
+        <v>0.8180466281545377</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.642687328833428</v>
+        <v>3.600832543641037</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-2.100311484147153</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.317765028642734</v>
+        <v>2.289861838514474</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.6793138220235055</v>
+        <v>0.6095558467028532</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.537931149701186</v>
+        <v>3.496076364508794</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.347512668912374</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.226983305145214</v>
+        <v>2.199080115016954</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.699467175522318</v>
+        <v>0.6297092002016657</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.558121912209042</v>
+        <v>3.51626712701665</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.839897696936471</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.031135685979308</v>
+        <v>2.003232495851047</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.1373241721775689</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.263797287438316</v>
+        <v>3.221942502245924</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.02844348929949</v>
+        <v>-3.098201464620142</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.926356717718702</v>
+        <v>1.898453527590442</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.1373241721775689</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.262339826251179</v>
+        <v>3.220485041058788</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.278314169314071</v>
+        <v>-3.348072144634723</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.828177569167486</v>
+        <v>1.800274379039225</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.2433448673286845</v>
+        <v>0.1735868920080322</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.285866581604073</v>
+        <v>3.244011796411681</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.484825946201093</v>
+        <v>-3.554583921521745</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.741678917068935</v>
+        <v>1.713775726940675</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.03292488487898931</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.158065574128118</v>
+        <v>3.116210788935727</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.804170021281594</v>
+        <v>-3.873927996602247</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.615714213736994</v>
+        <v>1.587811023608733</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.03292488487898931</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.159838500828378</v>
+        <v>3.117983715635986</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.190379852557369</v>
+        <v>-4.260137827878022</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.447563168694089</v>
+        <v>1.419659978565828</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.05393984927578033</v>
+        <v>-0.1236978245964326</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>3.049852839272924</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.458931643255243</v>
+        <v>-4.528689618575895</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.32842722741703</v>
+        <v>1.300524037288769</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.1179447876207835</v>
+        <v>-0.1877027629414358</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.041589436460405</v>
+        <v>2.999734651268013</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006536</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.794594290485695</v>
+        <v>-4.864352265806348</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.192742760180814</v>
+        <v>1.164839570052553</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.1858757731096883</v>
+        <v>-0.2556337484303406</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.999411436823027</v>
+        <v>2.957556651630636</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.871038620688567</v>
+        <v>-4.940796596009219</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.168652588333907</v>
+        <v>1.140749398205646</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.1054302640160264</v>
+        <v>-0.1751882393366787</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.054166302513466</v>
+        <v>3.012311517321074</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.236166003327313</v>
+        <v>-5.305923978647966</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.02185615028424</v>
+        <v>0.9939529601559789</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4017410483150389</v>
+        <v>-0.4714990236356912</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.87563434693989</v>
+        <v>2.833779561747498</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.644754780507992</v>
+        <v>-5.714512755828645</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.857182183426727</v>
+        <v>0.8292789932984665</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.8800878008163697</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.629242624646241</v>
+        <v>2.58738783945385</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.758515192530857</v>
+        <v>-5.82827316785151</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.806863451089042</v>
+        <v>0.7789602609607811</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.8800878008163697</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.624428057117702</v>
+        <v>2.582573271925311</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.174907066817855</v>
+        <v>-6.244665042138507</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6383007519831203</v>
+        <v>0.6103975618548594</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.8800878008163697</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.622422107726579</v>
+        <v>2.580567322534188</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.536080696634842</v>
+        <v>-6.605838671955495</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5040899907250038</v>
+        <v>0.4761868005967433</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.8800878008163697</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.632680798395258</v>
+        <v>2.590826013202867</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.949097191598514</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3628861480134917</v>
+        <v>0.3349829578852308</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.8800878008163697</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.628780363540954</v>
+        <v>2.586925578348562</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-6.997300008840858</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3420099411715549</v>
+        <v>0.3141067510432944</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.8103298254957174</v>
+        <v>-0.8800878008163697</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.627185283595955</v>
+        <v>2.585330498403563</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-7.16410866881522</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2790654531110186</v>
+        <v>0.2511622629827577</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.9223711245295063</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.605594265297281</v>
+        <v>2.56373948010489</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.350828377124523</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2003512652528943</v>
+        <v>0.1724480751246333</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.9223711245295063</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.601567960762878</v>
+        <v>2.559713175570486</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.733829765867154</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.04704860843425784</v>
+        <v>0.01914541830599692</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.852613149208854</v>
+        <v>-0.9223711245295063</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.601465859441294</v>
+        <v>2.559611074248902</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.738316211068542</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.04782554632513225</v>
+        <v>0.01992235619687177</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.9268575697308949</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.601345508291891</v>
+        <v>2.559490723099499</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-8.097846533572545</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.09063627937841856</v>
+        <v>-0.118539469506679</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.8570995944102426</v>
+        <v>-0.9268575697308949</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.606695811589941</v>
+        <v>2.564841026397549</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-8.148195597026767</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1028598848029296</v>
+        <v>-0.1307630749311905</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9074486578644647</v>
+        <v>-0.977206633185117</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.584402393474585</v>
+        <v>2.542547608282194</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.245814874448163</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1388658451497196</v>
+        <v>-0.16676903527798</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.005067935285861</v>
+        <v>-1.074825910606514</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.528872577643516</v>
+        <v>2.487017792451125</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.299886373956522</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1576008886314906</v>
+        <v>-0.1855040787597515</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.059139434794221</v>
+        <v>-1.128897410114873</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.499323234260073</v>
+        <v>2.457468449067681</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.303462160048269</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1535180059495476</v>
+        <v>-0.181421196077808</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.084668356710713</v>
+        <v>-1.154426332031366</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.489519078228819</v>
+        <v>2.447664293036428</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.337114998556743</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1624965868685009</v>
+        <v>-0.1903997769967614</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.185081724627751</v>
+        <v>-1.254839699948403</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.433753611963033</v>
+        <v>2.391898826770642</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.4762011131756</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2027593312226226</v>
+        <v>-0.2306625213508831</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.324167839246607</v>
+        <v>-1.39392581456726</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36567364468514</v>
+        <v>2.323818859492749</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.651325530562143</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2582538774297229</v>
+        <v>-0.2861570675579839</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.569050231953804</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.275154215000731</v>
+        <v>2.233299429808339</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.885777624576633</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.359253879937115</v>
+        <v>-0.3871570700653755</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.499292256633151</v>
+        <v>-1.569050231953804</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.267935050099135</v>
+        <v>2.226080264906743</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.920394380282426</v>
+        <v>-8.99015235560308</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4076759631216698</v>
+        <v>-0.4355791532499302</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.603666987659597</v>
+        <v>-1.673424962980249</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.198638020709291</v>
+        <v>2.156783235516899</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.08290784598101</v>
+        <v>-9.152665821301664</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.471565559562547</v>
+        <v>-0.4994687496908079</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.701300418078284</v>
+        <v>-1.771058393398936</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.141173752296635</v>
+        <v>2.099318967104244</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.2089446393493</v>
+        <v>-9.278702614669953</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5192865482807481</v>
+        <v>-0.547189738409009</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.745806770589194</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.159018454611595</v>
+        <v>2.117163669419204</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.151872867453369</v>
+        <v>-9.221630842774022</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4924675038359752</v>
+        <v>-0.5203706939642356</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.745806770589194</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.163008790297996</v>
+        <v>2.121154005105605</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.293544709177489</v>
+        <v>-9.363302684498143</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.550611467424365</v>
+        <v>-0.5785146575526254</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.676048795268541</v>
+        <v>-1.745806770589194</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.161533563399254</v>
+        <v>2.119678778206863</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.243953864752655</v>
+        <v>-9.313711840073308</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5157217194895587</v>
+        <v>-0.5436249096178196</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.626457950843708</v>
+        <v>-1.69621592616436</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.206341480219027</v>
+        <v>2.164486695026635</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.095035530280798</v>
+        <v>-9.164793505601452</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4692055193474993</v>
+        <v>-0.4971087094757598</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.595208360108535</v>
+        <v>-1.664966335429187</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.212040101013448</v>
+        <v>2.170185315821056</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.869190377561386</v>
+        <v>-8.93894835288204</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3692883852235256</v>
+        <v>-0.3971915753517865</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.623039659842023</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.246775179401955</v>
+        <v>2.204920394209563</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.744611721223794</v>
+        <v>-8.814369696544448</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.31831777813243</v>
+        <v>-0.3462209682606909</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.553281684521371</v>
+        <v>-1.623039659842023</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.247914323958013</v>
+        <v>2.206059538765622</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.719575039655284</v>
+        <v>-8.789333014975938</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3056693313429184</v>
+        <v>-0.3335725214711793</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.597710572291287</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.265745550650562</v>
+        <v>2.223890765458171</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.647441864367403</v>
+        <v>-8.717199839688057</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2710823569891296</v>
+        <v>-0.2989855471173901</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.527952596970635</v>
+        <v>-1.597710572291287</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.271479254889199</v>
+        <v>2.229624469696808</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.576075471757756</v>
+        <v>-8.64583344707841</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2522730623391358</v>
+        <v>-0.2801762524673963</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.526344179681639</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.304561828061122</v>
+        <v>2.262707042868731</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.482616437772531</v>
+        <v>-8.552374413093185</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2247729300579535</v>
+        <v>-0.2526761201862144</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.526344179681639</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.294678346748215</v>
+        <v>2.252823561555823</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436232</v>
+        <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.4719632562191</v>
+        <v>-8.541721231539753</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2223462179359545</v>
+        <v>-0.2502494080642155</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.456586204360987</v>
+        <v>-1.526344179681639</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.292843786248842</v>
+        <v>2.25098900105645</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.374056217542609</v>
+        <v>-8.443814192863263</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1834837174388193</v>
+        <v>-0.2113869075670798</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.388600454500431</v>
+        <v>-1.458358429821083</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.333334921191714</v>
+        <v>2.291480135999323</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.350102676566651</v>
+        <v>-8.419860651887305</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1732337949029423</v>
+        <v>-0.2011369850312033</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.364646913524473</v>
+        <v>-1.434404888845126</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.348375551922782</v>
+        <v>2.306520766730391</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.086042738243854</v>
+        <v>-8.155800713564508</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08087013573557567</v>
+        <v>-0.1087733258638366</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.170344950522329</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.493551198754708</v>
+        <v>2.451696413562317</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.378963114739016</v>
+        <v>-7.44872109005967</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1991746800060588</v>
+        <v>0.1712714898777978</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.100586975201677</v>
+        <v>-1.170344950522329</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.490764165094407</v>
+        <v>2.448909379902016</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937444738873</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.338778816372826</v>
+        <v>-7.408536791693479</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2155920232403763</v>
+        <v>0.1876888331121154</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.060402676835486</v>
+        <v>-1.130160652156138</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.515218368001963</v>
+        <v>2.473363582809572</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626477</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.175378945433463</v>
+        <v>-7.245136920754117</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2803187928368782</v>
+        <v>0.2524156027086173</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8970028058961237</v>
+        <v>-0.966760781216776</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.612625111786337</v>
+        <v>2.570770326593946</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.017261566054688</v>
+        <v>-7.087019541375342</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3514901734262406</v>
+        <v>0.3235869832979796</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7388854265173482</v>
+        <v>-0.8086434018380005</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.715419968251455</v>
+        <v>2.673565183059064</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.867595175047173</v>
+        <v>-6.937353150367827</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4084645195162873</v>
+        <v>0.3805613293880268</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6459819352748123</v>
+        <v>-0.7157399105954646</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.768269852684018</v>
+        <v>2.726415067491626</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.735319701416286</v>
+        <v>-6.80507767673694</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3626354949757968</v>
+        <v>0.3347323048475359</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5137064616439256</v>
+        <v>-0.5834644369645779</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.748895922869704</v>
+        <v>2.707041137677313</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.563458485851384</v>
+        <v>-6.633216461172037</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4341950418893945</v>
+        <v>0.4062918517611336</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3418452460790228</v>
+        <v>-0.4116032213996751</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.854827712896283</v>
+        <v>2.812972927703891</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.478493819122065</v>
+        <v>-6.548251794442718</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4810872498047809</v>
+        <v>0.45318405967652</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2568805793497032</v>
+        <v>-0.3266385546703555</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.918712854157533</v>
+        <v>2.876858068965142</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.584083808895169</v>
+        <v>-6.653841784215823</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3108753242963203</v>
+        <v>0.2829721341680598</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3624705691228076</v>
+        <v>-0.4322285444434599</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.727382930694452</v>
+        <v>2.68552814550206</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.515849224269742</v>
+        <v>-6.585607199590395</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3867135000235775</v>
+        <v>0.358810309895317</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3440552462502716</v>
+        <v>-0.4138132215709239</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.78697646629506</v>
+        <v>2.745121681102668</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.367909182862142</v>
+        <v>-6.437667158182796</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3292687079482102</v>
+        <v>0.3013655178199497</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.323734330341714</v>
+        <v>-0.3934923056623663</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.682548207201787</v>
+        <v>2.640693422009396</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.314939660608154</v>
+        <v>-6.384697635928807</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3417425305963278</v>
+        <v>0.3138393404680668</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.3405227834083774</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.705615934300702</v>
+        <v>2.663761149108311</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.149151464647863</v>
+        <v>-6.218909439968517</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4010971968853507</v>
+        <v>0.3731940067570898</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.3405227834083774</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.698655322205609</v>
+        <v>2.656800537013218</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.115788258169094</v>
+        <v>-6.185546233489748</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4289048338580015</v>
+        <v>0.4010016437297406</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.3405227834083774</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.713117676586752</v>
+        <v>2.671262891394361</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.007529121046573</v>
+        <v>-6.077287096367226</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4667406091662052</v>
+        <v>0.4388374190379443</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2707648080877251</v>
+        <v>-0.3405227834083774</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.707649797045947</v>
+        <v>2.665795011853556</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.884237986229442</v>
+        <v>-5.953995961550095</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5135551571036343</v>
+        <v>0.4856519669753734</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1474736732705946</v>
+        <v>-0.2172316485912469</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.779122571946802</v>
+        <v>2.737267786754411</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.831541119098151</v>
+        <v>-5.901299094418804</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5423348821934759</v>
+        <v>0.5144316920652154</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.09477680613930345</v>
+        <v>-0.1645347814599558</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.818441670462903</v>
+        <v>2.776586885270511</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.587775677114706</v>
+        <v>-5.65753365243536</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6356217673339044</v>
+        <v>0.6077185772056435</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.09477680613930345</v>
+        <v>-0.1645347814599558</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.814222378809953</v>
+        <v>2.772367593617562</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.498000004738234</v>
+        <v>-5.567757980058888</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6736563502045092</v>
+        <v>0.6457531600762487</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.1029353365456457</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.853306359678555</v>
+        <v>2.811451574486164</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.248149610789159</v>
+        <v>-5.317907586109813</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7663385827678413</v>
+        <v>0.7384353926395804</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.1029353365456457</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.846048434662257</v>
+        <v>2.804193649469866</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.072257518321727</v>
+        <v>-5.142015493642381</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8402945432754629</v>
+        <v>0.812391353147202</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.03317736122499343</v>
+        <v>-0.1029353365456457</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.849647558182906</v>
+        <v>2.807792772990515</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.900811055299264</v>
+        <v>-4.970569030619918</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9222006345390019</v>
+        <v>0.8942974444107412</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1382691017974697</v>
+        <v>0.0685111264768174</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.965842942050938</v>
+        <v>2.923988156858546</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.820788768190143</v>
+        <v>-4.890546743510797</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9532300269989473</v>
+        <v>0.9253268368706866</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2182913889065907</v>
+        <v>0.1485334135859384</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.012876791932707</v>
+        <v>2.971022006740316</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.757153025956208</v>
+        <v>-4.826911001276862</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9833791249468384</v>
+        <v>0.9554759348185775</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2819271311405252</v>
+        <v>0.2121691558198729</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.055753038327385</v>
+        <v>3.013898253134994</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.663455707739813</v>
+        <v>-4.733213683060467</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.002052311017192</v>
+        <v>0.9741491208889312</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2819271311405252</v>
+        <v>0.2121691558198729</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.036947297111181</v>
+        <v>2.995092511918789</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.673958330805102</v>
+        <v>-4.743716306125756</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9995943384159538</v>
+        <v>0.9716911482876931</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2714245080752363</v>
+        <v>0.201666532754584</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.032388799896885</v>
+        <v>2.990534014704493</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.561472070136228</v>
+        <v>-4.631230045456881</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.048518156518324</v>
+        <v>1.020614966390063</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2714245080752363</v>
+        <v>0.201666532754584</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.036318113731705</v>
+        <v>2.994463328539314</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.543758383258362</v>
+        <v>-4.613516358579016</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.05628221518681</v>
+        <v>1.028379025058549</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2746058369721531</v>
+        <v>0.2048478616515008</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.038905494987195</v>
+        <v>2.997050709794804</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.420284111945344</v>
+        <v>-4.490042087265998</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.102669994932011</v>
+        <v>1.07476680480375</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2746058369721531</v>
+        <v>0.2048478616515008</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.035903566207188</v>
+        <v>2.994048781014797</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.200263313908334</v>
+        <v>-4.270021289228987</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.192257351157429</v>
+        <v>1.164354161029168</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4158256820401334</v>
+        <v>0.3460677067194811</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.122214510258591</v>
+        <v>3.0803597250662</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.067395624845056</v>
+        <v>-4.13715360016571</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.261298609584564</v>
+        <v>1.233395419456303</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4158256820401334</v>
+        <v>0.3460677067194811</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.138108693060414</v>
+        <v>3.096253907868023</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496256</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.947222541480557</v>
+        <v>-4.016980516801211</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.310513687370665</v>
+        <v>1.282610497242404</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5359987654046323</v>
+        <v>0.46624079008398</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.211358387519415</v>
+        <v>3.169503602327024</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.81196918015058</v>
+        <v>-3.881727155471234</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.374703134464096</v>
+        <v>1.346799944335835</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6712521267346094</v>
+        <v>0.6014941514139571</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.302598506878842</v>
+        <v>3.26074372168645</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942101</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.871844007508273</v>
+        <v>-3.941601982828926</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.336790694922444</v>
+        <v>1.308887504794184</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6113772993769173</v>
+        <v>0.541619324056265</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.252711101865652</v>
+        <v>3.210856316673261</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.752023776597435</v>
+        <v>-3.821781751918089</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.400007956520988</v>
+        <v>1.372104766392727</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6113772993769173</v>
+        <v>0.541619324056265</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.268000271099861</v>
+        <v>3.226145485907469</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.754493483059241</v>
+        <v>-3.824251458379895</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.306664273258707</v>
+        <v>1.278761083130446</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6089075929151111</v>
+        <v>0.5391496175944588</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.174162646545219</v>
+        <v>3.132307861352827</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.822863669383251</v>
+        <v>-3.892621644703905</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.198578060214404</v>
+        <v>1.170674870086144</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.618183291951326</v>
+        <v>0.5484253166306737</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.098989927452249</v>
+        <v>3.057135142259857</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.934735949009402</v>
+        <v>-4.004493924330055</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.144265856995835</v>
+        <v>1.116362666867575</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.618183291951326</v>
+        <v>0.5484253166306737</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.08942663608414</v>
+        <v>3.047571850891749</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.918761283523134</v>
+        <v>-3.988519258843787</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.11723024811437</v>
+        <v>1.089327057986109</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.618183291951326</v>
+        <v>0.5484253166306737</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.056001161008167</v>
+        <v>3.014146375815776</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
         <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.743287023730665</v>
+        <v>-3.813044999051318</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.191987184023146</v>
+        <v>1.164083993894885</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.618183291951326</v>
+        <v>0.5484253166306737</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.060568392999955</v>
+        <v>3.018713607807564</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.73536264914575</v>
+        <v>-3.805120624466404</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.170898962618318</v>
+        <v>1.142995772490058</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.618183291951326</v>
+        <v>0.5484253166306737</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.036310421761162</v>
+        <v>2.994455636568771</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.729084446575901</v>
+        <v>-3.798842421896555</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.101948557047708</v>
+        <v>1.074045366919447</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.5547035192005227</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.968615656704522</v>
+        <v>2.92676087151213</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.669231827372178</v>
+        <v>-3.738989802692832</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.136061991161329</v>
+        <v>1.108158801033069</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.5547035192005227</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.978788043136654</v>
+        <v>2.936933257944263</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742296</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.582988364345801</v>
+        <v>-3.652746339666455</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.165505646945741</v>
+        <v>1.13760245681748</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6244614945211751</v>
+        <v>0.5547035192005227</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.973734313710514</v>
+        <v>2.931879528518123</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.628295183744781</v>
+        <v>-3.698053159065434</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.139158694630674</v>
+        <v>1.111255504502414</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5836513315119443</v>
+        <v>0.513893356191292</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.941023991349501</v>
+        <v>2.89916920615711</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.657328288447082</v>
+        <v>-3.727086263767736</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.128097325782855</v>
+        <v>1.100194135654594</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5836513315119443</v>
+        <v>0.513893356191292</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.941575864382603</v>
+        <v>2.899721079190211</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.564517806996223</v>
+        <v>-3.767568077616036</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.094494210254565</v>
+        <v>1.01327410200664</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6764618129628036</v>
+        <v>0.473411542342992</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.926534845144484</v>
+        <v>2.804704682772597</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.608907276325651</v>
+        <v>-3.811957546945464</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.078611898447394</v>
+        <v>0.9973917901994698</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6320723436333759</v>
+        <v>0.4290220730135643</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.901774639471428</v>
+        <v>2.779944477099541</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.588403582440153</v>
+        <v>-3.791453853059966</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.081889084513316</v>
+        <v>1.000668976265392</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6525760375188733</v>
+        <v>0.4495257668990617</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.90915256431445</v>
+        <v>2.787322401942563</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.628327677022726</v>
+        <v>-3.831377947642538</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.071410742510954</v>
+        <v>0.99019063426303</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6525760375188733</v>
+        <v>0.4495257668990617</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.914643860145117</v>
+        <v>2.79281369777323</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.656108074924079</v>
+        <v>-3.859158345543892</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.071795785118952</v>
+        <v>0.9905756768710279</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6247956396175203</v>
+        <v>0.4217453689977086</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.909472823172844</v>
+        <v>2.787642660800957</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.774488747654217</v>
+        <v>-3.97753901827403</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8627992360275503</v>
+        <v>0.7815791277796258</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.3545275168467324</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.707497831882912</v>
+        <v>2.585667669511025</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.883102826097548</v>
+        <v>-4.086153096717361</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9395032653694235</v>
+        <v>0.8582831571214991</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.3545275168467324</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.827647492602118</v>
+        <v>2.70581733023023</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.847693787849405</v>
+        <v>-4.050744058469218</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9681799067710035</v>
+        <v>0.8869597985230793</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5575777874665441</v>
+        <v>0.3545275168467324</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.842160518704441</v>
+        <v>2.720330356332553</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.856154956504867</v>
+        <v>-4.059205227124679</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9622148806511879</v>
+        <v>0.8809947724032636</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.549116618811083</v>
+        <v>0.3460663481912714</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.834503258853533</v>
+        <v>2.712673096481645</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.6790386264697</v>
+        <v>-3.882088897089512</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.029790441510557</v>
+        <v>0.9485703332626325</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.549116618811083</v>
+        <v>0.3460663481912714</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.831232287698835</v>
+        <v>2.709402125326948</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.724130871303246</v>
+        <v>-3.927181141923058</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.012436935339051</v>
+        <v>0.9312168270911272</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4872205756416932</v>
+        <v>0.2841703050218816</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.794778053559114</v>
+        <v>2.672947891187227</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.544755450064478</v>
+        <v>-3.747805720684291</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.077974079140973</v>
+        <v>0.9967539708930486</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6439973338124119</v>
+        <v>0.4409470631926002</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.88263108376796</v>
+        <v>2.760800921396072</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.589769663585085</v>
+        <v>-3.792819934204897</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.04077584906432</v>
+        <v>0.9595557408163959</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6136484384978073</v>
+        <v>0.4105981678779956</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.845229201910787</v>
+        <v>2.723399039538899</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.85677417385752</v>
+        <v>-4.059824444477332</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9396656072942917</v>
+        <v>0.8584454990463675</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4192854004548587</v>
+        <v>0.2162351298350471</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.734302941423963</v>
+        <v>2.612472779052076</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.957971955294693</v>
+        <v>-4.161022225914505</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.898390416615924</v>
+        <v>0.817170308368</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3508765869095395</v>
+        <v>0.1478263162897279</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.692461575193273</v>
+        <v>2.570631412821386</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.95146098868038</v>
+        <v>-4.154511259300192</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8985947648159658</v>
+        <v>0.8173746565680418</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3508765869095395</v>
+        <v>0.1478263162897279</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.69006153674759</v>
+        <v>2.568231374375703</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.932422860973083</v>
+        <v>-4.135473131592895</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9027347351071295</v>
+        <v>0.8215146268592055</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2926929755783449</v>
+        <v>0.08964270495853333</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.651676089157118</v>
+        <v>2.529845926785231</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.984938663247903</v>
+        <v>-4.187988933867715</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.001022815831392</v>
+        <v>0.9198027075834676</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2926929755783449</v>
+        <v>0.08964270495853333</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.770970490791308</v>
+        <v>2.649140328419421</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.988346974682483</v>
+        <v>-4.191397245302295</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.000492820243694</v>
+        <v>0.9192727119957693</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3252095445877223</v>
+        <v>0.1221592739679107</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.791313761183068</v>
+        <v>2.669483598811182</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.968990838788636</v>
+        <v>-4.172041109408448</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.014243804998158</v>
+        <v>0.9330236967502343</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3252095445877223</v>
+        <v>0.1221592739679107</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.797322291579994</v>
+        <v>2.675492129208108</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.821247868553634</v>
+        <v>-4.024298139173445</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9712912143693586</v>
+        <v>0.8900711061214348</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4930169018226055</v>
+        <v>0.2899666312027939</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.795956927198123</v>
+        <v>2.674126764826237</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.905069089828332</v>
+        <v>-4.108119360448144</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9405563473909604</v>
+        <v>0.8593362391430364</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4930169018226055</v>
+        <v>0.2899666312027939</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.798750548729604</v>
+        <v>2.676920386357718</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.898916383775547</v>
+        <v>-4.101966654395359</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9436797782037325</v>
+        <v>0.8624596699558085</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4991696078753898</v>
+        <v>0.2961193372555782</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.803104520752933</v>
+        <v>2.681274358381047</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.915725681926049</v>
+        <v>-4.118775952545861</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9360365356836422</v>
+        <v>0.854816427435718</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4823603097248881</v>
+        <v>0.2793100391050765</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.792099418602743</v>
+        <v>2.670269256230856</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.853427683149927</v>
+        <v>-4.056477953769739</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.027291288990912</v>
+        <v>0.9460711807429878</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5276545739993301</v>
+        <v>0.3246043033795186</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.885611530964229</v>
+        <v>2.763781368592342</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.651637485484769</v>
+        <v>-3.854687756104581</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9102993697711022</v>
+        <v>0.8290792615231779</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7256727661684845</v>
+        <v>0.5226224955486729</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.806714447979849</v>
+        <v>2.684884285607962</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
         <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.702524198170964</v>
+        <v>-3.905574468790776</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9602349170187994</v>
+        <v>0.8790148087708753</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.67478605348229</v>
+        <v>0.4717357828624784</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.846472652690307</v>
+        <v>2.72464249031842</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.615913455521156</v>
+        <v>-3.818963726140968</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.009506950194766</v>
+        <v>0.928286841946842</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.7534117846874483</v>
+        <v>0.5503615140676366</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.908275827529446</v>
+        <v>2.786445665157559</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.676122753526441</v>
+        <v>-3.879173024146253</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9839592118173239</v>
+        <v>0.9027391035693997</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.490152216062352</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.870686229550947</v>
+        <v>2.74885606717906</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.626936104842089</v>
+        <v>-3.829986375461901</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.002125489330993</v>
+        <v>0.920905381083069</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6932024866821638</v>
+        <v>0.490152216062352</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.869177847590875</v>
+        <v>2.747347685218988</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.582562973203521</v>
+        <v>-3.785613243823333</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.019737609421857</v>
+        <v>0.9385175011739326</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.5345253477009206</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.895664594009453</v>
+        <v>2.773834431637566</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.54783165188502</v>
+        <v>-3.750881922504832</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.028023932087847</v>
+        <v>0.9468038238399235</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7375756183207324</v>
+        <v>0.5345253477009206</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.890058388148043</v>
+        <v>2.768228225776156</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.500175921323964</v>
+        <v>-3.703226191943776</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.053467981340074</v>
+        <v>0.9722478730921502</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.785231348881788</v>
+        <v>0.5821810782619763</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.925033583512481</v>
+        <v>2.803203421140594</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.39965776282521</v>
+        <v>-3.602708033445022</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.098567618114301</v>
+        <v>1.017347509866377</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8857495073805426</v>
+        <v>0.6826992367607309</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.990236851986459</v>
+        <v>2.868406689614571</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.383752433392857</v>
+        <v>-3.586802704012669</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.091684422363114</v>
+        <v>1.01046431411519</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8066368466713036</v>
+        <v>0.603586576051492</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.929523928036788</v>
+        <v>2.807693765664901</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.338914031784459</v>
+        <v>-3.541964302404271</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.113717485617102</v>
+        <v>1.032497377369178</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8111802796161731</v>
+        <v>0.6081300089963615</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.936347690414338</v>
+        <v>2.814517528042451</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.358412488026467</v>
+        <v>-3.561462758646279</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.110079042751377</v>
+        <v>1.028858934503453</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7630956383362688</v>
+        <v>0.5600453677164572</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.911657845277473</v>
+        <v>2.789827682905586</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.314209650940567</v>
+        <v>-3.517259921560379</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.133639780113574</v>
+        <v>1.05241967186565</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8072984754221693</v>
+        <v>0.6042482048023576</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.944059150056851</v>
+        <v>2.822228987684964</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.321769316777614</v>
+        <v>-3.524819587397426</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.129025914248003</v>
+        <v>1.047805806000079</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.6590516088121769</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.97535119293199</v>
+        <v>2.853521030560103</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.163477899238341</v>
+        <v>-3.366528169858154</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.243590246446751</v>
+        <v>1.162370138198827</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8621018794319886</v>
+        <v>0.6590516088121769</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.026598958115029</v>
+        <v>2.904768795743142</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.955835895603865</v>
+        <v>-3.158886166223677</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.325087752494795</v>
+        <v>1.243867644246871</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.069743883066465</v>
+        <v>0.8666936124466531</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.149624864889968</v>
+        <v>3.027794702518081</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475138</v>
       </c>
       <c r="C1987" t="n">
         <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.904803802881337</v>
+        <v>-3.107854073501149</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.340448817822076</v>
+        <v>1.259228709574152</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.120775975788993</v>
+        <v>0.9177257051691811</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.175192348761755</v>
+        <v>3.053362186389868</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.839579621754131</v>
+        <v>-3.042629892373943</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.383725894365664</v>
+        <v>1.302505786117739</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.186000156916198</v>
+        <v>0.9829498862963867</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.231514261530783</v>
+        <v>3.109684099158896</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.802152601682998</v>
+        <v>-3.00520287230281</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.394657674693397</v>
+        <v>1.313437566445473</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.19125169494538</v>
+        <v>0.9882014243255683</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.230626156647573</v>
+        <v>3.108795994275686</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.800794616709452</v>
+        <v>-3.003844887329264</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.396457661014056</v>
+        <v>1.315237552766132</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.265589820483199</v>
+        <v>1.062539549863387</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.276485824301504</v>
+        <v>3.154655661929617</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.772381353609568</v>
+        <v>-2.975431624229381</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.56838073727522</v>
+        <v>1.487160629027296</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.20661425773677</v>
+        <v>1.003563987116958</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.401658257674858</v>
+        <v>3.279828095302971</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.697599092584556</v>
+        <v>-2.900649363204368</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.718406550903042</v>
+        <v>1.637186442655118</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.281396518761783</v>
+        <v>1.078346248141971</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.566640523507683</v>
+        <v>3.444810361135795</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.671515008320748</v>
+        <v>-2.87456527894056</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.720548160622425</v>
+        <v>1.6393280523745</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.281396518761783</v>
+        <v>1.078346248141971</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.558348499521542</v>
+        <v>3.436518337149654</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.583637095211627</v>
+        <v>-2.78668736583144</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.753892521449852</v>
+        <v>1.672672413201928</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.397322161185134</v>
+        <v>1.194271890565322</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.626097080559332</v>
+        <v>3.504266918187445</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.574744633818344</v>
+        <v>-2.777794904438156</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.775003911733957</v>
+        <v>1.693783803486033</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.397322161185134</v>
+        <v>1.194271890565322</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.643651486286123</v>
+        <v>3.521821323914236</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.743220750788222</v>
+        <v>-2.946271021408034</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.69946851235059</v>
+        <v>1.618248404102666</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.369374325468553</v>
+        <v>1.166324054848741</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.618737832260758</v>
+        <v>3.496907669888872</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.296964558158782</v>
+        <v>-2.500014828778594</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.859240686590228</v>
+        <v>1.778020578342304</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.27465565579892</v>
+        <v>1.071605385179109</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.543176327646841</v>
+        <v>3.421346165274953</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.27424345447563</v>
+        <v>-2.477293725095442</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.858993150560393</v>
+        <v>1.777773042312469</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.27465565579892</v>
+        <v>1.071605385179109</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.533840350143745</v>
+        <v>3.412010187771858</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.403445267769672</v>
+        <v>-2.606495538389484</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.966218551093945</v>
+        <v>1.884998442846021</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.145453842504878</v>
+        <v>0.9424035718850663</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.615225388018489</v>
+        <v>3.493395225646602</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.429319666243698</v>
+        <v>-2.63236993686351</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.992946614197981</v>
+        <v>1.911726505950057</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.190365451216619</v>
+        <v>0.9873151805968075</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.67925017573918</v>
+        <v>3.557420013367293</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.422264976028524</v>
+        <v>-2.625315246648336</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.992443846273596</v>
+        <v>1.911223738025672</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.197420141431793</v>
+        <v>0.9943698708119812</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.68015834585783</v>
+        <v>3.558328183485943</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.395313751702036</v>
+        <v>-2.598364022321848</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.013230489648933</v>
+        <v>1.932010381401009</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.212300487459512</v>
+        <v>1.0092502168397</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.699092707119203</v>
+        <v>3.577262544747316</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.416857979532824</v>
+        <v>-2.619908250152636</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.188715930661578</v>
+        <v>2.107495822413654</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.212300487459512</v>
+        <v>1.0092502168397</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.883195839264162</v>
+        <v>3.761365676892276</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.439266097337696</v>
+        <v>-2.642316367957508</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.171869378442622</v>
+        <v>2.090649270194698</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.212300487459512</v>
+        <v>1.0092502168397</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.875312534167155</v>
+        <v>3.753482371795269</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155033</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.467490332915296</v>
+        <v>-2.670540603535108</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.162633683761219</v>
+        <v>2.081413575513295</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.230277239910821</v>
+        <v>1.027226969291009</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.888152585187578</v>
+        <v>3.766322422815691</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.476931258803826</v>
+        <v>-2.81478134838132</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.215111031127655</v>
+        <v>2.079970995296657</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.352704357454212</v>
+        <v>1.003040291047026</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.01786257343546</v>
+        <v>3.808064133591149</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.5658078899723</v>
+        <v>-2.903657979549794</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.182451473205566</v>
+        <v>2.047311437374569</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.263827726285738</v>
+        <v>0.9141636598785523</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.967427689279677</v>
+        <v>3.757629249435365</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347705</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.642137867573206</v>
+        <v>-2.9799879571507</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.150031295058978</v>
+        <v>2.014891259227982</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.263827726285738</v>
+        <v>0.9141636598785523</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.965539502173452</v>
+        <v>3.755741062329141</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887751</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.797094652973335</v>
+        <v>-3.134944742550829</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.082868810501789</v>
+        <v>1.947728774670792</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.108870940885609</v>
+        <v>0.7592068744784231</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.867385660536237</v>
+        <v>3.657587220691925</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.95866307850059</v>
+        <v>-3.296513168078084</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.016675450501039</v>
+        <v>1.881535414670042</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9820880170877296</v>
+        <v>0.6324239506805437</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.789749916467661</v>
+        <v>3.57995147662335</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.06696374037071</v>
+        <v>-3.404813829948204</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.98642859261891</v>
+        <v>1.851288556787913</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9820880170877296</v>
+        <v>0.6324239506805437</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.80282332333358</v>
+        <v>3.593024883489269</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378386</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.084767712091454</v>
+        <v>-3.422617801668948</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.971312200713553</v>
+        <v>1.836172164882556</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9115533941825285</v>
+        <v>0.5618893277753425</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.752507746373399</v>
+        <v>3.542709306529088</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.112668499200927</v>
+        <v>-3.450518588778421</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.958675926996765</v>
+        <v>1.823535891165768</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8769564700395936</v>
+        <v>0.5272924036324077</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.73027363301464</v>
+        <v>3.520475193170329</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787384</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.23519460190382</v>
+        <v>-3.573044691481315</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.906429929892806</v>
+        <v>1.77128989406181</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7544303673366998</v>
+        <v>0.4047663009295138</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.653522415370103</v>
+        <v>3.443723975525791</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.465709098089409</v>
+        <v>-3.803559187666903</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.880930091009075</v>
+        <v>1.745790055178078</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.523915871151111</v>
+        <v>0.1742518047439251</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.581919677249253</v>
+        <v>3.372121237404942</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814663</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.814454183313853</v>
+        <v>-4.152304272891347</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.881743775921144</v>
+        <v>1.746603740090148</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.0655038508250273</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.656982623899762</v>
+        <v>3.44718418405545</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
         <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.968440601089993</v>
+        <v>-4.306290690667487</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.889129477956328</v>
+        <v>1.753989442125331</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.0655038508250273</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.725962893045402</v>
+        <v>3.51616445320109</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423386</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
         <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.173040035953002</v>
+        <v>-4.510890125530496</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.793340906131246</v>
+        <v>1.658200870300248</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.0655038508250273</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.712014095165522</v>
+        <v>3.502215655321211</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.425515189960726</v>
+        <v>-4.76336527953822</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.70422133358357</v>
+        <v>1.569081297752573</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.0655038508250273</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.723884584220936</v>
+        <v>3.514086144376625</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973157</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.718410946440138</v>
+        <v>-5.056261036017633</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.588273565510748</v>
+        <v>1.453133529679751</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4151679172322132</v>
+        <v>0.0655038508250273</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.72509511873988</v>
+        <v>3.515296678895568</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.905075074574946</v>
+        <v>-5.242925164152441</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.517729656484147</v>
+        <v>1.38258962065315</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.3884289464076534</v>
+        <v>0.03876488000046741</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.713173478472465</v>
+        <v>3.503375038628154</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916201</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.051095761488908</v>
+        <v>-5.388945851066403</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.454399234454751</v>
+        <v>1.319259198623755</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.02968178820661044</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.702801476132341</v>
+        <v>3.493003036288029</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.142809770598493</v>
+        <v>-5.480659860175988</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.579917687509961</v>
+        <v>1.444777651678964</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.3793458546137964</v>
+        <v>0.02968178820661044</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.865005532831385</v>
+        <v>3.655207092987073</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
         <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.174461429658463</v>
+        <v>-5.512311519235958</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.562103661849788</v>
+        <v>1.426963626018791</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.3741773973693562</v>
+        <v>0.02451333096217023</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.856751096448535</v>
+        <v>3.646952656604223</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.243527484231399</v>
+        <v>-5.581377573808894</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.544706657589105</v>
+        <v>1.409566621758107</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3118065198757461</v>
+        <v>-0.0378575465314398</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.82955798752086</v>
+        <v>3.619759547676549</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332693</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.345503606479807</v>
+        <v>-5.683353696057302</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.512841847145644</v>
+        <v>1.377701811314647</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.2098303976273386</v>
+        <v>-0.1398336687798474</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.777297952627718</v>
+        <v>3.567499512783407</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.79829678423181</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.235497323002585</v>
+        <v>-5.57334741258008</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.548997247780708</v>
+        <v>1.41385721194971</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.2330349695446138</v>
+        <v>-0.1166290968625722</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.783373583022259</v>
+        <v>3.573575143177947</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818516</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.092437747261659</v>
+        <v>-5.430287836839154</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.610471088799053</v>
+        <v>1.475331052968055</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.2410483961345931</v>
+        <v>-0.1086156702725929</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.79243164969822</v>
+        <v>3.582633209853909</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051784</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.58222756271021</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.790991021789822</v>
+        <v>-5.128841111367317</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.665474729680533</v>
+        <v>1.603170626039326</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.1928310551992444</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.907724635674068</v>
+        <v>3.770762128019547</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.583198740462921</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.815581266025005</v>
+        <v>-5.153431355602501</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.65660980973917</v>
+        <v>1.594305706097964</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.1928310551992444</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.908695813426779</v>
+        <v>3.771733305772258</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.584041644842676</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.764542890018485</v>
+        <v>-5.10239297959598</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.677868064521534</v>
+        <v>1.615563960880327</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.5424951216064303</v>
+        <v>0.1928310551992444</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.909538717806535</v>
+        <v>3.772576210152013</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.603079743716822</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.723403595151854</v>
+        <v>-5.061253684729349</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.713361881342332</v>
+        <v>1.651057777701125</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5836344164730611</v>
+        <v>0.2339703500658752</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.953260393600659</v>
+        <v>3.816297885946137</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700478</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.419263739840756</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.626768683133214</v>
+        <v>-4.964618772710709</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.568199842273722</v>
+        <v>1.505895738632515</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6802693284917011</v>
+        <v>0.3306052620845151</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.827425336935777</v>
+        <v>3.690462829281256</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077639</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.42276578391472</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.557730672184746</v>
+        <v>-4.895580761762242</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.599317090727073</v>
+        <v>1.537012987085867</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.7493073394401691</v>
+        <v>0.3996432730329832</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.872350187578822</v>
+        <v>3.735387679924301</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.407192602990802</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.393234337993785</v>
+        <v>-4.73108442757128</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.64954244347954</v>
+        <v>1.587238339838334</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.913803673631131</v>
+        <v>0.5641396072239451</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.955474807169481</v>
+        <v>3.818512299514961</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077624</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.406380313427232</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.316135736451912</v>
+        <v>-4.653985826029407</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.679569594532719</v>
+        <v>1.617265490891513</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.913803673631131</v>
+        <v>0.5641396072239451</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.954662517605911</v>
+        <v>3.81770000995139</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.416249092552305</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.326520931341801</v>
+        <v>-4.664371020919297</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.685284295701836</v>
+        <v>1.622980192060629</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9034184787412417</v>
+        <v>0.5537544123340558</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.95830017979705</v>
+        <v>3.821337672142529</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.48708609832873</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.345109090064026</v>
+        <v>-4.682959179641522</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.748686037989371</v>
+        <v>1.686381934348165</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.8848303200190164</v>
+        <v>0.5351662536118305</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.01798429034014</v>
+        <v>3.881021782685619</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496556</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.483955109147028</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.345407636760062</v>
+        <v>-4.683257726337557</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.745435630129255</v>
+        <v>1.683131526488049</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.8845317733229805</v>
+        <v>0.5348677069157945</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.014674173140817</v>
+        <v>3.877711665486296</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.48848600408642</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.244584503069635</v>
+        <v>-4.58243459264713</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.790295778544818</v>
+        <v>1.727991674903611</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.8969959888073343</v>
+        <v>0.5473319224001484</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.026683597370821</v>
+        <v>3.889721089716299</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.488615257564963</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.053803142317227</v>
+        <v>-4.391653231894722</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.866737576324324</v>
+        <v>1.804433472683117</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.087777349559742</v>
+        <v>0.7381132831525558</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.141281667300808</v>
+        <v>4.004319159646287</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.468452103302559</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.946839784467805</v>
+        <v>-4.2846898740453</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.889359765201689</v>
+        <v>1.827055661560483</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.146241957519543</v>
+        <v>0.7965778911123572</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.156197277814286</v>
+        <v>4.019234770159764</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912985</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.503419039914618</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.891509196566043</v>
+        <v>-4.229359286143538</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.946458936974452</v>
+        <v>1.884154833333246</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.201572545421305</v>
+        <v>0.8519084790141194</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.224362567167401</v>
+        <v>4.087400059512881</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.497105607816056</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.87945506965308</v>
+        <v>-4.217305159230575</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.944967155641075</v>
+        <v>1.882663051999869</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>0.8639626059270822</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.225281611216617</v>
+        <v>4.088319103562096</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.498986238000191</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.920610189221301</v>
+        <v>-4.258460278798796</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.930385737997923</v>
+        <v>1.868081634356717</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>0.8228074863588613</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.20246916965982</v>
+        <v>4.0655066620053</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.511837263878074</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-4.190411716107266</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.970456188952418</v>
+        <v>1.908152085311211</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>0.8908560490503911</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.256149333152621</v>
+        <v>4.119186825498099</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013427</v>
+        <v>3.645256780013425</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.532039934051668</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.422012109276767</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.898018701858211</v>
+        <v>1.835714598217005</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>0.8908560490503911</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.276352003326215</v>
+        <v>4.139389495671693</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498964</v>
+        <v>3.66674720149897</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.51564617011855</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.472063654805986</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.861604319713405</v>
+        <v>1.799300216072199</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>0.8908560490503911</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.259958239393097</v>
+        <v>4.122995731738576</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800095</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.475898083712017</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.64717048738243</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.751813500276294</v>
+        <v>1.689509396635088</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>0.8908560490503911</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.220210152986564</v>
+        <v>4.083247645332042</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660847</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.482920702708957</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.451070333951908</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.837276180645443</v>
+        <v>1.774972077004237</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.086956202480914</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.344892864041817</v>
+        <v>4.207930356387296</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.582091702281861</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-4.298044941838623</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.997657337063661</v>
+        <v>1.935353233422456</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.239981594594198</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.535879098882692</v>
+        <v>4.398916591228171</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791145</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.769557927190154</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-4.326352255711893</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.173800636422646</v>
+        <v>2.11149653278144</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.239981594594198</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.723345323790984</v>
+        <v>4.586382816136464</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620432</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.738960878544237</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.492945480825416</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.07656629773132</v>
+        <v>2.014262194090114</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.073388369480676</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.592792340076953</v>
+        <v>4.455829832422433</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.742637281205954</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.46990968746385</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.089457017737664</v>
+        <v>2.027152914096458</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.073388369480676</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.596468742738671</v>
+        <v>4.459506235084151</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.74058140139947</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.74025533632945</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.440663707008153</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.098773465043438</v>
+        <v>2.036469361402232</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.073388369480676</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.594086797862166</v>
+        <v>4.457124290207646</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256369</v>
+        <v>3.699404642256371</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.737548575487085</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.547589254886004</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.053296485049932</v>
+        <v>1.990992381408726</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>0.9664628216028243</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.527224708293091</v>
+        <v>4.39026220063857</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.738977377630319</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.692607813393253</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.996717863790267</v>
+        <v>1.934413760149061</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>0.8214442630955757</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.441642375331976</v>
+        <v>4.304679867677455</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.838908616888072</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.81094957917797</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.049312396734133</v>
+        <v>1.987008293092927</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>0.8321303016584658</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.547985237727463</v>
+        <v>4.411022730072942</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.836694314014011</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.862360001498678</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.026533924931789</v>
+        <v>1.964229821290583</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>0.8321303016584658</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.545770934853402</v>
+        <v>4.408808427198881</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437331</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.8365974420883</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.94177945270643</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.994669272522978</v>
+        <v>1.932365168881772</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>0.8321303016584658</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.545674062927691</v>
+        <v>4.40871155527317</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298399</v>
+        <v>3.736804952298397</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.836591335646343</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-5.037242450623648</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.956477966914133</v>
+        <v>1.894173863272927</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>0.8321303016584658</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.545667956485734</v>
+        <v>4.408705448831213</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218001</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.834687732208954</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.972866539772933</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.98032472781703</v>
+        <v>1.918020624175824</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>0.8965062125091809</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.582389899558774</v>
+        <v>4.445427391904254</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353537</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.84042154995668</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-5.028235701905126</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.963910880711879</v>
+        <v>1.901606777070673</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>0.8965062125091809</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.588123717306501</v>
+        <v>4.45116120965198</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.73682287011328</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.839959913299613</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.708604079325242</v>
+        <v>-5.046454168902735</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.956161857255768</v>
+        <v>1.893857753614562</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.221063841660525</v>
+        <v>0.8713997752533388</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.572598218295928</v>
+        <v>4.435635710641407</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113689</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.859834306149931</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.620397245177664</v>
+        <v>-4.958247334755157</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.011318983765118</v>
+        <v>1.949014880123912</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.221063841660525</v>
+        <v>0.8713997752533388</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.592472611146246</v>
+        <v>4.455510103491726</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016435</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.843535006674659</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.514362249972354</v>
+        <v>-4.852212339549848</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.03743368237197</v>
+        <v>1.975129578730764</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.221063841660525</v>
+        <v>0.8713997752533388</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.576173311670974</v>
+        <v>4.439210804016454</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.845965956138705</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.331150586839259</v>
+        <v>-4.669000676416752</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.113149297089254</v>
+        <v>2.050845193448047</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.221063841660525</v>
+        <v>0.8713997752533388</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.578604261135021</v>
+        <v>4.441641753480499</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863547</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.811757141986595</v>
+        <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.259429139825408</v>
+        <v>-4.597279229402901</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.107629061742684</v>
+        <v>2.045324958101477</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.292785288674375</v>
+        <v>0.9431212222671894</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.587428315191221</v>
+        <v>4.450465807536699</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.758672887907767</v>
+        <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.237056114217702</v>
+        <v>-4.574906203795195</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.063494017906938</v>
+        <v>2.001189914265732</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.304041039787277</v>
+        <v>0.954376973380091</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.541097511780133</v>
+        <v>4.404135004125612</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
-        <v>3.943871092793122</v>
+        <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.270072410128447</v>
+        <v>-4.60792249970594</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.235485704427996</v>
+        <v>2.173181600786789</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.234603663120525</v>
+        <v>0.8849395967133393</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.684633290665437</v>
+        <v>4.547670783010916</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883677</v>
       </c>
       <c r="C2071" t="n">
-        <v>3.935792318621371</v>
+        <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.258544774478838</v>
+        <v>-4.596394864056331</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.232017984516088</v>
+        <v>2.169713880874881</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.293604321321888</v>
+        <v>0.9439402549147018</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.711954911414504</v>
+        <v>4.574992403759983</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236298</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
-        <v>3.93946043114316</v>
+        <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.355886275821207</v>
+        <v>-4.6937363653987</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.196749496500929</v>
+        <v>2.134445392859722</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.249184139156399</v>
+        <v>0.8995200727492134</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.688970914636999</v>
+        <v>4.552008406982478</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427685</v>
+        <v>3.705201079427684</v>
       </c>
       <c r="C2073" t="n">
-        <v>3.940711513335998</v>
+        <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.441742305161173</v>
+        <v>-4.779592394738667</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.163658166957781</v>
+        <v>2.101354063316574</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.206808069930264</v>
+        <v>0.8571440035230784</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.664796355294157</v>
+        <v>4.527833847639635</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610377</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.9231307151565</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.450579102577293</v>
+        <v>-4.788429192154786</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.142542649811835</v>
+        <v>2.080238546170628</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.199365897288914</v>
+        <v>0.8497018308817277</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.642750253529848</v>
+        <v>4.505787745875327</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.715544411667455</v>
       </c>
       <c r="C2075" t="n">
-        <v>3.933295226201549</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.541961665142751</v>
+        <v>-4.879811754720245</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.116154135830701</v>
+        <v>2.053850032189494</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.162801012569569</v>
+        <v>0.813136946162383</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.630975833743291</v>
+        <v>4.494013326088769</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889192</v>
+        <v>3.673978374889191</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.035423484025817</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.530254947155745</v>
+        <v>-4.868105036733239</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.222965080849771</v>
+        <v>2.160660977208564</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.174507730556575</v>
+        <v>0.8248436641493894</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.740128122359762</v>
+        <v>4.60316561470524</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409568</v>
+        <v>3.682476099409566</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.038455822757221</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.601167020898023</v>
+        <v>-4.939017110475517</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.197632590084264</v>
+        <v>2.135328486443057</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.174507730556575</v>
+        <v>0.8248436641493894</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.743160461091167</v>
+        <v>4.606197953436645</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.251360656035279</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.611483119064375</v>
+        <v>-4.949333208641868</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.406410984095781</v>
+        <v>2.344106880454575</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.174507730556575</v>
+        <v>0.8248436641493894</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.956065294369225</v>
+        <v>4.819102786714703</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762288</v>
+        <v>3.623960959762286</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.250539322947369</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.611389151047002</v>
+        <v>-4.949239240624496</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.40562723821482</v>
+        <v>2.343323134573613</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.174877591903893</v>
+        <v>0.8252135254967073</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.955465878089705</v>
+        <v>4.818503370435184</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988019</v>
+        <v>3.633213467988017</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.244771308891723</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.759755378703147</v>
+        <v>-5.097605468280641</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.340512733096716</v>
+        <v>2.278208629455509</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.174877591903893</v>
+        <v>0.8252135254967073</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.949697864034059</v>
+        <v>4.812735356379537</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740917</v>
+        <v>3.647907242740923</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.244771308891723</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.758806955585109</v>
+        <v>-5.096657045162602</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.340892102343932</v>
+        <v>2.278587998702724</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.174877591903893</v>
+        <v>0.8252135254967073</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.949697864034059</v>
+        <v>4.812735356379537</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663621</v>
+        <v>3.881065366663627</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.257498916872815</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.85907677354413</v>
+        <v>-5.196926863121623</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.313511783141415</v>
+        <v>2.251207679500208</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.174877591903893</v>
+        <v>0.8252135254967073</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.962425472015151</v>
+        <v>4.825462964360629</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424771</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.259444915297203</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.853084526755318</v>
+        <v>-5.285192496045648</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.317854680281327</v>
+        <v>2.217847424754986</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.174877591903893</v>
+        <v>0.8252135254967073</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.964371470439539</v>
+        <v>4.827408962785017</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.253099051314972</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.764526565624551</v>
+        <v>-5.19663453491488</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.346932000751403</v>
+        <v>2.246924745225062</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.174877591903893</v>
+        <v>0.8252135254967073</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.958025606457308</v>
+        <v>4.821063098802786</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383085</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.252407728753967</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.746767488121477</v>
+        <v>-5.178875457411806</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.353344309191629</v>
+        <v>2.253337053665287</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.174877591903893</v>
+        <v>0.8252135254967073</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.957334283896303</v>
+        <v>4.820371776241782</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720993</v>
+        <v>3.778232147720999</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.265189914662554</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.647137337072409</v>
+        <v>-5.079245306362738</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.405978555519843</v>
+        <v>2.305971299993501</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.274507742952961</v>
+        <v>0.9248436765457748</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.029894560434331</v>
+        <v>4.892932052779809</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.775357097455273</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.45434418016128</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.69653684576142</v>
+        <v>-5.128644815051749</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.575373017542964</v>
+        <v>2.475365762016623</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.284766576384706</v>
+        <v>0.9351025099775195</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.225204125992104</v>
+        <v>5.088241618337582</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963134</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.441532853264142</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.489852372119044</v>
+        <v>-4.921960341409374</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.645235480102777</v>
+        <v>2.545228224576435</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.491451050027081</v>
+        <v>1.141786983619895</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.336403483280391</v>
+        <v>5.19944097562587</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162543</v>
+        <v>3.740284389162544</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.443534366918247</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.52400926711657</v>
+        <v>-4.9561172364069</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.633574235757871</v>
+        <v>2.53356698023153</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.407867280486269</v>
+        <v>1.058203214079083</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.288254735210009</v>
+        <v>5.151292227555487</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.782482115652384</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.797031480907915</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.431419788055114</v>
+        <v>-4.863527757345444</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.024107141372121</v>
+        <v>2.92409988584578</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.407867280486269</v>
+        <v>1.058203214079083</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.641751849199676</v>
+        <v>5.504789341545155</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108672</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.801594592475018</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.491308415878664</v>
+        <v>-4.923416385168994</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.004714801809804</v>
+        <v>2.904707546283463</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.393745365798804</v>
+        <v>1.044081299391618</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.637841811954301</v>
+        <v>5.500879304299779</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103564</v>
+        <v>3.835202441103563</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.851424533798546</v>
+        <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.439092106082322</v>
+        <v>-4.871200075372652</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.075431267051869</v>
+        <v>2.975424011525527</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.393745365798804</v>
+        <v>1.044081299391618</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.687671753277828</v>
+        <v>5.550709245623306</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047745</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.860238504008557</v>
+        <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.407194588997077</v>
+        <v>-4.839302558287407</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.097004244095978</v>
+        <v>2.996996988569636</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.42564288288405</v>
+        <v>1.075978816476864</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.715624233738986</v>
+        <v>5.578661726084465</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650754</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.855876088047753</v>
+        <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.421949913197217</v>
+        <v>-4.854057882487547</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.086739698455118</v>
+        <v>2.986732442928777</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.42564288288405</v>
+        <v>1.075978816476864</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.711261817778183</v>
+        <v>5.574299310123662</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135749</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.846800591464033</v>
+        <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.372485289827305</v>
+        <v>-4.804593259117635</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.097450051219363</v>
+        <v>2.997442795693022</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.475107506253962</v>
+        <v>1.125443439846775</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.731865095216411</v>
+        <v>5.594902587561888</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.825931790479222</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.843208259178968</v>
+        <v>4.916044191368758</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.20937729767369</v>
+        <v>-4.64148526696402</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.159100915795744</v>
+        <v>3.059093660269403</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.638215498407577</v>
+        <v>1.288551432000391</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.826137558223514</v>
+        <v>5.689175050568992</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844239</v>
+        <v>3.847096478844247</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.852255295870096</v>
+        <v>4.925091228059886</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.076569672176523</v>
+        <v>-4.508677641466853</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.221271002685739</v>
+        <v>3.121263747159397</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.638215498407577</v>
+        <v>1.288551432000391</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.835184594914642</v>
+        <v>5.69822208726012</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790948</v>
+        <v>3.832425987790955</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.853112760856217</v>
+        <v>4.925948693046007</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.139277588651082</v>
+        <v>-4.571385557941412</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.197045301082037</v>
+        <v>3.097038045555696</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.575507581933019</v>
+        <v>1.225843515525833</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.798417310016029</v>
+        <v>5.661454802361507</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.83251510151092</v>
+        <v>3.566968654133285</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.927761295252113</v>
+        <v>4.875155990723531</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.139277588651082</v>
+        <v>-4.571385557941412</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.197045301082037</v>
+        <v>3.097038045555696</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.575507581933019</v>
+        <v>1.225843515525833</v>
       </c>
       <c r="G2099" t="n">
-        <v>4.920825092238481</v>
+        <v>4.868219787709899</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240926.xlsx
+++ b/tame_output/ON/bt/strategyON_20240926.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>52.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>112.4%</t>
+          <t>117.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>175.9%</t>
+          <t>190.3%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-614.4%</t>
+          <t>-607.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>426.9%</t>
+          <t>421.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-618.7%</t>
+          <t>-579.2%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-246.2%</t>
+          <t>-234.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>333.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-66.5%</t>
+          <t>-41.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.8%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-242.8%</t>
+          <t>-235.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-298.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-101.4%</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>137.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-146.1%</t>
+          <t>-132.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1461,52 +1461,52 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>126.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>150.5%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.2937328739283852</v>
+        <v>0.3634908492490375</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.239706897370549</v>
+        <v>3.26761008749881</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.637814634520188</v>
+        <v>1.70757260984084</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.105258952825055</v>
+        <v>4.147113738017447</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.1700383883725511</v>
+        <v>0.2397963636932034</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.225170187645757</v>
+        <v>3.253073377774018</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.637814634520188</v>
+        <v>1.70757260984084</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.140200037322598</v>
+        <v>4.182054822514989</v>
       </c>
     </row>
     <row r="1840">
@@ -43868,19 +43868,19 @@
         <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.156088696795822</v>
+        <v>3.249949287655787</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.1750759791001376</v>
+        <v>0.2448339544207899</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.22576266412213</v>
+        <v>3.347526445110355</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.693459090786505</v>
+        <v>1.763217066107158</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.172164151267726</v>
+        <v>4.307879527320082</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.13483507841956</v>
+        <v>3.228695669279524</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.08211805560791913</v>
+        <v>-0.01236008028726682</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.101631431862645</v>
+        <v>3.22339521285087</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.436265056078448</v>
+        <v>1.506023031399101</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.996594112066629</v>
+        <v>4.132309488118985</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.13585268755003</v>
+        <v>3.229713278409994</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.1478854456573312</v>
+        <v>-0.07812747033667888</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.07634208497335</v>
+        <v>3.198105865961575</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.436265056078448</v>
+        <v>1.506023031399101</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.997611721197099</v>
+        <v>4.133327097249454</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.126480719537785</v>
+        <v>3.22034131039775</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.3802563598190059</v>
+        <v>-0.3104983844983536</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.974021751296436</v>
+        <v>3.095785532284661</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.436265056078448</v>
+        <v>1.506023031399101</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.988239753184855</v>
+        <v>4.12395512923721</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.116563445493024</v>
+        <v>3.210424036352988</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.4620282602467576</v>
+        <v>-0.3922702849261053</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.931395717080573</v>
+        <v>3.053159498068799</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.463300629484585</v>
+        <v>1.533058604805237</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.994543823183775</v>
+        <v>4.13025919923613</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296833</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.121328762326726</v>
+        <v>3.21518935318669</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7243491816667322</v>
+        <v>-0.6545912063460799</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.831232665346286</v>
+        <v>2.952996446334511</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.463300629484585</v>
+        <v>1.533058604805237</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.999309140017477</v>
+        <v>4.135024516069833</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201484</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.119153558445966</v>
+        <v>3.213014149305931</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7129599450119308</v>
+        <v>-0.6432019696912785</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.833613156127447</v>
+        <v>2.955376937115672</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.474689866139387</v>
+        <v>1.544447841460039</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.003967478129598</v>
+        <v>4.139682854181954</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153003</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.117080449951029</v>
+        <v>3.210941040810994</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.9654378394313368</v>
+        <v>-0.8956798641106845</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.730548889864747</v>
+        <v>2.852312670852973</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.222211971719981</v>
+        <v>1.291969947040633</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.850407632983018</v>
+        <v>3.986123009035373</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.116946666549951</v>
+        <v>3.210807257409916</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.255569506036768</v>
+        <v>-1.185811530716116</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.614362439821496</v>
+        <v>2.736126220809722</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.246293766460161</v>
+        <v>1.316051741780813</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.864722926426048</v>
+        <v>4.000438302478403</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.121838811103876</v>
+        <v>3.215699401963841</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.463573564389846</v>
+        <v>-1.393815589069193</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.536052961034191</v>
+        <v>2.657816742022416</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.246293766460161</v>
+        <v>1.316051741780813</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.869615070979973</v>
+        <v>4.005330447032328</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.116920267441865</v>
+        <v>3.210780858301829</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.525751975550816</v>
+        <v>-1.455994000230163</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.506263052907791</v>
+        <v>2.628026833896016</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.18411535529919</v>
+        <v>1.253873330619843</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.827389480621379</v>
+        <v>3.963104856673735</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.110004566748314</v>
+        <v>3.203865157608278</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.891820702695468</v>
+        <v>-1.822062727374816</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.352919861356379</v>
+        <v>2.474683642344604</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8180466281545377</v>
+        <v>0.88780460347519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.600832543641037</v>
+        <v>3.736547919693392</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.130342856487082</v>
+        <v>3.224203447347046</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.100311484147153</v>
+        <v>-2.0305535088265</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.289861838514474</v>
+        <v>2.411625619502699</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.6095558467028532</v>
+        <v>0.6793138220235055</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.496076364508794</v>
+        <v>3.63179174056115</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.13844160689565</v>
+        <v>3.232302197755615</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.347512668912374</v>
+        <v>-2.277754693591722</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.199080115016954</v>
+        <v>2.320843896005179</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.6297092002016657</v>
+        <v>0.699467175522318</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.51626712701665</v>
+        <v>3.651982503069006</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.139547998939383</v>
+        <v>3.233408589799347</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.839897696936471</v>
+        <v>-2.770139721615819</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.003232495851047</v>
+        <v>2.124996276839273</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1373241721775689</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.221942502245924</v>
+        <v>3.35765787829828</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.138090537752246</v>
+        <v>3.231951128612211</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.098201464620142</v>
+        <v>-3.02844348929949</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.898453527590442</v>
+        <v>2.020217308578667</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1373241721775689</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.220485041058788</v>
+        <v>3.356200417111144</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.139859661206862</v>
+        <v>3.233720252066827</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.348072144634723</v>
+        <v>-3.278314169314071</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.800274379039225</v>
+        <v>1.922038160027451</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.1735868920080322</v>
+        <v>0.2433448673286845</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.244011796411681</v>
+        <v>3.379727172464038</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.13596571986312</v>
+        <v>3.229826310723085</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.554583921521745</v>
+        <v>-3.484825946201093</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.713775726940675</v>
+        <v>1.8355395079289</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.03292488487898931</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.116210788935727</v>
+        <v>3.251926164988083</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.137738646563379</v>
+        <v>3.231599237423344</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.873927996602247</v>
+        <v>-3.804170021281594</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.587811023608733</v>
+        <v>1.709574804596959</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.03292488487898931</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.117983715635986</v>
+        <v>3.253699091688342</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.124071534030784</v>
+        <v>3.217932124890749</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.260137827878022</v>
+        <v>-4.190379852557369</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.419659978565828</v>
+        <v>1.541423759554053</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.1236978245964326</v>
+        <v>-0.05393984927578033</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.049852839272924</v>
+        <v>3.185568215325281</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.112356309032875</v>
+        <v>3.206216899892839</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.528689618575895</v>
+        <v>-4.458931643255243</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.300524037288769</v>
+        <v>1.422287818276995</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.1877027629414358</v>
+        <v>-0.1179447876207835</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.999734651268013</v>
+        <v>3.13545002732037</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.11093690068884</v>
+        <v>3.204797491548804</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.864352265806348</v>
+        <v>-4.794594290485695</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.164839570052553</v>
+        <v>1.286603351040779</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.2556337484303406</v>
+        <v>-0.1858757731096883</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.957556651630636</v>
+        <v>3.093272027682992</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.117424460923081</v>
+        <v>3.211285051783046</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.940796596009219</v>
+        <v>-4.871038620688567</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.140749398205646</v>
+        <v>1.262513179193872</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.1751882393366787</v>
+        <v>-0.1054302640160264</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.012311517321074</v>
+        <v>3.148026893373431</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.116678975928913</v>
+        <v>3.210539566788877</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.305923978647966</v>
+        <v>-5.236166003327313</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9939529601559789</v>
+        <v>1.115716741144205</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4714990236356912</v>
+        <v>-0.4017410483150389</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.833779561747498</v>
+        <v>2.969494937799854</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.209301110803636</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.714512755828645</v>
+        <v>-5.644754780507992</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8292789932984665</v>
+        <v>0.9510427742866918</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.8800878008163697</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.58738783945385</v>
+        <v>2.723103215506206</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.204486543275097</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.82827316785151</v>
+        <v>-5.758515192530857</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7789602609607811</v>
+        <v>0.9007240419490068</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.8800878008163697</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.582573271925311</v>
+        <v>2.718288647977667</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.202480593883974</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.244665042138507</v>
+        <v>-6.174907066817855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6103975618548594</v>
+        <v>0.7321613428430851</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.8800878008163697</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.580567322534188</v>
+        <v>2.716282698586544</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.212739284552653</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.605838671955495</v>
+        <v>-6.536080696634842</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4761868005967433</v>
+        <v>0.5979505815849686</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.8800878008163697</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.590826013202867</v>
+        <v>2.726541389255223</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.208838849698349</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.949097191598514</v>
+        <v>-6.879339216277861</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3349829578852308</v>
+        <v>0.4567467388734565</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.8800878008163697</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.586925578348562</v>
+        <v>2.722640954400918</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.20724376975335</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.997300008840858</v>
+        <v>-6.927542033520205</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3141067510432944</v>
+        <v>0.4358705320315197</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.8800878008163697</v>
+        <v>-0.8103298254957174</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.585330498403563</v>
+        <v>2.721045874455919</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.211022745682558</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.16410866881522</v>
+        <v>-7.094350693494567</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2511622629827577</v>
+        <v>0.3729260439709834</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.9223711245295063</v>
+        <v>-0.852613149208854</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.56373948010489</v>
+        <v>2.699454856157246</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.206996441148155</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.350828377124523</v>
+        <v>-7.28107040180387</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1724480751246333</v>
+        <v>0.294211856112859</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.9223711245295063</v>
+        <v>-0.852613149208854</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.559713175570486</v>
+        <v>2.695428551622843</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.206894339826571</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.733829765867154</v>
+        <v>-7.664071790546501</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.01914541830599692</v>
+        <v>0.1409091992942226</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.9223711245295063</v>
+        <v>-0.852613149208854</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.559611074248902</v>
+        <v>2.695326450301259</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.209465855798001</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.738316211068542</v>
+        <v>-7.66855823574789</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.01992235619687177</v>
+        <v>0.141686137185097</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.9268575697308949</v>
+        <v>-0.8570995944102426</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.559490723099499</v>
+        <v>2.695206099151855</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.214816159096051</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.097846533572545</v>
+        <v>-8.028088558251891</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.118539469506679</v>
+        <v>0.003224311481546227</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.9268575697308949</v>
+        <v>-0.8570995944102426</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.564841026397549</v>
+        <v>2.700556402449906</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.222732179053228</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.148195597026767</v>
+        <v>-8.078437621706113</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1307630749311905</v>
+        <v>-0.008999293942964837</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.977206633185117</v>
+        <v>-0.9074486578644647</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.542547608282194</v>
+        <v>2.67826298433455</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.225773929674997</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.245814874448163</v>
+        <v>-8.176056899127509</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.16676903527798</v>
+        <v>-0.04500525428975477</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.074825910606514</v>
+        <v>-1.005067935285861</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.487017792451125</v>
+        <v>2.622733168503481</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.228667485996569</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.299886373956522</v>
+        <v>-8.230128398635868</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1855040787597515</v>
+        <v>-0.06374029777152579</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.128897410114873</v>
+        <v>-1.059139434794221</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.457468449067681</v>
+        <v>2.593183825120037</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.234180683115212</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.303462160048269</v>
+        <v>-8.233704184727616</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.181421196077808</v>
+        <v>-0.05965741508958278</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.154426332031366</v>
+        <v>-1.084668356710713</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.447664293036428</v>
+        <v>2.583379669088784</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.238663237599648</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.337114998556743</v>
+        <v>-8.267357023236089</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1903997769967614</v>
+        <v>-0.06863599600853609</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.254839699948403</v>
+        <v>-1.185081724627751</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.391898826770642</v>
+        <v>2.527614202822998</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.254034939093069</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.4762011131756</v>
+        <v>-8.406443137854946</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2306625213508831</v>
+        <v>-0.1088987403626578</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.39392581456726</v>
+        <v>-1.324167839246607</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.323818859492749</v>
+        <v>2.459534235545105</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.268590159840586</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.651325530562143</v>
+        <v>-8.58156755524149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2861570675579839</v>
+        <v>-0.1643932865697582</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.569050231953804</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.233299429808339</v>
+        <v>2.369014805860695</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.26137099493899</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.885777624576633</v>
+        <v>-8.816019649255979</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3871570700653755</v>
+        <v>-0.2653932890771502</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.569050231953804</v>
+        <v>-1.499292256633151</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.226080264906743</v>
+        <v>2.361795640959099</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.254698804165014</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.99015235560308</v>
+        <v>-8.982559630026746</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4355791532499302</v>
+        <v>-0.3386814721594327</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.673424962980249</v>
+        <v>-1.665832237403918</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.156783235516899</v>
+        <v>2.255199461722663</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.25581459400357</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.152665821301664</v>
+        <v>-9.146847776944615</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4994687496908079</v>
+        <v>-0.403280941088024</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.771058393398936</v>
+        <v>-1.790046597030577</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.099318967104244</v>
+        <v>2.181786635785224</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.258508322632685</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.278702614669953</v>
+        <v>-9.272884570312904</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.547189738409009</v>
+        <v>-0.4510019298062251</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.745806770589194</v>
+        <v>-1.764794974220835</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.117163669419204</v>
+        <v>2.199631338100184</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.262498658319085</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.221630842774022</v>
+        <v>-9.215812798416973</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5203706939642356</v>
+        <v>-0.4241828853614518</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.745806770589194</v>
+        <v>-1.764794974220835</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.121154005105605</v>
+        <v>2.203621673786585</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.261023431420344</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.363302684498143</v>
+        <v>-9.357484640141093</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5785146575526254</v>
+        <v>-0.4823268489498416</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.745806770589194</v>
+        <v>-1.764794974220835</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.119678778206863</v>
+        <v>2.202146446887843</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940721</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.276076841585216</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.313711840073308</v>
+        <v>-9.307893795716259</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5436249096178196</v>
+        <v>-0.4474371010150358</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.69621592616436</v>
+        <v>-1.715204129796001</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.164486695026635</v>
+        <v>2.246954363707616</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.263025707938533</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.164793505601452</v>
+        <v>-9.158975461244403</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4971087094757598</v>
+        <v>-0.4009209008729759</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.664966335429187</v>
+        <v>-1.683954539060828</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.170185315821056</v>
+        <v>2.252652984502037</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.272604780974742</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.93894835288204</v>
+        <v>-8.933130308524992</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3971915753517865</v>
+        <v>-0.3010037667490035</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.623039659842023</v>
+        <v>-1.642027863473664</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.204920394209563</v>
+        <v>2.287388062890543</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.273743925530801</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.814369696544448</v>
+        <v>-8.808551652187401</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3462209682606909</v>
+        <v>-0.250033159657908</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.623039659842023</v>
+        <v>-1.642027863473664</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.206059538765622</v>
+        <v>2.288527207446602</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.276377699692908</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.789333014975938</v>
+        <v>-8.78351497061889</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3335725214711793</v>
+        <v>-0.2373847128683959</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.597710572291287</v>
+        <v>-1.616698775922929</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.223890765458171</v>
+        <v>2.306358434139151</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.282111403931545</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.717199839688057</v>
+        <v>-8.711381795331009</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2989855471173901</v>
+        <v>-0.2027977385146071</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.597710572291287</v>
+        <v>-1.616698775922929</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.229624469696808</v>
+        <v>2.312092138377788</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.272374141537679</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.64583344707841</v>
+        <v>-8.640015402721362</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2801762524673963</v>
+        <v>-0.1839884438646133</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.526344179681639</v>
+        <v>-1.545332383313281</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.262707042868731</v>
+        <v>2.345174711549712</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.262490660224772</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.552374413093185</v>
+        <v>-8.546556368736137</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2526761201862144</v>
+        <v>-0.156488311583431</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.526344179681639</v>
+        <v>-1.545332383313281</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.252823561555823</v>
+        <v>2.335291230236804</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.260656099725398</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.541721231539753</v>
+        <v>-8.535903187182706</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2502494080642155</v>
+        <v>-0.1540615994614325</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.526344179681639</v>
+        <v>-1.545332383313281</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.25098900105645</v>
+        <v>2.33345666973743</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.260355784751937</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.443814192863263</v>
+        <v>-8.437996148506215</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2113869075670798</v>
+        <v>-0.1151990989642968</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.458358429821083</v>
+        <v>-1.477346633452724</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.291480135999323</v>
+        <v>2.373947804680303</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.261024290897431</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.419860651887305</v>
+        <v>-8.414042607530257</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2011369850312033</v>
+        <v>-0.1049491764284203</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.434404888845126</v>
+        <v>-1.453393092476767</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.306520766730391</v>
+        <v>2.388988435411371</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.247763974735679</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.155800713564508</v>
+        <v>-8.149982669207461</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1087733258638366</v>
+        <v>-0.01258551726105361</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.170344950522329</v>
+        <v>-1.18933315415397</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.451696413562317</v>
+        <v>2.534164082243297</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.244976941075378</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.44872109005967</v>
+        <v>-7.442903045702622</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1712714898777978</v>
+        <v>0.2674592984805808</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.170344950522329</v>
+        <v>-1.18933315415397</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.448909379902016</v>
+        <v>2.531377048582996</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.245320564963219</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.408536791693479</v>
+        <v>-7.402718747336432</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1876888331121154</v>
+        <v>0.2838766417148983</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.130160652156138</v>
+        <v>-1.14914885578778</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.473363582809572</v>
+        <v>2.555831251490552</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.244687386183976</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.245136920754117</v>
+        <v>-7.23931887639707</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2524156027086173</v>
+        <v>0.3486034113114003</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.966760781216776</v>
+        <v>-0.9857489848484171</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.570770326593946</v>
+        <v>2.653237995274926</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.252611815021829</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.087019541375342</v>
+        <v>-7.081201497018294</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3235869832979796</v>
+        <v>0.4197747919007631</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8086434018380005</v>
+        <v>-0.8276316054696417</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.673565183059064</v>
+        <v>2.756032851740044</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.249719604708869</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.937353150367827</v>
+        <v>-6.931535106010779</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3805613293880268</v>
+        <v>0.4767491379908098</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7157399105954646</v>
+        <v>-0.7347281142271057</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.726415067491626</v>
+        <v>2.808882736172606</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.057119799856059</v>
+        <v>3.150980390716024</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.80507767673694</v>
+        <v>-6.799259632379893</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3347323048475359</v>
+        <v>0.4309201134503189</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5834644369645779</v>
+        <v>-0.6024526405962191</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.707041137677313</v>
+        <v>2.789508806358293</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105955</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.059934860543696</v>
+        <v>3.153795451403661</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.633216461172037</v>
+        <v>-6.62739841681499</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4062918517611336</v>
+        <v>0.5024796603639166</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4116032213996751</v>
+        <v>-0.4305914250313162</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.812972927703891</v>
+        <v>2.895440596384872</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.072841201767355</v>
+        <v>3.16670179262732</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.548251794442718</v>
+        <v>-6.542433750085671</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.45318405967652</v>
+        <v>0.549371868279303</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3266385546703555</v>
+        <v>-0.3456267583019966</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.876858068965142</v>
+        <v>2.959325737646122</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.944865272168136</v>
+        <v>3.038725863028101</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.653841784215823</v>
+        <v>-6.648023739858775</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2829721341680598</v>
+        <v>0.3791599427708428</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.4322285444434599</v>
+        <v>-0.451216748075101</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.68552814550206</v>
+        <v>2.767995814183041</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>2.993409614045222</v>
+        <v>3.087270204905187</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.585607199590395</v>
+        <v>-6.579789155233348</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.358810309895317</v>
+        <v>0.4549981184981</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.4138132215709239</v>
+        <v>-0.432801425202565</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.745121681102668</v>
+        <v>2.827589349783648</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.876788805406815</v>
+        <v>2.97064939626678</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.437667158182796</v>
+        <v>-6.431849113825749</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3013655178199497</v>
+        <v>0.3975533264227327</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3934923056623663</v>
+        <v>-0.4124805092940074</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.640693422009396</v>
+        <v>2.723161090690376</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.868074819153337</v>
+        <v>2.961935410013302</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.384697635928807</v>
+        <v>-6.37887959157176</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3138393404680668</v>
+        <v>0.4100271490708498</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3405227834083774</v>
+        <v>-0.3595109870400185</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.663761149108311</v>
+        <v>2.746228817789291</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.861114207058244</v>
+        <v>2.954974797918209</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.218909439968517</v>
+        <v>-6.213091395611469</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3731940067570898</v>
+        <v>0.4693818153598732</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3405227834083774</v>
+        <v>-0.3595109870400185</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.656800537013218</v>
+        <v>2.739268205694198</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.875576561439387</v>
+        <v>2.969437152299352</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.185546233489748</v>
+        <v>-6.1797281891327</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4010016437297406</v>
+        <v>0.4971894523325235</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3405227834083774</v>
+        <v>-0.3595109870400185</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.671262891394361</v>
+        <v>2.753730560075341</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.870108681898582</v>
+        <v>2.963969272758547</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.077287096367226</v>
+        <v>-6.071469052010179</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4388374190379443</v>
+        <v>0.5350252276407272</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3405227834083774</v>
+        <v>-0.3595109870400185</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.665795011853556</v>
+        <v>2.748262680534536</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.867606775909159</v>
+        <v>2.961467366769124</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.953995961550095</v>
+        <v>-5.948177917193048</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4856519669753734</v>
+        <v>0.5818397755781568</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.2172316485912469</v>
+        <v>-0.236219852222888</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.737267786754411</v>
+        <v>2.819735455435391</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.875307754146484</v>
+        <v>2.969168345006449</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.901299094418804</v>
+        <v>-5.895481050061757</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5144316920652154</v>
+        <v>0.6106195006679984</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1645347814599558</v>
+        <v>-0.1835229850915969</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.776586885270511</v>
+        <v>2.859054553951491</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.871088462493535</v>
+        <v>2.9649490533535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.65753365243536</v>
+        <v>-5.651715608078312</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6077185772056435</v>
+        <v>0.7039063858084269</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1645347814599558</v>
+        <v>-0.1835229850915969</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.772367593617562</v>
+        <v>2.854835262298542</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057528</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.873212776413551</v>
+        <v>2.967073367273516</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.567757980058888</v>
+        <v>-5.56193993570184</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6457531600762487</v>
+        <v>0.7419409686790317</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1029353365456457</v>
+        <v>-0.1219235401772868</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.811451574486164</v>
+        <v>2.893919243167144</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.865954851397253</v>
+        <v>2.959815442257218</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.317907586109813</v>
+        <v>-5.312089541752766</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7384353926395804</v>
+        <v>0.8346232012423638</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1029353365456457</v>
+        <v>-0.1219235401772868</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.804193649469866</v>
+        <v>2.886661318150846</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.869553974917902</v>
+        <v>2.963414565777867</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.142015493642381</v>
+        <v>-5.136197449285334</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.812391353147202</v>
+        <v>0.908579161749985</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1029353365456457</v>
+        <v>-0.1219235401772868</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.807792772990515</v>
+        <v>2.890260441671495</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.882881480972455</v>
+        <v>2.97674207183242</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.970569030619918</v>
+        <v>-4.96475098626287</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8942974444107412</v>
+        <v>0.9904852530135242</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.0685111264768174</v>
+        <v>0.04952292284517629</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.923988156858546</v>
+        <v>3.006455825539526</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.881901958588752</v>
+        <v>2.975762549448717</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.890546743510797</v>
+        <v>-4.884728699153749</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9253268368706866</v>
+        <v>1.02151464547347</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1485334135859384</v>
+        <v>0.1295452099542972</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.971022006740316</v>
+        <v>3.053489675421296</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.88659675964307</v>
+        <v>2.980457350503035</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.826911001276862</v>
+        <v>-4.821092956919815</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9554759348185775</v>
+        <v>1.051663743421361</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2121691558198729</v>
+        <v>0.1931809521882318</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.013898253134994</v>
+        <v>3.096365921815974</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.867791018426865</v>
+        <v>2.96165160928683</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.733213683060467</v>
+        <v>-4.72739563870342</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9741491208889312</v>
+        <v>1.070336929491714</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2121691558198729</v>
+        <v>0.1931809521882318</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.995092511918789</v>
+        <v>3.077560180599769</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.869534095051743</v>
+        <v>2.963394685911708</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.743716306125756</v>
+        <v>-4.737898261768708</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9716911482876931</v>
+        <v>1.067878956890476</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.201666532754584</v>
+        <v>0.1826783291229429</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.990534014704493</v>
+        <v>3.073001683385474</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.873463408886563</v>
+        <v>2.967323999746528</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.631230045456881</v>
+        <v>-4.625412001099834</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.020614966390063</v>
+        <v>1.116802774992846</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.201666532754584</v>
+        <v>0.1826783291229429</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.994463328539314</v>
+        <v>3.076930997220294</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.874141992803903</v>
+        <v>2.968002583663868</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.613516358579016</v>
+        <v>-4.607698314221969</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.028379025058549</v>
+        <v>1.124566833661332</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2048478616515008</v>
+        <v>0.1858596580198597</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.997050709794804</v>
+        <v>3.079518378475784</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.871140064023896</v>
+        <v>2.965000654883861</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.490042087265998</v>
+        <v>-4.48422404290895</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.07476680480375</v>
+        <v>1.170954613406533</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2048478616515008</v>
+        <v>0.1858596580198597</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.994048781014797</v>
+        <v>3.076516449695777</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.872719101034511</v>
+        <v>2.966579691894475</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.270021289228987</v>
+        <v>-4.26420324487194</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.164354161029168</v>
+        <v>1.260541969631952</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3460677067194811</v>
+        <v>0.32707950308784</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.0803597250662</v>
+        <v>3.16282739374718</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.888613283836334</v>
+        <v>2.982473874696299</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.13715360016571</v>
+        <v>-4.131335555808662</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.233395419456303</v>
+        <v>1.329583228059086</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3460677067194811</v>
+        <v>0.32707950308784</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.096253907868023</v>
+        <v>3.178721576549003</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.889759128276636</v>
+        <v>2.983619719136601</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.016980516801211</v>
+        <v>-4.011162472444163</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.282610497242404</v>
+        <v>1.378798305845187</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.46624079008398</v>
+        <v>0.4472525864523389</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.169503602327024</v>
+        <v>3.251971271008004</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.899847230838076</v>
+        <v>2.99370782169804</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.881727155471234</v>
+        <v>-3.875909111114186</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.346799944335835</v>
+        <v>1.442987752938618</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6014941514139571</v>
+        <v>0.582505947782316</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.26074372168645</v>
+        <v>3.34321139036743</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.885884722239501</v>
+        <v>2.979745313099466</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.941601982828926</v>
+        <v>-3.935783938471879</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.308887504794184</v>
+        <v>1.405075313396967</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.541619324056265</v>
+        <v>0.5226311204246239</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.210856316673261</v>
+        <v>3.293323985354241</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.90117389147371</v>
+        <v>2.995034482333675</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.821781751918089</v>
+        <v>-3.815963707561041</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.372104766392727</v>
+        <v>1.46829257499551</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.541619324056265</v>
+        <v>0.5226311204246239</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.226145485907469</v>
+        <v>3.308613154588449</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.808818090796152</v>
+        <v>2.902678681656116</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.824251458379895</v>
+        <v>-3.818433414022847</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.278761083130446</v>
+        <v>1.374948891733229</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5391496175944588</v>
+        <v>0.5201614139628177</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.132307861352827</v>
+        <v>3.214775530033807</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.728079952281453</v>
+        <v>2.821940543141418</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.892621644703905</v>
+        <v>-3.886803600346857</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.170674870086144</v>
+        <v>1.266862678688927</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5484253166306737</v>
+        <v>0.5294371129990326</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.057135142259857</v>
+        <v>3.139602810940838</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.718516660913344</v>
+        <v>2.812377251773309</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.004493924330055</v>
+        <v>-3.998675879973008</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.116362666867575</v>
+        <v>1.212550475470358</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5484253166306737</v>
+        <v>0.5294371129990326</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.047571850891749</v>
+        <v>3.130039519572729</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.685091185837372</v>
+        <v>2.778951776697336</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.988519258843787</v>
+        <v>-3.98270121448674</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.089327057986109</v>
+        <v>1.185514866588892</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5484253166306737</v>
+        <v>0.5294371129990326</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.014146375815776</v>
+        <v>3.096614044496756</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.689658417829159</v>
+        <v>2.783519008689124</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.813044999051318</v>
+        <v>-3.807226954694271</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.164083993894885</v>
+        <v>1.260271802497668</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5484253166306737</v>
+        <v>0.5294371129990326</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.018713607807564</v>
+        <v>3.101181276488544</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.665400446590366</v>
+        <v>2.759261037450331</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.805120624466404</v>
+        <v>-3.799302580109357</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.142995772490058</v>
+        <v>1.239183581092841</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5484253166306737</v>
+        <v>0.5294371129990326</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.994455636568771</v>
+        <v>3.076923305249751</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.593938759991816</v>
+        <v>2.687799350851781</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.798842421896555</v>
+        <v>-3.793024377539508</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.074045366919447</v>
+        <v>1.17023317552223</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5547035192005227</v>
+        <v>0.5357153155688816</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.92676087151213</v>
+        <v>3.00922854019311</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.604111146423949</v>
+        <v>2.697971737283913</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.738989802692832</v>
+        <v>-3.733171758335784</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.108158801033069</v>
+        <v>1.204346609635852</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5547035192005227</v>
+        <v>0.5357153155688816</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.936933257944263</v>
+        <v>3.019400926625242</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.599057416997809</v>
+        <v>2.692918007857774</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.652746339666455</v>
+        <v>-3.646928295309407</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.13760245681748</v>
+        <v>1.233790265420263</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5547035192005227</v>
+        <v>0.5357153155688816</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.931879528518123</v>
+        <v>3.014347197199103</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.590833192442334</v>
+        <v>2.684693783302299</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.698053159065434</v>
+        <v>-3.692235114708387</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.111255504502414</v>
+        <v>1.207443313105196</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.513893356191292</v>
+        <v>0.4949051525596508</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.89916920615711</v>
+        <v>2.98163687483809</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.591385065475436</v>
+        <v>2.685245656335401</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.727086263767736</v>
+        <v>-3.721268219410689</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.100194135654594</v>
+        <v>1.196381944257377</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.513893356191292</v>
+        <v>0.4949051525596508</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.899721079190211</v>
+        <v>2.982188747871191</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.520657757366802</v>
+        <v>2.614518348226766</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.767568077616036</v>
+        <v>-3.628457737959829</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.01327410200664</v>
+        <v>1.162778828729087</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.473411542342992</v>
+        <v>0.5877156340105102</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.804704682772597</v>
+        <v>2.967147728633073</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.522531233291402</v>
+        <v>2.616391824151367</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.811957546945464</v>
+        <v>-3.672847207289257</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9973917901994698</v>
+        <v>1.146896516921917</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4290220730135643</v>
+        <v>0.5433261646810825</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.779944477099541</v>
+        <v>2.942387522960017</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.517606941803125</v>
+        <v>2.61146753266309</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.791453853059966</v>
+        <v>-3.65234351340376</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.000668976265392</v>
+        <v>1.150173702987838</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4495257668990617</v>
+        <v>0.5638298585665799</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.787322401942563</v>
+        <v>2.949765447803038</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.523098237633793</v>
+        <v>2.616958828493757</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.831377947642538</v>
+        <v>-3.692267607986332</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.99019063426303</v>
+        <v>1.139695360985477</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4495257668990617</v>
+        <v>0.5638298585665799</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.79281369777323</v>
+        <v>2.955256743633706</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.534595439402332</v>
+        <v>2.628456030262297</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.859158345543892</v>
+        <v>-3.720048005887685</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9905756768710279</v>
+        <v>1.140080403593475</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4217453689977086</v>
+        <v>0.5360494606652269</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.787642660800957</v>
+        <v>2.950085706661433</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.372951159402985</v>
+        <v>2.46681175026295</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.97753901827403</v>
+        <v>-3.838428678617823</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7815791277796258</v>
+        <v>0.9310838545020725</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3545275168467324</v>
+        <v>0.4688316085142507</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.585667669511025</v>
+        <v>2.7481107153715</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.493100820122191</v>
+        <v>2.586961410982155</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.086153096717361</v>
+        <v>-3.947042757061154</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8582831571214991</v>
+        <v>1.007787883843946</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3545275168467324</v>
+        <v>0.4688316085142507</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.70581733023023</v>
+        <v>2.868260376090706</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.507613846224514</v>
+        <v>2.601474437084478</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.050744058469218</v>
+        <v>-3.911633718813011</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8869597985230793</v>
+        <v>1.036464525245526</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3545275168467324</v>
+        <v>0.4688316085142507</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.720330356332553</v>
+        <v>2.882773402193029</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.505033287566882</v>
+        <v>2.598893878426847</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.059205227124679</v>
+        <v>-3.920094887468473</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8809947724032636</v>
+        <v>1.03049949912571</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3460663481912714</v>
+        <v>0.4603704398587896</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.712673096481645</v>
+        <v>2.875116142342121</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.501762316412185</v>
+        <v>2.59562290727215</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.882088897089512</v>
+        <v>-3.742978557433307</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9485703332626325</v>
+        <v>1.098075059985079</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3460663481912714</v>
+        <v>0.4603704398587896</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.709402125326948</v>
+        <v>2.871845171187424</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.502445708174098</v>
+        <v>2.596306299034063</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.927181141923058</v>
+        <v>-3.788070802266852</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9312168270911272</v>
+        <v>1.080721553813574</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.2841703050218816</v>
+        <v>0.3984743966893998</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.672947891187227</v>
+        <v>2.835390937047703</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.496232683480512</v>
+        <v>2.590093274340477</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.747805720684291</v>
+        <v>-3.608695381028085</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9967539708930486</v>
+        <v>1.146258697615495</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4409470631926002</v>
+        <v>0.5552511548601184</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.760800921396072</v>
+        <v>2.923243967256548</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.477040138812102</v>
+        <v>2.570900729672067</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.792819934204897</v>
+        <v>-3.653709594548691</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9595557408163959</v>
+        <v>1.109060467538842</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4105981678779956</v>
+        <v>0.5249022595455138</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.723399039538899</v>
+        <v>2.885842085399375</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.482731701151048</v>
+        <v>2.576592292011012</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.059824444477332</v>
+        <v>-3.920714104821126</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8584454990463675</v>
+        <v>1.007950225768814</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2162351298350471</v>
+        <v>0.3305392215025653</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.612472779052076</v>
+        <v>2.774915824912552</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.481935623047549</v>
+        <v>2.575796213907514</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.161022225914505</v>
+        <v>-4.021911886258299</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.817170308368</v>
+        <v>0.9666750350904463</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1478263162897279</v>
+        <v>0.2621304079572461</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.570631412821386</v>
+        <v>2.733074458681862</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.479535584601866</v>
+        <v>2.573396175461831</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.154511259300192</v>
+        <v>-4.015400919643986</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8173746565680418</v>
+        <v>0.9668793832904881</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1478263162897279</v>
+        <v>0.2621304079572461</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.568231374375703</v>
+        <v>2.730674420236178</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.476060303810111</v>
+        <v>2.569920894670076</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.135473131592895</v>
+        <v>-3.996362791936689</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8215146268592055</v>
+        <v>0.971019353581652</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.08964270495853333</v>
+        <v>0.2039467966260515</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.529845926785231</v>
+        <v>2.692288972645707</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.595354705444301</v>
+        <v>2.689215296304266</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.187988933867715</v>
+        <v>-4.04887859421151</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9198027075834676</v>
+        <v>1.069307434305914</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.08964270495853333</v>
+        <v>0.2039467966260515</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.649140328419421</v>
+        <v>2.811583374279897</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.596188034430435</v>
+        <v>2.690048625290399</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.191397245302295</v>
+        <v>-4.052286905646089</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9192727119957693</v>
+        <v>1.068777438718216</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1221592739679107</v>
+        <v>0.2364633656354289</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.669483598811182</v>
+        <v>2.831926644671657</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.602196564827361</v>
+        <v>2.696057155687325</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.172041109408448</v>
+        <v>-4.032930769752242</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9330236967502343</v>
+        <v>1.082528423472681</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1221592739679107</v>
+        <v>0.2364633656354289</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.675492129208108</v>
+        <v>2.837935175068583</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.50014678610456</v>
+        <v>2.594007376964525</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.024298139173445</v>
+        <v>-3.88518779951724</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.8900711061214348</v>
+        <v>1.039575832843881</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2899666312027939</v>
+        <v>0.4042707228703121</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.674126764826237</v>
+        <v>2.836569810686712</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.502940407636041</v>
+        <v>2.596800998496006</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.108119360448144</v>
+        <v>-3.969009020791938</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.8593362391430364</v>
+        <v>1.008840965865483</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2899666312027939</v>
+        <v>0.4042707228703121</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.676920386357718</v>
+        <v>2.839363432218193</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.503602756027699</v>
+        <v>2.597463346887664</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.101966654395359</v>
+        <v>-3.962856314739153</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.8624596699558085</v>
+        <v>1.011964396678255</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2961193372555782</v>
+        <v>0.4104234289230964</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.681274358381047</v>
+        <v>2.843717404241522</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.50268323276781</v>
+        <v>2.596543823627774</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.118775952545861</v>
+        <v>-3.979665612889655</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.854816427435718</v>
+        <v>1.004321154158164</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2793100391050765</v>
+        <v>0.3936141307725947</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.670269256230856</v>
+        <v>2.832712302091331</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.569018786564631</v>
+        <v>2.662879377424595</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.056477953769739</v>
+        <v>-3.917367614113533</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9460711807429878</v>
+        <v>1.095575907465434</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3246043033795186</v>
+        <v>0.4389083950470368</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.763781368592342</v>
+        <v>2.926224414452818</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.371310788278758</v>
+        <v>2.465171379138722</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.854687756104581</v>
+        <v>-3.715577416448375</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8290792615231779</v>
+        <v>0.9785839882456244</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5226224955486729</v>
+        <v>0.6369265872161911</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.684884285607962</v>
+        <v>2.847327331468438</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.441601020600933</v>
+        <v>2.535461611460898</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.905574468790776</v>
+        <v>-3.76646412913457</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8790148087708753</v>
+        <v>1.028519535493322</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.4717357828624784</v>
+        <v>0.5860398745299966</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.72464249031842</v>
+        <v>2.887085536178896</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.456228756716976</v>
+        <v>2.550089347576941</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.818963726140968</v>
+        <v>-3.679853386484762</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.928286841946842</v>
+        <v>1.077791568669288</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5503615140676366</v>
+        <v>0.6646656057351549</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.786445665157559</v>
+        <v>2.948888711018034</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.454764737541648</v>
+        <v>2.548625328401613</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.879173024146253</v>
+        <v>-3.740062684490047</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9027391035693997</v>
+        <v>1.052243830291846</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.490152216062352</v>
+        <v>0.6044563077298704</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.74885606717906</v>
+        <v>2.911299113039536</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.453256355581577</v>
+        <v>2.547116946441542</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.829986375461901</v>
+        <v>-3.690876035805696</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.920905381083069</v>
+        <v>1.070410107805515</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.490152216062352</v>
+        <v>0.6044563077298704</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.747347685218988</v>
+        <v>2.909790731079464</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.453119223017013</v>
+        <v>2.546979813876978</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.785613243823333</v>
+        <v>-3.646502904167127</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9385175011739326</v>
+        <v>1.088022227896379</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5345253477009206</v>
+        <v>0.648829439368439</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.773834431637566</v>
+        <v>2.936277477498041</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.447513017155603</v>
+        <v>2.541373608015568</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.750881922504832</v>
+        <v>-3.611771582848626</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9468038238399235</v>
+        <v>1.09630855056237</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5345253477009206</v>
+        <v>0.648829439368439</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.768228225776156</v>
+        <v>2.930671271636632</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.453894774183408</v>
+        <v>2.547755365043373</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.703226191943776</v>
+        <v>-3.56411585228757</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9722478730921502</v>
+        <v>1.121752599814597</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.5821810782619763</v>
+        <v>0.6964851699294946</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.803203421140594</v>
+        <v>2.96564646700107</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.458787147558133</v>
+        <v>2.552647738418098</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.602708033445022</v>
+        <v>-3.463597693788816</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.017347509866377</v>
+        <v>1.166852236588823</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.6826992367607309</v>
+        <v>0.7970033284282492</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.868406689614571</v>
+        <v>3.030849735475047</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.445541820034005</v>
+        <v>2.53940241089397</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.586802704012669</v>
+        <v>-3.447692364356463</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.01046431411519</v>
+        <v>1.159969040837637</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.603586576051492</v>
+        <v>0.7178906677190102</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.807693765664901</v>
+        <v>2.970136811525376</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.449639522644634</v>
+        <v>2.543500113504598</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.541964302404271</v>
+        <v>-3.402853962748065</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.032497377369178</v>
+        <v>1.182002104091624</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6081300089963615</v>
+        <v>0.7224341006638797</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.814517528042451</v>
+        <v>2.976960573902927</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.453800462275712</v>
+        <v>2.547661053135676</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.561462758646279</v>
+        <v>-3.422352418990073</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.028858934503453</v>
+        <v>1.178363661225899</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5600453677164572</v>
+        <v>0.6743494593839754</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.789827682905586</v>
+        <v>2.952270728766062</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.459680064803549</v>
+        <v>2.553540655663514</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.517259921560379</v>
+        <v>-3.378149581904173</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.05241967186565</v>
+        <v>1.201924398588097</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6042482048023576</v>
+        <v>0.7185522964698758</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.822228987684964</v>
+        <v>2.98467203354544</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.458090065272796</v>
+        <v>2.551950656132761</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.524819587397426</v>
+        <v>-3.38570924774122</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.047805806000079</v>
+        <v>1.197310532722525</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6590516088121769</v>
+        <v>0.7733557004796952</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.853521030560103</v>
+        <v>3.015964076420579</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.509337830455836</v>
+        <v>2.603198421315801</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.366528169858154</v>
+        <v>-3.227417830201948</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.162370138198827</v>
+        <v>1.311874864921274</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6590516088121769</v>
+        <v>0.7733557004796952</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.904768795743142</v>
+        <v>3.067211841603618</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.507778535050089</v>
+        <v>2.601639125910054</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.158886166223677</v>
+        <v>-3.019775826567471</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.243867644246871</v>
+        <v>1.393372370969317</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8666936124466531</v>
+        <v>0.9809977041141713</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.027794702518081</v>
+        <v>3.190237748378557</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475138</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.502726763288359</v>
+        <v>2.596587354148324</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.107854073501149</v>
+        <v>-2.968743733844943</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.259228709574152</v>
+        <v>1.408733436296599</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9177257051691811</v>
+        <v>1.032029796836699</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.053362186389868</v>
+        <v>3.215805232250344</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.519914167381064</v>
+        <v>2.613774758241029</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.042629892373943</v>
+        <v>-2.903519552717738</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.302505786117739</v>
+        <v>1.452010512840186</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9829498862963867</v>
+        <v>1.097253977963905</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.109684099158896</v>
+        <v>3.272127145019372</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.515875139680344</v>
+        <v>2.609735730540309</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.00520287230281</v>
+        <v>-2.866092532646604</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.313437566445473</v>
+        <v>1.46294229316792</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9882014243255683</v>
+        <v>1.102505515993087</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.108795994275686</v>
+        <v>3.271239040136162</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.517131932011585</v>
+        <v>2.61099252287155</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.003844887329264</v>
+        <v>-2.864734547673058</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.315237552766132</v>
+        <v>1.464742279488578</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.062539549863387</v>
+        <v>1.176843641530905</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.154655661929617</v>
+        <v>3.317098707790093</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.677689703032796</v>
+        <v>2.77155029389276</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.975431624229381</v>
+        <v>-2.836321284573175</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.487160629027296</v>
+        <v>1.636665355749743</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.003563987116958</v>
+        <v>1.117868078784477</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.279828095302971</v>
+        <v>3.442271141163447</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957621</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.797802612250613</v>
+        <v>2.891663203110578</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.900649363204368</v>
+        <v>-2.761539023548162</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.637186442655118</v>
+        <v>1.786691169377565</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.078346248141971</v>
+        <v>1.192650339809489</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.444810361135795</v>
+        <v>3.607253406996271</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.789510588264472</v>
+        <v>2.883371179124437</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.87456527894056</v>
+        <v>-2.735454939284354</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.6393280523745</v>
+        <v>1.788832779096947</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.078346248141971</v>
+        <v>1.192650339809489</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.436518337149654</v>
+        <v>3.59896138301013</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.787703783848251</v>
+        <v>2.881564374708216</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.78668736583144</v>
+        <v>-2.647577026175234</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.672672413201928</v>
+        <v>1.822177139924375</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.194271890565322</v>
+        <v>1.30857598223284</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.504266918187445</v>
+        <v>3.666709964047921</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.805258189575043</v>
+        <v>2.899118780435007</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.777794904438156</v>
+        <v>-2.746582921302173</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.693783803486033</v>
+        <v>1.80012918760039</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.194271890565322</v>
+        <v>1.30857598223284</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.521821323914236</v>
+        <v>3.684264369774712</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.797113236979627</v>
+        <v>2.890973827839591</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.946271021408034</v>
+        <v>-2.915059038272051</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.618248404102666</v>
+        <v>1.724593788217023</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.166324054848741</v>
+        <v>1.280628146516259</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.496907669888872</v>
+        <v>3.659350715749347</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.778382934167488</v>
+        <v>2.872243525027453</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.500014828778594</v>
+        <v>-2.468802845642611</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.778020578342304</v>
+        <v>1.884365962456661</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.071605385179109</v>
+        <v>1.185909476846627</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.421346165274953</v>
+        <v>3.583789211135429</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.769046956664393</v>
+        <v>2.862907547524358</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.477293725095442</v>
+        <v>-2.446081741959459</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.777773042312469</v>
+        <v>1.884118426426826</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.071605385179109</v>
+        <v>1.185909476846627</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.412010187771858</v>
+        <v>3.574453233632334</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777669</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.927953082515562</v>
+        <v>3.021813673375527</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.606495538389484</v>
+        <v>-2.575283555253501</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.884998442846021</v>
+        <v>1.991343826960378</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9424035718850663</v>
+        <v>1.056707663552584</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.493395225646602</v>
+        <v>3.655838271507078</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644408</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.965030905009209</v>
+        <v>3.058891495869173</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.63236993686351</v>
+        <v>-2.601157953727527</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.911726505950057</v>
+        <v>2.018071890064415</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9873151805968075</v>
+        <v>1.101619272264326</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.557420013367293</v>
+        <v>3.719863059227769</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.961706260998754</v>
+        <v>3.055566851858718</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.625315246648336</v>
+        <v>-2.594103263512353</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.911223738025672</v>
+        <v>2.017569122140029</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9943698708119812</v>
+        <v>1.108673962479499</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.558328183485943</v>
+        <v>3.720771229346418</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331113</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.971712414643495</v>
+        <v>3.06557300550346</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.598364022321848</v>
+        <v>-2.567152039185865</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.932010381401009</v>
+        <v>2.038355765515366</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.0092502168397</v>
+        <v>1.123554308507219</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.577262544747316</v>
+        <v>3.739705590607791</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.155815546788455</v>
+        <v>3.24967613764842</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.619908250152636</v>
+        <v>-2.588696267016652</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.107495822413654</v>
+        <v>2.213841206528011</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.0092502168397</v>
+        <v>1.123554308507219</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.761365676892276</v>
+        <v>3.923808722752751</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.147932241691448</v>
+        <v>3.241792832551413</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.642316367957508</v>
+        <v>-2.611104384821525</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.090649270194698</v>
+        <v>2.196994654309055</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.0092502168397</v>
+        <v>1.123554308507219</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.753482371795269</v>
+        <v>3.915925417655744</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.149986241241086</v>
+        <v>3.24384683210105</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.670540603535108</v>
+        <v>-2.639328620399125</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.081413575513295</v>
+        <v>2.187758959627653</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.027226969291009</v>
+        <v>1.141531060958527</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.766322422815691</v>
+        <v>3.928765468676167</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.206239958962933</v>
+        <v>3.300100549822897</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.81478134838132</v>
+        <v>-2.763884339370801</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.079970995296657</v>
+        <v>2.194190389760829</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.003040291047026</v>
+        <v>1.13017308275042</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.808064133591149</v>
+        <v>3.97820439947315</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.209131053508234</v>
+        <v>3.302991644368198</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.903657979549794</v>
+        <v>-2.852760970539275</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.047311437374569</v>
+        <v>2.16153083183874</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.9141636598785523</v>
+        <v>1.041296451581946</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.757629249435365</v>
+        <v>3.927769515317366</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.207242866402009</v>
+        <v>3.301103457261974</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.9799879571507</v>
+        <v>-2.929090948140181</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.014891259227982</v>
+        <v>2.129110653692153</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.9141636598785523</v>
+        <v>1.041296451581946</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.755741062329141</v>
+        <v>3.925881328211141</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.202063096004871</v>
+        <v>3.295923686864836</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.134944742550829</v>
+        <v>-3.08404773354031</v>
       </c>
       <c r="E2009" t="n">
-        <v>1.947728774670792</v>
+        <v>2.061948169134964</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7592068744784231</v>
+        <v>0.8863396661818166</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.657587220691925</v>
+        <v>3.827727486573926</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343062</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.200497106215023</v>
+        <v>3.294357697074988</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.296513168078084</v>
+        <v>-3.245616159067565</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.881535414670042</v>
+        <v>1.995754809134214</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.6324239506805437</v>
+        <v>0.7595567423839372</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.57995147662335</v>
+        <v>3.750091742505351</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.213570513080942</v>
+        <v>3.307431103940907</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.404813829948204</v>
+        <v>-3.353916820937685</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.851288556787913</v>
+        <v>1.965507951252085</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.6324239506805437</v>
+        <v>0.7595567423839372</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.593024883489269</v>
+        <v>3.763165149371269</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.205575709863882</v>
+        <v>3.299436300723847</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.422617801668948</v>
+        <v>-3.371720792658429</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.836172164882556</v>
+        <v>1.950391559346727</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.5618893277753425</v>
+        <v>0.689022119478736</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.542709306529088</v>
+        <v>3.712849572411089</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.204099750990884</v>
+        <v>3.297960341850849</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.450518588778421</v>
+        <v>-3.399621579767902</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.823535891165768</v>
+        <v>1.93775528562994</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.5272924036324077</v>
+        <v>0.6544251953358012</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.520475193170329</v>
+        <v>3.69061545905233</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.200864194968083</v>
+        <v>3.294724785828048</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.573044691481315</v>
+        <v>-3.522147682470796</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.77128989406181</v>
+        <v>1.885509288525981</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.4047663009295138</v>
+        <v>0.5318990926329074</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.443723975525791</v>
+        <v>3.613864241407792</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585935</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.267570154558586</v>
+        <v>3.361430745418551</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.803559187666903</v>
+        <v>-3.752662178656385</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.745790055178078</v>
+        <v>1.860009449642249</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.1742518047439251</v>
+        <v>0.3013845964473186</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.372121237404942</v>
+        <v>3.542261503286943</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.407881873560433</v>
+        <v>3.501742464420398</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.152304272891347</v>
+        <v>-4.101407263880828</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.746603740090148</v>
+        <v>1.860823134554319</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.0655038508250273</v>
+        <v>0.1926366425284208</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.44718418405545</v>
+        <v>3.617324449937451</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237096</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.476862142706073</v>
+        <v>3.570722733566038</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.306290690667487</v>
+        <v>-4.255393681656969</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.753989442125331</v>
+        <v>1.868208836589503</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.0655038508250273</v>
+        <v>0.1926366425284208</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.51616445320109</v>
+        <v>3.686304719083091</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423389</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.462913344826194</v>
+        <v>3.556773935686159</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.510890125530496</v>
+        <v>-4.459993116519978</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.658200870300248</v>
+        <v>1.77242026476442</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.0655038508250273</v>
+        <v>0.1926366425284208</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.502215655321211</v>
+        <v>3.672355921203212</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.474783833881608</v>
+        <v>3.568644424741573</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.76336527953822</v>
+        <v>-4.712468270527702</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.569081297752573</v>
+        <v>1.683300692216744</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.0655038508250273</v>
+        <v>0.1926366425284208</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.514086144376625</v>
+        <v>3.684226410258626</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.475994368400552</v>
+        <v>3.569854959260517</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.056261036017633</v>
+        <v>-5.005364027007114</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.453133529679751</v>
+        <v>1.567352924143923</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.0655038508250273</v>
+        <v>0.1926366425284208</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.515296678895568</v>
+        <v>3.685436944777569</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.480116110627873</v>
+        <v>3.573976701487838</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.242925164152441</v>
+        <v>-5.192028155141922</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.38258962065315</v>
+        <v>1.496809015117321</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.03876488000046741</v>
+        <v>0.1658976717038609</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.503375038628154</v>
+        <v>3.673515304510155</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.475193963364063</v>
+        <v>3.569054554224028</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.388945851066403</v>
+        <v>-5.338048842055884</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.319259198623755</v>
+        <v>1.433478593087926</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.02968178820661044</v>
+        <v>0.156814579910004</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.493003036288029</v>
+        <v>3.66314330217003</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830328</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.637398020063107</v>
+        <v>3.731258610923072</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.480659860175988</v>
+        <v>-5.429762851165469</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.444777651678964</v>
+        <v>1.558997046143136</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.02968178820661044</v>
+        <v>0.156814579910004</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.655207092987073</v>
+        <v>3.825347358869074</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69653946807155</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.632244658026921</v>
+        <v>3.726105248886886</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.512311519235958</v>
+        <v>-5.461414510225438</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.426963626018791</v>
+        <v>1.541183020482963</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.02451333096217023</v>
+        <v>0.1516461226655638</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.646952656604223</v>
+        <v>3.817092922486224</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.642474075595412</v>
+        <v>3.736334666455377</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.581377573808894</v>
+        <v>-5.530480564798375</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.409566621758107</v>
+        <v>1.523786016222279</v>
       </c>
       <c r="F2025" t="n">
-        <v>-0.0378575465314398</v>
+        <v>0.08927524517195373</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.619759547676549</v>
+        <v>3.78989981355855</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.651399714051315</v>
+        <v>3.745260304911279</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.683353696057302</v>
+        <v>-5.632456687046782</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.377701811314647</v>
+        <v>1.491921205778818</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.1398336687798474</v>
+        <v>-0.01270087707645384</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.567499512783407</v>
+        <v>3.737639778665407</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.64355260129549</v>
+        <v>3.737413192155455</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.57334741258008</v>
+        <v>-5.522450403569561</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.41385721194971</v>
+        <v>1.528076606413882</v>
       </c>
       <c r="F2027" t="n">
-        <v>-0.1166290968625722</v>
+        <v>0.01050369484082136</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.573575143177947</v>
+        <v>3.743715409059948</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.647802612017464</v>
+        <v>3.741663202877429</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.430287836839154</v>
+        <v>-5.379390827828635</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.475331052968055</v>
+        <v>1.589550447432227</v>
       </c>
       <c r="F2028" t="n">
-        <v>-0.1086156702725929</v>
+        <v>0.01851712143080064</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.582633209853909</v>
+        <v>3.75277347573591</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.6550634949</v>
+        <v>3.748924085759965</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.128841111367317</v>
+        <v>-5.077944102356797</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.603170626039326</v>
+        <v>1.717390020503498</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.1928310551992444</v>
+        <v>0.3199638469026379</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.770762128019547</v>
+        <v>3.940902393901548</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679624</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.656034672652711</v>
+        <v>3.749895263512676</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.153431355602501</v>
+        <v>-5.102534346591981</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.594305706097964</v>
+        <v>1.708525100562135</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.1928310551992444</v>
+        <v>0.3199638469026379</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.771733305772258</v>
+        <v>3.941873571654258</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.82118418247416</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.656877577032466</v>
+        <v>3.750738167892431</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.10239297959598</v>
+        <v>-5.051495970585461</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.615563960880327</v>
+        <v>1.729783355344499</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.1928310551992444</v>
+        <v>0.3199638469026379</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.772576210152013</v>
+        <v>3.942716476034014</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969543</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.675915675906612</v>
+        <v>3.769776266766577</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.061253684729349</v>
+        <v>-5.01035667571883</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.651057777701125</v>
+        <v>1.765277172165296</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.2339703500658752</v>
+        <v>0.3611031417692687</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.816297885946137</v>
+        <v>3.986438151828138</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.492099672030546</v>
+        <v>3.585960262890511</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.964618772710709</v>
+        <v>-4.91372176370019</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.505895738632515</v>
+        <v>1.620115133096687</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.3306052620845151</v>
+        <v>0.4577380537879087</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.690462829281256</v>
+        <v>3.860603095163257</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.495601716104511</v>
+        <v>3.589462306964475</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.895580761762242</v>
+        <v>-4.844683752751722</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.537012987085867</v>
+        <v>1.651232381550038</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3996432730329832</v>
+        <v>0.5267760647363767</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.735387679924301</v>
+        <v>3.905527945806301</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.480028535180593</v>
+        <v>3.573889126040558</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.73108442757128</v>
+        <v>-4.68018741856076</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.587238339838334</v>
+        <v>1.701457734302506</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5641396072239451</v>
+        <v>0.6912723989273386</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.818512299514961</v>
+        <v>3.988652565396961</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.479216245617023</v>
+        <v>3.573076836476988</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.653985826029407</v>
+        <v>-4.603088817018888</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.617265490891513</v>
+        <v>1.731484885355685</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5641396072239451</v>
+        <v>0.6912723989273386</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.81770000995139</v>
+        <v>3.987840275833391</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.489085024742095</v>
+        <v>3.58294561560206</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.664371020919297</v>
+        <v>-4.613474011908777</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.622980192060629</v>
+        <v>1.737199586524801</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5537544123340558</v>
+        <v>0.6808872040374493</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.821337672142529</v>
+        <v>3.99147793802453</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.55992203051852</v>
+        <v>3.653782621378485</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.682959179641522</v>
+        <v>-4.632062170631002</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.686381934348165</v>
+        <v>1.800601328812336</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5351662536118305</v>
+        <v>0.662299045315224</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.881021782685619</v>
+        <v>4.05116204856762</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496556</v>
+        <v>3.855120535496554</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.556791041336819</v>
+        <v>3.650651632196784</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.683257726337557</v>
+        <v>-4.632360717327038</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.683131526488049</v>
+        <v>1.79735092095222</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5348677069157945</v>
+        <v>0.6620004986191881</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.877711665486296</v>
+        <v>4.047851931368297</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.56132193627621</v>
+        <v>3.655182527136175</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.58243459264713</v>
+        <v>-4.53153758363661</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.727991674903611</v>
+        <v>1.842211069367783</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5473319224001484</v>
+        <v>0.6744647141035419</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.889721089716299</v>
+        <v>4.059861355598301</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.561451189754754</v>
+        <v>3.655311780614718</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.391653231894722</v>
+        <v>-4.340756222884202</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.804433472683117</v>
+        <v>1.918652867147289</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7381132831525558</v>
+        <v>0.8652460748559493</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.004319159646287</v>
+        <v>4.174459425528288</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.54128803549235</v>
+        <v>3.635148626352315</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.2846898740453</v>
+        <v>-4.233792865034781</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.827055661560483</v>
+        <v>1.941275056024654</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7965778911123572</v>
+        <v>0.9237106828157507</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.019234770159764</v>
+        <v>4.189375036041765</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.576254972104409</v>
+        <v>3.670115562964373</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.229359286143538</v>
+        <v>-4.178462277133018</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.884154833333246</v>
+        <v>1.998374227797418</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8519084790141194</v>
+        <v>0.9790412707175129</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.087400059512881</v>
+        <v>4.257540325394881</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.569941540005846</v>
+        <v>3.663802130865811</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.217305159230575</v>
+        <v>-4.166408150220056</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.882663051999869</v>
+        <v>1.996882446464041</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8639626059270822</v>
+        <v>0.9910953976304757</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.088319103562096</v>
+        <v>4.258459369444097</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.571822170189982</v>
+        <v>3.665682761049947</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.258460278798796</v>
+        <v>-4.207563269788277</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.868081634356717</v>
+        <v>1.982301028820888</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8228074863588613</v>
+        <v>0.9499402780622548</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.0655066620053</v>
+        <v>4.2356469278873</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.584673196067865</v>
+        <v>3.678533786927829</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.190411716107266</v>
+        <v>-4.139514707096747</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.908152085311211</v>
+        <v>2.022371479775383</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8908560490503911</v>
+        <v>1.017988840753785</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.119186825498099</v>
+        <v>4.2893270913801</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013425</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.604875866241459</v>
+        <v>3.698736457101424</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.422012109276767</v>
+        <v>-4.371115100266247</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.835714598217005</v>
+        <v>1.949933992681177</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8908560490503911</v>
+        <v>1.017988840753785</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.139389495671693</v>
+        <v>4.309529761553694</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.66674720149897</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.588482102308341</v>
+        <v>3.682342693168306</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.472063654805986</v>
+        <v>-4.421166645795466</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.799300216072199</v>
+        <v>1.913519610536371</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8908560490503911</v>
+        <v>1.017988840753785</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.122995731738576</v>
+        <v>4.293135997620577</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.548734015901807</v>
+        <v>3.642594606761772</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.64717048738243</v>
+        <v>-4.596273478371911</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.689509396635088</v>
+        <v>1.80372879109926</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8908560490503911</v>
+        <v>1.017988840753785</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.083247645332042</v>
+        <v>4.253387911214043</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.555756634898747</v>
+        <v>3.649617225758712</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.451070333951908</v>
+        <v>-4.400173324941388</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.774972077004237</v>
+        <v>1.889191471468409</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.086956202480914</v>
+        <v>1.214088994184308</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.207930356387296</v>
+        <v>4.378070622269297</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.654927634471652</v>
+        <v>3.748788225331617</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.298044941838623</v>
+        <v>-4.247147932828104</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.935353233422456</v>
+        <v>2.049572627886628</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.239981594594198</v>
+        <v>1.367114386297592</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.398916591228171</v>
+        <v>4.569056857110172</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.842393859379944</v>
+        <v>3.936254450239909</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.326352255711893</v>
+        <v>-4.275455246701374</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.11149653278144</v>
+        <v>2.225715927245612</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.239981594594198</v>
+        <v>1.367114386297592</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.586382816136464</v>
+        <v>4.756523082018465</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.811796810734027</v>
+        <v>3.905657401593992</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.492945480825416</v>
+        <v>-4.442048471814896</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.014262194090114</v>
+        <v>2.128481588554286</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.073388369480676</v>
+        <v>1.200521161184069</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.455829832422433</v>
+        <v>4.625970098304434</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.815473213395745</v>
+        <v>3.90933380425571</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.46990968746385</v>
+        <v>-4.41901267845333</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.027152914096458</v>
+        <v>2.14137230856063</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.073388369480676</v>
+        <v>1.200521161184069</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.459506235084151</v>
+        <v>4.629646500966151</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.74058140139947</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.81309126851924</v>
+        <v>3.906951859379205</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.440663707008153</v>
+        <v>-4.389766697997634</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.036469361402232</v>
+        <v>2.150688755866403</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.073388369480676</v>
+        <v>1.200521161184069</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.457124290207646</v>
+        <v>4.627264556089647</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256371</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.810384507676875</v>
+        <v>3.90424509853684</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.547589254886004</v>
+        <v>-4.496692245875485</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.990992381408726</v>
+        <v>2.105211775872898</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.9664628216028243</v>
+        <v>1.093595613306218</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.39026220063857</v>
+        <v>4.560402466520571</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701001</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.811813309820109</v>
+        <v>3.905673900680074</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.692607813393253</v>
+        <v>-4.641710804382734</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.934413760149061</v>
+        <v>2.048633154613233</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.8214442630955757</v>
+        <v>0.9485770547989694</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.304679867677455</v>
+        <v>4.474820133559456</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687013</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.911744549077862</v>
+        <v>4.005605139937827</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.81094957917797</v>
+        <v>-4.760052570167451</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.987008293092927</v>
+        <v>2.101227687557098</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.8321303016584658</v>
+        <v>0.9592630933618594</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.411022730072942</v>
+        <v>4.581162995954942</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790803</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.909530246203802</v>
+        <v>4.003390837063765</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.862360001498678</v>
+        <v>-4.811462992488159</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.964229821290583</v>
+        <v>2.078449215754754</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.8321303016584658</v>
+        <v>0.9592630933618594</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.408808427198881</v>
+        <v>4.578948693080881</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.909433374278091</v>
+        <v>4.003293965138055</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.94177945270643</v>
+        <v>-4.890882443695911</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.932365168881772</v>
+        <v>2.046584563345943</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.8321303016584658</v>
+        <v>0.9592630933618594</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.40871155527317</v>
+        <v>4.578851821155171</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298397</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.909427267836134</v>
+        <v>4.003287858696098</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.037242450623648</v>
+        <v>-4.986345441613128</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.894173863272927</v>
+        <v>2.008393257737099</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.8321303016584658</v>
+        <v>0.9592630933618594</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.408705448831213</v>
+        <v>4.578845714713214</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.907523664398744</v>
+        <v>4.001384255258709</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.972866539772933</v>
+        <v>-4.921969530762413</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.918020624175824</v>
+        <v>2.032240018639996</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.8965062125091809</v>
+        <v>1.023639004212574</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.445427391904254</v>
+        <v>4.615567657786254</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353535</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.913257482146471</v>
+        <v>4.007118073006436</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.028235701905126</v>
+        <v>-4.977338692894607</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.901606777070673</v>
+        <v>2.015826171534845</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.8965062125091809</v>
+        <v>1.023639004212574</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.45116120965198</v>
+        <v>4.621301475533981</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.912795845489403</v>
+        <v>4.006656436349369</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.046454168902735</v>
+        <v>-4.995557159892216</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.893857753614562</v>
+        <v>2.008077148078734</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.8713997752533388</v>
+        <v>0.9985325669567322</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.435635710641407</v>
+        <v>4.605775976523408</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113687</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.932670238339722</v>
+        <v>4.026530829199688</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.958247334755157</v>
+        <v>-4.907350325744638</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.949014880123912</v>
+        <v>2.063234274588085</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.8713997752533388</v>
+        <v>0.9985325669567322</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.455510103491726</v>
+        <v>4.625650369373727</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.91637093886445</v>
+        <v>4.010231529724416</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.852212339549848</v>
+        <v>-4.801315330539328</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.975129578730764</v>
+        <v>2.089348973194936</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.8713997752533388</v>
+        <v>0.9985325669567322</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.439210804016454</v>
+        <v>4.609351069898455</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.918801888328495</v>
+        <v>4.012662479188461</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.669000676416752</v>
+        <v>-4.618103667406233</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.050845193448047</v>
+        <v>2.16506458791222</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.8713997752533388</v>
+        <v>0.9985325669567322</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.441641753480499</v>
+        <v>4.611782019362501</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.884593074176385</v>
+        <v>3.97845366503635</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.597279229402901</v>
+        <v>-4.546382220392382</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.045324958101477</v>
+        <v>2.15954435256565</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.9431212222671894</v>
+        <v>1.070254013970583</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.450465807536699</v>
+        <v>4.6206060734187</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.831508820097557</v>
+        <v>3.925369410957522</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.574906203795195</v>
+        <v>-4.524009194784676</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.001189914265732</v>
+        <v>2.115409308729904</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.954376973380091</v>
+        <v>1.081509765083484</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.404135004125612</v>
+        <v>4.574275270007613</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456731</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.016707024982912</v>
+        <v>4.110567615842878</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.60792249970594</v>
+        <v>-4.557025490695421</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.173181600786789</v>
+        <v>2.287400995250962</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.8849395967133393</v>
+        <v>1.012072388416733</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.547670783010916</v>
+        <v>4.717811048892917</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883677</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.008628250811161</v>
+        <v>4.102488841671127</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.596394864056331</v>
+        <v>-4.545497855045812</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.169713880874881</v>
+        <v>2.283933275339054</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.9439402549147018</v>
+        <v>1.071073046618095</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.574992403759983</v>
+        <v>4.745132669641984</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236297</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.01229636333295</v>
+        <v>4.106156954192915</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.6937363653987</v>
+        <v>-4.642839356388181</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.134445392859722</v>
+        <v>2.248664787323895</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.8995200727492134</v>
+        <v>1.026652864452607</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.552008406982478</v>
+        <v>4.722148672864479</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427684</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.013547445525788</v>
+        <v>4.107408036385753</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.779592394738667</v>
+        <v>-4.728695385728147</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.101354063316574</v>
+        <v>2.215573457780747</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.8571440035230784</v>
+        <v>0.9842767952264717</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.527833847639635</v>
+        <v>4.697974113521637</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.99596664734629</v>
+        <v>4.089827238206255</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.788429192154786</v>
+        <v>-4.737532183144267</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.080238546170628</v>
+        <v>2.194457940634801</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.8497018308817277</v>
+        <v>0.976834622585121</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.505787745875327</v>
+        <v>4.675928011757328</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667455</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.006131158391339</v>
+        <v>4.099991749251305</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.879811754720245</v>
+        <v>-4.828914745709725</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.053850032189494</v>
+        <v>2.168069426653667</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.813136946162383</v>
+        <v>0.9402697378657763</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.494013326088769</v>
+        <v>4.664153591970771</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889191</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.108259416215606</v>
+        <v>4.202120007075573</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.868105036733239</v>
+        <v>-4.817208027722719</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.160660977208564</v>
+        <v>2.274880371672737</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.8248436641493894</v>
+        <v>0.9519764558527827</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.60316561470524</v>
+        <v>4.773305880587243</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409566</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.111291754947011</v>
+        <v>4.205152345806978</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.939017110475517</v>
+        <v>-4.888120101464997</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.135328486443057</v>
+        <v>2.249547880907231</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.8248436641493894</v>
+        <v>0.9519764558527827</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.606197953436645</v>
+        <v>4.776338219318648</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.324196588225069</v>
+        <v>4.418057179085036</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.949333208641868</v>
+        <v>-4.898436199631349</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.344106880454575</v>
+        <v>2.458326274918748</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.8248436641493894</v>
+        <v>0.9519764558527827</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.819102786714703</v>
+        <v>4.989243052596706</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762286</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.323375255137159</v>
+        <v>4.417235845997125</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.949239240624496</v>
+        <v>-4.898342231613976</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.343323134573613</v>
+        <v>2.457542529037787</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.8252135254967073</v>
+        <v>0.9523463172001007</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.818503370435184</v>
+        <v>4.988643636317186</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988017</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.317607241081513</v>
+        <v>4.411467831941479</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.097605468280641</v>
+        <v>-5.046708459270121</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.278208629455509</v>
+        <v>2.392428023919683</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.8252135254967073</v>
+        <v>0.9523463172001007</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.812735356379537</v>
+        <v>4.98287562226154</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740923</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.317607241081513</v>
+        <v>4.411467831941479</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.096657045162602</v>
+        <v>-5.045760036152083</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.278587998702724</v>
+        <v>2.392807393166898</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.8252135254967073</v>
+        <v>0.9523463172001007</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.812735356379537</v>
+        <v>4.98287562226154</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663627</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.330334849062605</v>
+        <v>4.424195439922571</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.196926863121623</v>
+        <v>-5.146029854111104</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.251207679500208</v>
+        <v>2.365427073964382</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.8252135254967073</v>
+        <v>0.9523463172001007</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.825462964360629</v>
+        <v>4.995603230242632</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424771</v>
+        <v>3.71707115842477</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.332280847486992</v>
+        <v>4.426141438346959</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.285192496045648</v>
+        <v>-5.140037607322292</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.217847424754986</v>
+        <v>2.369769971104294</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.8252135254967073</v>
+        <v>0.9523463172001007</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.827408962785017</v>
+        <v>4.99754922866702</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149219</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.325934983504761</v>
+        <v>4.419795574364728</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.19663453491488</v>
+        <v>-5.051479646191525</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.246924745225062</v>
+        <v>2.39884729157437</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.8252135254967073</v>
+        <v>0.9523463172001007</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.821063098802786</v>
+        <v>4.991203364684789</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.325243660943757</v>
+        <v>4.419104251803724</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.178875457411806</v>
+        <v>-5.033720568688451</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.253337053665287</v>
+        <v>2.405259600014595</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.8252135254967073</v>
+        <v>0.9523463172001007</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.820371776241782</v>
+        <v>4.990512042123784</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720999</v>
+        <v>3.778232147720996</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.338025846852344</v>
+        <v>4.43188643771231</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.079245306362738</v>
+        <v>-4.934090417639383</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.305971299993501</v>
+        <v>2.457893846342809</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.9248436765457748</v>
+        <v>1.051976468249168</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.892932052779809</v>
+        <v>5.063072318661812</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455273</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.52718011235107</v>
+        <v>4.621040703211037</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.128644815051749</v>
+        <v>-4.983489926328394</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.475365762016623</v>
+        <v>2.627288308365931</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.9351025099775195</v>
+        <v>1.062235301680913</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.088241618337582</v>
+        <v>5.258381884219585</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963134</v>
+        <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.514368785453932</v>
+        <v>4.608229376313899</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.921960341409374</v>
+        <v>-4.776805452686018</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.545228224576435</v>
+        <v>2.697150770925743</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.141786983619895</v>
+        <v>1.268919775323289</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.19944097562587</v>
+        <v>5.369581241507873</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162544</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.516370299108037</v>
+        <v>4.610230889968004</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.9561172364069</v>
+        <v>-4.810962347683544</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.53356698023153</v>
+        <v>2.685489526580838</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.058203214079083</v>
+        <v>1.185336005782476</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.151292227555487</v>
+        <v>5.32143249343749</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652384</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.869867413097705</v>
+        <v>4.963728003957671</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.863527757345444</v>
+        <v>-4.718372868622088</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.92409988584578</v>
+        <v>3.076022432195088</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.058203214079083</v>
+        <v>1.185336005782476</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.504789341545155</v>
+        <v>5.674929607427157</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108672</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.874430524664808</v>
+        <v>4.968291115524774</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.923416385168994</v>
+        <v>-4.778261496445638</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.904707546283463</v>
+        <v>3.056630092632771</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.044081299391618</v>
+        <v>1.171214091095012</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.500879304299779</v>
+        <v>5.671019570181782</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103563</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>4.924260465988335</v>
+        <v>5.018121056848302</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.871200075372652</v>
+        <v>-4.726045186649296</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.975424011525527</v>
+        <v>3.127346557874835</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.044081299391618</v>
+        <v>1.171214091095012</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.550709245623306</v>
+        <v>5.720849511505309</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047745</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>4.933074436198346</v>
+        <v>5.026935027058313</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.839302558287407</v>
+        <v>-4.69414766956405</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.996996988569636</v>
+        <v>3.148919534918945</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.075978816476864</v>
+        <v>1.203111608180257</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.578661726084465</v>
+        <v>5.748801991966467</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650754</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>4.928712020237543</v>
+        <v>5.02257261109751</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.854057882487547</v>
+        <v>-4.708902993764191</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.986732442928777</v>
+        <v>3.138654989278085</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.075978816476864</v>
+        <v>1.203111608180257</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.574299310123662</v>
+        <v>5.744439576005664</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135749</v>
+        <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.919636523653823</v>
+        <v>5.01349711451379</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.804593259117635</v>
+        <v>-4.659438370394279</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.997442795693022</v>
+        <v>3.14936534204233</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.125443439846775</v>
+        <v>1.252576231550169</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.594902587561888</v>
+        <v>5.765042853443891</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479222</v>
+        <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
-        <v>4.916044191368758</v>
+        <v>5.009904782228724</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.64148526696402</v>
+        <v>-4.496330378240664</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.059093660269403</v>
+        <v>3.21101620661871</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.288551432000391</v>
+        <v>1.415684223703784</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.689175050568992</v>
+        <v>5.859315316450995</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844247</v>
+        <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
-        <v>4.925091228059886</v>
+        <v>5.018951818919852</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.508677641466853</v>
+        <v>-4.363522752743497</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.121263747159397</v>
+        <v>3.273186293508705</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.288551432000391</v>
+        <v>1.415684223703784</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.69822208726012</v>
+        <v>5.868362353142123</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790955</v>
+        <v>3.832425987790952</v>
       </c>
       <c r="C2098" t="n">
-        <v>4.925948693046007</v>
+        <v>5.019809283905974</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.571385557941412</v>
+        <v>-4.179862536414437</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.097038045555696</v>
+        <v>3.347507845026451</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.225843515525833</v>
+        <v>1.599344440032844</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.661454802361507</v>
+        <v>5.979415947925681</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.566968654133285</v>
+        <v>3.803639579680029</v>
       </c>
       <c r="C2099" t="n">
-        <v>4.875155990723531</v>
+        <v>5.018816867454944</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.571385557941412</v>
+        <v>-4.176262764434139</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.097038045555696</v>
+        <v>3.347955337367541</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.225843515525833</v>
+        <v>1.57759795162533</v>
       </c>
       <c r="G2099" t="n">
-        <v>4.868219787709899</v>
+        <v>5.965375638430142</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240926.xlsx
+++ b/tame_output/ON/bt/strategyON_20240926.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>190.3%</t>
+          <t>180.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-607.5%</t>
+          <t>-605.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-71.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.3%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.8%</t>
+          <t>422.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-579.2%</t>
+          <t>-595.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-234.0%</t>
+          <t>-242.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>333.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-41.4%</t>
+          <t>-57.4%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-298.7%</t>
+          <t>-320.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-68.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>137.8%</t>
+          <t>133.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-132.5%</t>
+          <t>-141.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>126.4%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>150.5%</t>
+          <t>139.5%</t>
         </is>
       </c>
     </row>
@@ -43868,19 +43868,19 @@
         <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
-        <v>3.249949287655787</v>
+        <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
         <v>0.2448339544207899</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.347526445110355</v>
+        <v>3.253665854250391</v>
       </c>
       <c r="F1840" t="n">
         <v>1.763217066107158</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.307879527320082</v>
+        <v>4.214018936460117</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
-        <v>3.228695669279524</v>
+        <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
         <v>-0.01236008028726682</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.22339521285087</v>
+        <v>3.129534621990905</v>
       </c>
       <c r="F1841" t="n">
         <v>1.506023031399101</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.132309488118985</v>
+        <v>4.03844889725902</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
-        <v>3.229713278409994</v>
+        <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
         <v>-0.07812747033667888</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.198105865961575</v>
+        <v>3.104245275101611</v>
       </c>
       <c r="F1842" t="n">
         <v>1.506023031399101</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.133327097249454</v>
+        <v>4.03946650638949</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
-        <v>3.22034131039775</v>
+        <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
         <v>-0.3104983844983536</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.095785532284661</v>
+        <v>3.001924941424697</v>
       </c>
       <c r="F1843" t="n">
         <v>1.506023031399101</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.12395512923721</v>
+        <v>4.030094538377246</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
-        <v>3.210424036352988</v>
+        <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
         <v>-0.3922702849261053</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.053159498068799</v>
+        <v>2.959298907208834</v>
       </c>
       <c r="F1844" t="n">
         <v>1.533058604805237</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.13025919923613</v>
+        <v>4.036398608376166</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296833</v>
       </c>
       <c r="C1845" t="n">
-        <v>3.21518935318669</v>
+        <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6545912063460799</v>
+        <v>-0.6384895974748048</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.952996446334511</v>
+        <v>2.865576499023057</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.135024516069833</v>
+        <v>4.041163925209869</v>
       </c>
     </row>
     <row r="1846">
@@ -44006,19 +44006,19 @@
         <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
-        <v>3.213014149305931</v>
+        <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6432019696912785</v>
+        <v>-0.6271003608200034</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.955376937115672</v>
+        <v>2.867956989804218</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.139682854181954</v>
+        <v>4.045822263321989</v>
       </c>
     </row>
     <row r="1847">
@@ -44029,19 +44029,19 @@
         <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
-        <v>3.210941040810994</v>
+        <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8956798641106845</v>
+        <v>-0.8795782552394094</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.852312670852973</v>
+        <v>2.764892723541518</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.986123009035373</v>
+        <v>3.89226241817541</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
-        <v>3.210807257409916</v>
+        <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.185811530716116</v>
+        <v>-1.169709921844841</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.736126220809722</v>
+        <v>2.648706273498267</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.000438302478403</v>
+        <v>3.906577711618439</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
-        <v>3.215699401963841</v>
+        <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.393815589069193</v>
+        <v>-1.377713980197918</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.657816742022416</v>
+        <v>2.570396794710962</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.005330447032328</v>
+        <v>3.911469856172364</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
-        <v>3.210780858301829</v>
+        <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.439892391358888</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.628026833896016</v>
+        <v>2.540606886584562</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.963104856673735</v>
+        <v>3.86924426581377</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
-        <v>3.203865157608278</v>
+        <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-1.805961118503541</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.474683642344604</v>
+        <v>2.38726369503315</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.736547919693392</v>
+        <v>3.642687328833428</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
-        <v>3.224203447347046</v>
+        <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-2.014451899955225</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.411625619502699</v>
+        <v>2.324205672191245</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.63179174056115</v>
+        <v>3.537931149701186</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
-        <v>3.232302197755615</v>
+        <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.261653084720447</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.320843896005179</v>
+        <v>2.233423948693724</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.651982503069006</v>
+        <v>3.558121912209042</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
-        <v>3.233408589799347</v>
+        <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.754038112744544</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.124996276839273</v>
+        <v>2.037576329527818</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.35765787829828</v>
+        <v>3.263797287438316</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
-        <v>3.231951128612211</v>
+        <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.02844348929949</v>
+        <v>-3.012341880428214</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.020217308578667</v>
+        <v>1.932797361267212</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.356200417111144</v>
+        <v>3.262339826251179</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
-        <v>3.233720252066827</v>
+        <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.278314169314071</v>
+        <v>-3.262212560442796</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.922038160027451</v>
+        <v>1.834618212715996</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.379727172464038</v>
+        <v>3.285866581604073</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
-        <v>3.229826310723085</v>
+        <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.484825946201093</v>
+        <v>-3.468724337329818</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.8355395079289</v>
+        <v>1.748119560617445</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.251926164988083</v>
+        <v>3.158065574128118</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
-        <v>3.231599237423344</v>
+        <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.804170021281594</v>
+        <v>-3.788068412410319</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.709574804596959</v>
+        <v>1.622154857285504</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.253699091688342</v>
+        <v>3.159838500828378</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
-        <v>3.217932124890749</v>
+        <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.190379852557369</v>
+        <v>-4.174278243686095</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.541423759554053</v>
+        <v>1.454003812242599</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.185568215325281</v>
+        <v>3.091707624465316</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
-        <v>3.206216899892839</v>
+        <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.458931643255243</v>
+        <v>-4.442830034383968</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.422287818276995</v>
+        <v>1.33486787096554</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.1179447876207835</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.13545002732037</v>
+        <v>3.041589436460405</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
-        <v>3.204797491548804</v>
+        <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.794594290485695</v>
+        <v>-4.778492681614421</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.286603351040779</v>
+        <v>1.199183403729324</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.1858757731096883</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.093272027682992</v>
+        <v>2.999411436823027</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
-        <v>3.211285051783046</v>
+        <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.871038620688567</v>
+        <v>-4.854937011817293</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.262513179193872</v>
+        <v>1.175093231882417</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.1054302640160264</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.148026893373431</v>
+        <v>3.054166302513466</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
-        <v>3.210539566788877</v>
+        <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.236166003327313</v>
+        <v>-5.220064394456039</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.115716741144205</v>
+        <v>1.02829679383275</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.4017410483150389</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.969494937799854</v>
+        <v>2.87563434693989</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.209301110803636</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.644754780507992</v>
+        <v>-5.628653171636717</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.9510427742866918</v>
+        <v>0.8636228269752375</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.723103215506206</v>
+        <v>2.629242624646241</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.204486543275097</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.758515192530857</v>
+        <v>-5.742413583659582</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.9007240419490068</v>
+        <v>0.813304094637552</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.718288647977667</v>
+        <v>2.624428057117702</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.202480593883974</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.174907066817855</v>
+        <v>-6.158805457946579</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.7321613428430851</v>
+        <v>0.6447413955316303</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.716282698586544</v>
+        <v>2.622422107726579</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.212739284552653</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.536080696634842</v>
+        <v>-6.519979087763567</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5979505815849686</v>
+        <v>0.5105306342735143</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.726541389255223</v>
+        <v>2.632680798395258</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.208838849698349</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.879339216277861</v>
+        <v>-6.863237607406586</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.4567467388734565</v>
+        <v>0.3693267915620022</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.722640954400918</v>
+        <v>2.628780363540954</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.20724376975335</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.927542033520205</v>
+        <v>-6.91144042464893</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.4358705320315197</v>
+        <v>0.3484505847200654</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.8103298254957174</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.721045874455919</v>
+        <v>2.627185283595955</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.211022745682558</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.094350693494567</v>
+        <v>-7.078249084623292</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.3729260439709834</v>
+        <v>0.2855060966595286</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.852613149208854</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.699454856157246</v>
+        <v>2.605594265297281</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.206996441148155</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.28107040180387</v>
+        <v>-7.264968792932595</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.294211856112859</v>
+        <v>0.2067919088014047</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.852613149208854</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.695428551622843</v>
+        <v>2.601567960762878</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.206894339826571</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.664071790546501</v>
+        <v>-7.647970181675226</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.1409091992942226</v>
+        <v>0.05348925198276788</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.852613149208854</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.695326450301259</v>
+        <v>2.601465859441294</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.209465855798001</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.66855823574789</v>
+        <v>-7.652456626876615</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.141686137185097</v>
+        <v>0.05426618987364273</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.8570995944102426</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.695206099151855</v>
+        <v>2.601345508291891</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.214816159096051</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.028088558251891</v>
+        <v>-8.011986949380617</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.003224311481546227</v>
+        <v>-0.08419563582990808</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.8570995944102426</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.700556402449906</v>
+        <v>2.606695811589941</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.222732179053228</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.078437621706113</v>
+        <v>-8.062336012834839</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.008999293942964837</v>
+        <v>-0.09641924125441959</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.9074486578644647</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.67826298433455</v>
+        <v>2.584402393474585</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.225773929674997</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.176056899127509</v>
+        <v>-8.159955290256235</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.04500525428975477</v>
+        <v>-0.1324252016012091</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.005067935285861</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.622733168503481</v>
+        <v>2.528872577643516</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.228667485996569</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230128398635868</v>
+        <v>-8.214026789764594</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.06374029777152579</v>
+        <v>-0.1511602450829801</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.059139434794221</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.593183825120037</v>
+        <v>2.499323234260073</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.234180683115212</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.233704184727616</v>
+        <v>-8.217602575856342</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.05965741508958278</v>
+        <v>-0.1470773624010371</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.084668356710713</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.583379669088784</v>
+        <v>2.489519078228819</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.238663237599648</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.267357023236089</v>
+        <v>-8.251255414364815</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.06863599600853609</v>
+        <v>-0.1560559433199904</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.185081724627751</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.527614202822998</v>
+        <v>2.433753611963033</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.254034939093069</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.406443137854946</v>
+        <v>-8.390341528983672</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1088987403626578</v>
+        <v>-0.1963186876741121</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.324167839246607</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.459534235545105</v>
+        <v>2.36567364468514</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.268590159840586</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.58156755524149</v>
+        <v>-8.565465946370216</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1643932865697582</v>
+        <v>-0.2518132338812125</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.499292256633151</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.369014805860695</v>
+        <v>2.275154215000731</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.26137099493899</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.816019649255979</v>
+        <v>-8.799918040384705</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2653932890771502</v>
+        <v>-0.3528132363886045</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.499292256633151</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.361795640959099</v>
+        <v>2.267935050099135</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.254698804165014</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.982559630026746</v>
+        <v>-8.904292771411152</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3386814721594327</v>
+        <v>-0.4012353195731593</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.665832237403918</v>
+        <v>-1.603666987659597</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.255199461722663</v>
+        <v>2.198638020709291</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.25581459400357</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.146847776944615</v>
+        <v>-9.066806237109736</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.403280941088024</v>
+        <v>-0.4651249160140365</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.790046597030577</v>
+        <v>-1.701300418078284</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.181786635785224</v>
+        <v>2.141173752296635</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.258508322632685</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.272884570312904</v>
+        <v>-9.192843030478025</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.4510019298062251</v>
+        <v>-0.5128459047322376</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.764794974220835</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.199631338100184</v>
+        <v>2.159018454611595</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.262498658319085</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.215812798416973</v>
+        <v>-9.135771258582094</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.4241828853614518</v>
+        <v>-0.4860268602874647</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.764794974220835</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.203621673786585</v>
+        <v>2.163008790297996</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.261023431420344</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.357484640141093</v>
+        <v>-9.277443100306215</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4823268489498416</v>
+        <v>-0.5441708238758545</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.764794974220835</v>
+        <v>-1.676048795268541</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.202146446887843</v>
+        <v>2.161533563399254</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940721</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.276076841585216</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.307893795716259</v>
+        <v>-9.22785225588138</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.4474371010150358</v>
+        <v>-0.5092810759410482</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.715204129796001</v>
+        <v>-1.626457950843708</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.246954363707616</v>
+        <v>2.206341480219027</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.263025707938533</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.158975461244403</v>
+        <v>-9.078933921409524</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4009209008729759</v>
+        <v>-0.4627648757989888</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.683954539060828</v>
+        <v>-1.595208360108535</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.252652984502037</v>
+        <v>2.212040101013448</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.272604780974742</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.933130308524992</v>
+        <v>-8.853088768690114</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3010037667490035</v>
+        <v>-0.362847741675016</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.642027863473664</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.287388062890543</v>
+        <v>2.246775179401955</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.273743925530801</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.808551652187401</v>
+        <v>-8.728510112352522</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.250033159657908</v>
+        <v>-0.3118771345839204</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.642027863473664</v>
+        <v>-1.553281684521371</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.288527207446602</v>
+        <v>2.247914323958013</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.276377699692908</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.78351497061889</v>
+        <v>-8.703473430784012</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.2373847128683959</v>
+        <v>-0.2992286877944088</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.616698775922929</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.306358434139151</v>
+        <v>2.265745550650562</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.282111403931545</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.711381795331009</v>
+        <v>-8.631340255496131</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.2027977385146071</v>
+        <v>-0.2646417134406196</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.616698775922929</v>
+        <v>-1.527952596970635</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.312092138377788</v>
+        <v>2.271479254889199</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.272374141537679</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.640015402721362</v>
+        <v>-8.559973862886483</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.1839884438646133</v>
+        <v>-0.2458324187906262</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.545332383313281</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.345174711549712</v>
+        <v>2.304561828061122</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232414</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.262490660224772</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.546556368736137</v>
+        <v>-8.466514828901259</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.156488311583431</v>
+        <v>-0.2183322865094439</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.545332383313281</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.335291230236804</v>
+        <v>2.294678346748215</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.76631707943623</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.260656099725398</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.535903187182706</v>
+        <v>-8.455861647347827</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1540615994614325</v>
+        <v>-0.215905574387445</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.545332383313281</v>
+        <v>-1.456586204360987</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.33345666973743</v>
+        <v>2.292843786248842</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.260355784751937</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.437996148506215</v>
+        <v>-8.357954608671337</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1151990989642968</v>
+        <v>-0.1770430738903097</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.477346633452724</v>
+        <v>-1.388600454500431</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.373947804680303</v>
+        <v>2.333334921191714</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.261024290897431</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.414042607530257</v>
+        <v>-8.334001067695379</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1049491764284203</v>
+        <v>-0.1667931513544327</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.453393092476767</v>
+        <v>-1.364646913524473</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.388988435411371</v>
+        <v>2.348375551922782</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.247763974735679</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.149982669207461</v>
+        <v>-8.069941129372582</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.01258551726105361</v>
+        <v>-0.07442949218706607</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.18933315415397</v>
+        <v>-1.100586975201677</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.534164082243297</v>
+        <v>2.493551198754708</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.244976941075378</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.442903045702622</v>
+        <v>-7.362861505867744</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2674592984805808</v>
+        <v>0.2056153235545684</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.18933315415397</v>
+        <v>-1.100586975201677</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.531377048582996</v>
+        <v>2.490764165094407</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.245320564963219</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.402718747336432</v>
+        <v>-7.322677207501553</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2838766417148983</v>
+        <v>0.2220326667888859</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.14914885578778</v>
+        <v>-1.060402676835486</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.555831251490552</v>
+        <v>2.515218368001963</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.244687386183976</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.23931887639707</v>
+        <v>-7.159277336562191</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3486034113114003</v>
+        <v>0.2867594363853878</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9857489848484171</v>
+        <v>-0.8970028058961237</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.653237995274926</v>
+        <v>2.612625111786337</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.252611815021829</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.081201497018294</v>
+        <v>-7.001159957183416</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4197747919007631</v>
+        <v>0.3579308169747502</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8276316054696417</v>
+        <v>-0.7388854265173482</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.756032851740044</v>
+        <v>2.715419968251455</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.249719604708869</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.931535106010779</v>
+        <v>-6.8514935661759</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4767491379908098</v>
+        <v>0.4149051630647973</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7347281142271057</v>
+        <v>-0.6459819352748123</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.808882736172606</v>
+        <v>2.768269852684018</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.150980390716024</v>
+        <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.799259632379893</v>
+        <v>-6.719218092545014</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4309201134503189</v>
+        <v>0.3690761385243064</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6024526405962191</v>
+        <v>-0.5137064616439256</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.789508806358293</v>
+        <v>2.748895922869704</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105955</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.153795451403661</v>
+        <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.62739841681499</v>
+        <v>-6.547356876980111</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5024796603639166</v>
+        <v>0.4406356854379041</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4305914250313162</v>
+        <v>-0.3418452460790228</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.895440596384872</v>
+        <v>2.854827712896283</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.16670179262732</v>
+        <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.542433750085671</v>
+        <v>-6.462392210250792</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.549371868279303</v>
+        <v>0.4875278933532905</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.3456267583019966</v>
+        <v>-0.2568805793497032</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.959325737646122</v>
+        <v>2.918712854157533</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038725863028101</v>
+        <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.648023739858775</v>
+        <v>-6.567982200023897</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3791599427708428</v>
+        <v>0.3173159678448298</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.451216748075101</v>
+        <v>-0.3624705691228076</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.767995814183041</v>
+        <v>2.727382930694452</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087270204905187</v>
+        <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.579789155233348</v>
+        <v>-6.499747615398469</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4549981184981</v>
+        <v>0.3931541435720876</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.432801425202565</v>
+        <v>-0.3440552462502716</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.827589349783648</v>
+        <v>2.78697646629506</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.97064939626678</v>
+        <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.431849113825749</v>
+        <v>-6.35180757399087</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3975533264227327</v>
+        <v>0.3357093514967202</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.4124805092940074</v>
+        <v>-0.323734330341714</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.723161090690376</v>
+        <v>2.682548207201787</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.961935410013302</v>
+        <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.37887959157176</v>
+        <v>-6.298838051736881</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4100271490708498</v>
+        <v>0.3481831741448373</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.3595109870400185</v>
+        <v>-0.2707648080877251</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.746228817789291</v>
+        <v>2.705615934300702</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.954974797918209</v>
+        <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.213091395611469</v>
+        <v>-6.133049855776591</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4693818153598732</v>
+        <v>0.4075378404338603</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.3595109870400185</v>
+        <v>-0.2707648080877251</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.739268205694198</v>
+        <v>2.698655322205609</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.969437152299352</v>
+        <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.1797281891327</v>
+        <v>-6.099686649297822</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4971894523325235</v>
+        <v>0.4353454774065111</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.3595109870400185</v>
+        <v>-0.2707648080877251</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.753730560075341</v>
+        <v>2.713117676586752</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.963969272758547</v>
+        <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.071469052010179</v>
+        <v>-5.9914275121753</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5350252276407272</v>
+        <v>0.4731812527147148</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.3595109870400185</v>
+        <v>-0.2707648080877251</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.748262680534536</v>
+        <v>2.707649797045947</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.961467366769124</v>
+        <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.948177917193048</v>
+        <v>-5.868136377358169</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5818397755781568</v>
+        <v>0.5199958006521439</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.236219852222888</v>
+        <v>-0.1474736732705946</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.819735455435391</v>
+        <v>2.779122571946802</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.969168345006449</v>
+        <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.895481050061757</v>
+        <v>-5.815439510226878</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6106195006679984</v>
+        <v>0.5487755257419855</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.1835229850915969</v>
+        <v>-0.09477680613930345</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.859054553951491</v>
+        <v>2.818441670462903</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.9649490533535</v>
+        <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.651715608078312</v>
+        <v>-5.571674068243434</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7039063858084269</v>
+        <v>0.642062410882414</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.1835229850915969</v>
+        <v>-0.09477680613930345</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.854835262298542</v>
+        <v>2.814222378809953</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057528</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.967073367273516</v>
+        <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.56193993570184</v>
+        <v>-5.481898395866962</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7419409686790317</v>
+        <v>0.6800969937530188</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.1219235401772868</v>
+        <v>-0.03317736122499343</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.893919243167144</v>
+        <v>2.853306359678555</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.959815442257218</v>
+        <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.312089541752766</v>
+        <v>-5.232048001917887</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8346232012423638</v>
+        <v>0.7727792263163509</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.1219235401772868</v>
+        <v>-0.03317736122499343</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.886661318150846</v>
+        <v>2.846048434662257</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.963414565777867</v>
+        <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.136197449285334</v>
+        <v>-5.056155909450455</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.908579161749985</v>
+        <v>0.8467351868239725</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.1219235401772868</v>
+        <v>-0.03317736122499343</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.890260441671495</v>
+        <v>2.849647558182906</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.97674207183242</v>
+        <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.96475098626287</v>
+        <v>-4.884709446427991</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9904852530135242</v>
+        <v>0.9286412780875115</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.04952292284517629</v>
+        <v>0.1382691017974697</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.006455825539526</v>
+        <v>2.965842942050938</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.975762549448717</v>
+        <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.884728699153749</v>
+        <v>-4.80468715931887</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.02151464547347</v>
+        <v>0.9596706705474569</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.1295452099542972</v>
+        <v>0.2182913889065907</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.053489675421296</v>
+        <v>3.012876791932707</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.980457350503035</v>
+        <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.821092956919815</v>
+        <v>-4.741051417084936</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.051663743421361</v>
+        <v>0.989819768495348</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.1931809521882318</v>
+        <v>0.2819271311405252</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.096365921815974</v>
+        <v>3.055753038327385</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074784</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.96165160928683</v>
+        <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.72739563870342</v>
+        <v>-4.647354098868541</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.070336929491714</v>
+        <v>1.008492954565702</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.1931809521882318</v>
+        <v>0.2819271311405252</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.077560180599769</v>
+        <v>3.036947297111181</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.963394685911708</v>
+        <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.737898261768708</v>
+        <v>-4.65785672193383</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.067878956890476</v>
+        <v>1.006034981964464</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1826783291229429</v>
+        <v>0.2714245080752363</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.073001683385474</v>
+        <v>3.032388799896885</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.967323999746528</v>
+        <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.625412001099834</v>
+        <v>-4.545370461264955</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.116802774992846</v>
+        <v>1.054958800066834</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1826783291229429</v>
+        <v>0.2714245080752363</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.076930997220294</v>
+        <v>3.036318113731705</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.968002583663868</v>
+        <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.607698314221969</v>
+        <v>-4.52765677438709</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.124566833661332</v>
+        <v>1.06272285873532</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1858596580198597</v>
+        <v>0.2746058369721531</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.079518378475784</v>
+        <v>3.038905494987195</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502335</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.965000654883861</v>
+        <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.48422404290895</v>
+        <v>-4.404182503074072</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.170954613406533</v>
+        <v>1.10911063848052</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1858596580198597</v>
+        <v>0.2746058369721531</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.076516449695777</v>
+        <v>3.035903566207188</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.966579691894475</v>
+        <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.26420324487194</v>
+        <v>-4.184161705037061</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.260541969631952</v>
+        <v>1.198697994705939</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.32707950308784</v>
+        <v>0.4158256820401334</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.16282739374718</v>
+        <v>3.122214510258591</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.982473874696299</v>
+        <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.131335555808662</v>
+        <v>-4.051294015973784</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.329583228059086</v>
+        <v>1.267739253133073</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.32707950308784</v>
+        <v>0.4158256820401334</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.178721576549003</v>
+        <v>3.138108693060414</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.983619719136601</v>
+        <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.011162472444163</v>
+        <v>-3.931120932609285</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.378798305845187</v>
+        <v>1.316954330919174</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4472525864523389</v>
+        <v>0.5359987654046323</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.251971271008004</v>
+        <v>3.211358387519415</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.99370782169804</v>
+        <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.875909111114186</v>
+        <v>-3.795867571279308</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.442987752938618</v>
+        <v>1.381143778012605</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.582505947782316</v>
+        <v>0.6712521267346094</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.34321139036743</v>
+        <v>3.302598506878842</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.979745313099466</v>
+        <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.935783938471879</v>
+        <v>-3.855742398637</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.405075313396967</v>
+        <v>1.343231338470954</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5226311204246239</v>
+        <v>0.6113772993769173</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.293323985354241</v>
+        <v>3.252711101865652</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.995034482333675</v>
+        <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.815963707561041</v>
+        <v>-3.735922167726163</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.46829257499551</v>
+        <v>1.406448600069498</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5226311204246239</v>
+        <v>0.6113772993769173</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.308613154588449</v>
+        <v>3.268000271099861</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430695</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.902678681656116</v>
+        <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.818433414022847</v>
+        <v>-3.738391874187969</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.374948891733229</v>
+        <v>1.313104916807217</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5201614139628177</v>
+        <v>0.6089075929151111</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.214775530033807</v>
+        <v>3.174162646545219</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.821940543141418</v>
+        <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.886803600346857</v>
+        <v>-3.806762060511979</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.266862678688927</v>
+        <v>1.205018703762914</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5294371129990326</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.139602810940838</v>
+        <v>3.098989927452249</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.812377251773309</v>
+        <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.998675879973008</v>
+        <v>-3.918634340138129</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.212550475470358</v>
+        <v>1.150706500544345</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5294371129990326</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.130039519572729</v>
+        <v>3.08942663608414</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.778951776697336</v>
+        <v>2.685091185837372</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.98270121448674</v>
+        <v>-3.902659674651861</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.185514866588892</v>
+        <v>1.12367089166288</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5294371129990326</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.096614044496756</v>
+        <v>3.056001161008167</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205897</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.783519008689124</v>
+        <v>2.689658417829159</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.807226954694271</v>
+        <v>-3.727185414859392</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.260271802497668</v>
+        <v>1.198427827571655</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5294371129990326</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.101181276488544</v>
+        <v>3.060568392999955</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.759261037450331</v>
+        <v>2.665400446590366</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.799302580109357</v>
+        <v>-3.719261040274478</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.239183581092841</v>
+        <v>1.177339606166828</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5294371129990326</v>
+        <v>0.618183291951326</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.076923305249751</v>
+        <v>3.036310421761162</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.687799350851781</v>
+        <v>2.593938759991816</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.793024377539508</v>
+        <v>-3.712982837704629</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.17023317552223</v>
+        <v>1.108389200596217</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5357153155688816</v>
+        <v>0.6244614945211751</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.00922854019311</v>
+        <v>2.968615656704522</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.697971737283913</v>
+        <v>2.604111146423949</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.733171758335784</v>
+        <v>-3.653130218500906</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.204346609635852</v>
+        <v>1.142502634709839</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5357153155688816</v>
+        <v>0.6244614945211751</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.019400926625242</v>
+        <v>2.978788043136654</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.692918007857774</v>
+        <v>2.599057416997809</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.646928295309407</v>
+        <v>-3.566886755474528</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.233790265420263</v>
+        <v>1.17194629049425</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5357153155688816</v>
+        <v>0.6244614945211751</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.014347197199103</v>
+        <v>2.973734313710514</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.684693783302299</v>
+        <v>2.590833192442334</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.692235114708387</v>
+        <v>-3.612193574873508</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.207443313105196</v>
+        <v>1.145599338179184</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4949051525596508</v>
+        <v>0.5836513315119443</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.98163687483809</v>
+        <v>2.941023991349501</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.685245656335401</v>
+        <v>2.591385065475436</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.721268219410689</v>
+        <v>-3.64122667957581</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.196381944257377</v>
+        <v>1.134537969331365</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4949051525596508</v>
+        <v>0.5836513315119443</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.982188747871191</v>
+        <v>2.941575864382603</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.614518348226766</v>
+        <v>2.520657757366802</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.628457737959829</v>
+        <v>-3.548416198124951</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.162778828729087</v>
+        <v>1.100934853803074</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5877156340105102</v>
+        <v>0.6764618129628036</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.967147728633073</v>
+        <v>2.926534845144484</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.616391824151367</v>
+        <v>2.522531233291402</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.672847207289257</v>
+        <v>-3.592805667454378</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.146896516921917</v>
+        <v>1.085052541995904</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5433261646810825</v>
+        <v>0.6320723436333759</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.942387522960017</v>
+        <v>2.901774639471428</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.61146753266309</v>
+        <v>2.517606941803125</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.65234351340376</v>
+        <v>-3.572301973568881</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.150173702987838</v>
+        <v>1.088329728061826</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5638298585665799</v>
+        <v>0.6525760375188733</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.949765447803038</v>
+        <v>2.90915256431445</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798538</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.616958828493757</v>
+        <v>2.523098237633793</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.692267607986332</v>
+        <v>-3.612226068151453</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.139695360985477</v>
+        <v>1.077851386059464</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5638298585665799</v>
+        <v>0.6525760375188733</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.955256743633706</v>
+        <v>2.914643860145117</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.628456030262297</v>
+        <v>2.534595439402332</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.720048005887685</v>
+        <v>-3.640006466052806</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.140080403593475</v>
+        <v>1.078236428667462</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5360494606652269</v>
+        <v>0.6247956396175203</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.950085706661433</v>
+        <v>2.909472823172844</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.46681175026295</v>
+        <v>2.372951159402985</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.838428678617823</v>
+        <v>-3.758387138782945</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9310838545020725</v>
+        <v>0.8692398795760599</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4688316085142507</v>
+        <v>0.5575777874665441</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.7481107153715</v>
+        <v>2.707497831882912</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.586961410982155</v>
+        <v>2.493100820122191</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.947042757061154</v>
+        <v>-3.867001217226276</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.007787883843946</v>
+        <v>0.9459439089179331</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4688316085142507</v>
+        <v>0.5575777874665441</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.868260376090706</v>
+        <v>2.827647492602118</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.601474437084478</v>
+        <v>2.507613846224514</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.911633718813011</v>
+        <v>-3.831592178978133</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.036464525245526</v>
+        <v>0.9746205503195133</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4688316085142507</v>
+        <v>0.5575777874665441</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.882773402193029</v>
+        <v>2.842160518704441</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.598893878426847</v>
+        <v>2.505033287566882</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.920094887468473</v>
+        <v>-3.840053347633594</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.03049949912571</v>
+        <v>0.9686555241996975</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4603704398587896</v>
+        <v>0.549116618811083</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.875116142342121</v>
+        <v>2.834503258853533</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.59562290727215</v>
+        <v>2.501762316412185</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.742978557433307</v>
+        <v>-3.662937017598428</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.098075059985079</v>
+        <v>1.036231085059066</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4603704398587896</v>
+        <v>0.549116618811083</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.871845171187424</v>
+        <v>2.831232287698835</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.596306299034063</v>
+        <v>2.502445708174098</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.788070802266852</v>
+        <v>-3.708029262431974</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.080721553813574</v>
+        <v>1.018877578887561</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3984743966893998</v>
+        <v>0.4872205756416932</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.835390937047703</v>
+        <v>2.794778053559114</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.590093274340477</v>
+        <v>2.496232683480512</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.608695381028085</v>
+        <v>-3.528653841193206</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.146258697615495</v>
+        <v>1.084414722689482</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5552511548601184</v>
+        <v>0.6439973338124119</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.923243967256548</v>
+        <v>2.88263108376796</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.570900729672067</v>
+        <v>2.477040138812102</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.653709594548691</v>
+        <v>-3.573668054713812</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.109060467538842</v>
+        <v>1.04721649261283</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5249022595455138</v>
+        <v>0.6136484384978073</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.885842085399375</v>
+        <v>2.845229201910787</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.576592292011012</v>
+        <v>2.482731701151048</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.920714104821126</v>
+        <v>-3.840672564986248</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.007950225768814</v>
+        <v>0.9461062508428013</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3305392215025653</v>
+        <v>0.4192854004548587</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.774915824912552</v>
+        <v>2.734302941423963</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.575796213907514</v>
+        <v>2.481935623047549</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.021911886258299</v>
+        <v>-3.94187034642342</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9666750350904463</v>
+        <v>0.9048310601644336</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2621304079572461</v>
+        <v>0.3508765869095395</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.733074458681862</v>
+        <v>2.692461575193273</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.573396175461831</v>
+        <v>2.479535584601866</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.015400919643986</v>
+        <v>-3.935359379809108</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9668793832904881</v>
+        <v>0.9050354083644754</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2621304079572461</v>
+        <v>0.3508765869095395</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.730674420236178</v>
+        <v>2.69006153674759</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.569920894670076</v>
+        <v>2.476060303810111</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.996362791936689</v>
+        <v>-3.91632125210181</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.971019353581652</v>
+        <v>0.9091753786556394</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2039467966260515</v>
+        <v>0.2926929755783449</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.692288972645707</v>
+        <v>2.651676089157118</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.689215296304266</v>
+        <v>2.595354705444301</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.04887859421151</v>
+        <v>-3.96883705437663</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.069307434305914</v>
+        <v>1.007463459379902</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2039467966260515</v>
+        <v>0.2926929755783449</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.811583374279897</v>
+        <v>2.770970490791308</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.690048625290399</v>
+        <v>2.596188034430435</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.052286905646089</v>
+        <v>-3.97224536581121</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.068777438718216</v>
+        <v>1.006933463792203</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2364633656354289</v>
+        <v>0.3252095445877223</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.831926644671657</v>
+        <v>2.791313761183068</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.696057155687325</v>
+        <v>2.602196564827361</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.032930769752242</v>
+        <v>-3.952889229917363</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.082528423472681</v>
+        <v>1.020684448546668</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2364633656354289</v>
+        <v>0.3252095445877223</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.837935175068583</v>
+        <v>2.797322291579994</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.594007376964525</v>
+        <v>2.50014678610456</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.88518779951724</v>
+        <v>-3.805146259682361</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.039575832843881</v>
+        <v>0.9777318579178684</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4042707228703121</v>
+        <v>0.4930169018226055</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.836569810686712</v>
+        <v>2.795956927198123</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.596800998496006</v>
+        <v>2.502940407636041</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.969009020791938</v>
+        <v>-3.888967480957059</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.008840965865483</v>
+        <v>0.9469969909394702</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4042707228703121</v>
+        <v>0.4930169018226055</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.839363432218193</v>
+        <v>2.798750548729604</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.597463346887664</v>
+        <v>2.503602756027699</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.962856314739153</v>
+        <v>-3.882814774904275</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.011964396678255</v>
+        <v>0.9501204217522423</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4104234289230964</v>
+        <v>0.4991696078753898</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.843717404241522</v>
+        <v>2.803104520752933</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.596543823627774</v>
+        <v>2.50268323276781</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.979665612889655</v>
+        <v>-3.899624073054776</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.004321154158164</v>
+        <v>0.942477179232152</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3936141307725947</v>
+        <v>0.4823603097248881</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.832712302091331</v>
+        <v>2.792099418602743</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.662879377424595</v>
+        <v>2.569018786564631</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.917367614113533</v>
+        <v>-3.837326074278654</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.095575907465434</v>
+        <v>1.033731932539422</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4389083950470368</v>
+        <v>0.5276545739993301</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.926224414452818</v>
+        <v>2.885611530964229</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.465171379138722</v>
+        <v>2.371310788278758</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.715577416448375</v>
+        <v>-3.635535876613496</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9785839882456244</v>
+        <v>0.9167400133196117</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6369265872161911</v>
+        <v>0.7256727661684845</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.847327331468438</v>
+        <v>2.806714447979849</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.535461611460898</v>
+        <v>2.441601020600933</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.76646412913457</v>
+        <v>-3.686422589299691</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.028519535493322</v>
+        <v>0.9666755605673092</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5860398745299966</v>
+        <v>0.67478605348229</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.887085536178896</v>
+        <v>2.846472652690307</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.550089347576941</v>
+        <v>2.456228756716976</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.679853386484762</v>
+        <v>-3.599811846649884</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.077791568669288</v>
+        <v>1.015947593743276</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6646656057351549</v>
+        <v>0.7534117846874483</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.948888711018034</v>
+        <v>2.908275827529446</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.548625328401613</v>
+        <v>2.454764737541648</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.740062684490047</v>
+        <v>-3.660021144655168</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.052243830291846</v>
+        <v>0.9903998553658335</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6044563077298704</v>
+        <v>0.6932024866821638</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.911299113039536</v>
+        <v>2.870686229550947</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.547116946441542</v>
+        <v>2.453256355581577</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.690876035805696</v>
+        <v>-3.610834495970817</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.070410107805515</v>
+        <v>1.008566132879503</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6044563077298704</v>
+        <v>0.6932024866821638</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.909790731079464</v>
+        <v>2.869177847590875</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.546979813876978</v>
+        <v>2.453119223017013</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.646502904167127</v>
+        <v>-3.566461364332248</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.088022227896379</v>
+        <v>1.026178252970366</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.648829439368439</v>
+        <v>0.7375756183207324</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.936277477498041</v>
+        <v>2.895664594009453</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.541373608015568</v>
+        <v>2.447513017155603</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.611771582848626</v>
+        <v>-3.531730043013747</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.09630855056237</v>
+        <v>1.034464575636357</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.648829439368439</v>
+        <v>0.7375756183207324</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.930671271636632</v>
+        <v>2.890058388148043</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.547755365043373</v>
+        <v>2.453894774183408</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.56411585228757</v>
+        <v>-3.484074312452692</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.121752599814597</v>
+        <v>1.059908624888584</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6964851699294946</v>
+        <v>0.785231348881788</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.96564646700107</v>
+        <v>2.925033583512481</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.552647738418098</v>
+        <v>2.458787147558133</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.463597693788816</v>
+        <v>-3.383556153953937</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.166852236588823</v>
+        <v>1.105008261662811</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7970033284282492</v>
+        <v>0.8857495073805426</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.030849735475047</v>
+        <v>2.990236851986459</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.53940241089397</v>
+        <v>2.445541820034005</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.447692364356463</v>
+        <v>-3.367650824521585</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.159969040837637</v>
+        <v>1.098125065911624</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7178906677190102</v>
+        <v>0.8066368466713036</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.970136811525376</v>
+        <v>2.929523928036788</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.543500113504598</v>
+        <v>2.449639522644634</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.402853962748065</v>
+        <v>-3.322812422913187</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.182002104091624</v>
+        <v>1.120158129165612</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7224341006638797</v>
+        <v>0.8111802796161731</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.976960573902927</v>
+        <v>2.936347690414338</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.547661053135676</v>
+        <v>2.453800462275712</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.422352418990073</v>
+        <v>-3.342310879155195</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.178363661225899</v>
+        <v>1.116519686299887</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6743494593839754</v>
+        <v>0.7630956383362688</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.952270728766062</v>
+        <v>2.911657845277473</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.553540655663514</v>
+        <v>2.459680064803549</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.378149581904173</v>
+        <v>-3.298108042069294</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.201924398588097</v>
+        <v>1.140080423662084</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7185522964698758</v>
+        <v>0.8072984754221693</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.98467203354544</v>
+        <v>2.944059150056851</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.551950656132761</v>
+        <v>2.458090065272796</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.38570924774122</v>
+        <v>-3.305667707906341</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.197310532722525</v>
+        <v>1.135466557796513</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7733557004796952</v>
+        <v>0.8621018794319886</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.015964076420579</v>
+        <v>2.97535119293199</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.603198421315801</v>
+        <v>2.509337830455836</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.227417830201948</v>
+        <v>-3.147376290367069</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.311874864921274</v>
+        <v>1.250030889995261</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7733557004796952</v>
+        <v>0.8621018794319886</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.067211841603618</v>
+        <v>3.026598958115029</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.601639125910054</v>
+        <v>2.507778535050089</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.019775826567471</v>
+        <v>-2.939734286732593</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.393372370969317</v>
+        <v>1.331528396043305</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9809977041141713</v>
+        <v>1.069743883066465</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.190237748378557</v>
+        <v>3.149624864889968</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.596587354148324</v>
+        <v>2.502726763288359</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.968743733844943</v>
+        <v>-2.888702194010065</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.408733436296599</v>
+        <v>1.346889461370586</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.032029796836699</v>
+        <v>1.120775975788993</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.215805232250344</v>
+        <v>3.175192348761755</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.613774758241029</v>
+        <v>2.519914167381064</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.903519552717738</v>
+        <v>-2.823478012882859</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.452010512840186</v>
+        <v>1.390166537914173</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.097253977963905</v>
+        <v>1.186000156916198</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.272127145019372</v>
+        <v>3.231514261530783</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.609735730540309</v>
+        <v>2.515875139680344</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.866092532646604</v>
+        <v>-2.786050992811725</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.46294229316792</v>
+        <v>1.401098318241907</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.102505515993087</v>
+        <v>1.19125169494538</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.271239040136162</v>
+        <v>3.230626156647573</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.61099252287155</v>
+        <v>2.517131932011585</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.864734547673058</v>
+        <v>-2.78469300783818</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.464742279488578</v>
+        <v>1.402898304562566</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.176843641530905</v>
+        <v>1.265589820483199</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.317098707790093</v>
+        <v>3.276485824301504</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.77155029389276</v>
+        <v>2.677689703032796</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.836321284573175</v>
+        <v>-2.756279744738296</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.636665355749743</v>
+        <v>1.57482138082373</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.117868078784477</v>
+        <v>1.20661425773677</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.442271141163447</v>
+        <v>3.401658257674858</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957621</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.891663203110578</v>
+        <v>2.797802612250613</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.761539023548162</v>
+        <v>-2.681497483713283</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.786691169377565</v>
+        <v>1.724847194451552</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.192650339809489</v>
+        <v>1.281396518761783</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.607253406996271</v>
+        <v>3.566640523507683</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.883371179124437</v>
+        <v>2.789510588264472</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.735454939284354</v>
+        <v>-2.655413399449476</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.788832779096947</v>
+        <v>1.726988804170934</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.192650339809489</v>
+        <v>1.281396518761783</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.59896138301013</v>
+        <v>3.558348499521542</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.881564374708216</v>
+        <v>2.787703783848251</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.647577026175234</v>
+        <v>-2.567535486340355</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.822177139924375</v>
+        <v>1.760333164998362</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.30857598223284</v>
+        <v>1.397322161185134</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.666709964047921</v>
+        <v>3.626097080559332</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.899118780435007</v>
+        <v>2.805258189575043</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.746582921302173</v>
+        <v>-2.558643024947072</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.80012918760039</v>
+        <v>1.781444555282466</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.30857598223284</v>
+        <v>1.397322161185134</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.684264369774712</v>
+        <v>3.643651486286123</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.890973827839591</v>
+        <v>2.797113236979627</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.915059038272051</v>
+        <v>-2.72711914191695</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.724593788217023</v>
+        <v>1.705909155899099</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.280628146516259</v>
+        <v>1.369374325468553</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.659350715749347</v>
+        <v>3.618737832260758</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.872243525027453</v>
+        <v>2.778382934167488</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.468802845642611</v>
+        <v>-2.28086294928751</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.884365962456661</v>
+        <v>1.865681330138737</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.185909476846627</v>
+        <v>1.27465565579892</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.583789211135429</v>
+        <v>3.543176327646841</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.862907547524358</v>
+        <v>2.769046956664393</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.446081741959459</v>
+        <v>-2.258141845604357</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.884118426426826</v>
+        <v>1.865433794108903</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.185909476846627</v>
+        <v>1.27465565579892</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.574453233632334</v>
+        <v>3.533840350143745</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777669</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.021813673375527</v>
+        <v>2.927953082515562</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.575283555253501</v>
+        <v>-2.3873436588984</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.991343826960378</v>
+        <v>1.972659194642455</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.056707663552584</v>
+        <v>1.145453842504878</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.655838271507078</v>
+        <v>3.615225388018489</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644408</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>3.058891495869173</v>
+        <v>2.965030905009209</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.601157953727527</v>
+        <v>-2.413218057372426</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.018071890064415</v>
+        <v>1.999387257746491</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.101619272264326</v>
+        <v>1.190365451216619</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.719863059227769</v>
+        <v>3.67925017573918</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>3.055566851858718</v>
+        <v>2.961706260998754</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.594103263512353</v>
+        <v>-2.406163367157252</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.017569122140029</v>
+        <v>1.998884489822106</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.108673962479499</v>
+        <v>1.197420141431793</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.720771229346418</v>
+        <v>3.68015834585783</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331113</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
-        <v>3.06557300550346</v>
+        <v>2.971712414643495</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.567152039185865</v>
+        <v>-2.379212142830764</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.038355765515366</v>
+        <v>2.019671133197442</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.123554308507219</v>
+        <v>1.212300487459512</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.739705590607791</v>
+        <v>3.699092707119203</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.24967613764842</v>
+        <v>3.155815546788455</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.588696267016652</v>
+        <v>-2.400756370661551</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.213841206528011</v>
+        <v>2.195156574210087</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.123554308507219</v>
+        <v>1.212300487459512</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.923808722752751</v>
+        <v>3.883195839264162</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.241792832551413</v>
+        <v>3.147932241691448</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.611104384821525</v>
+        <v>-2.423164488466423</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.196994654309055</v>
+        <v>2.178310021991132</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.123554308507219</v>
+        <v>1.212300487459512</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.915925417655744</v>
+        <v>3.875312534167155</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155028</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.24384683210105</v>
+        <v>3.149986241241086</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.639328620399125</v>
+        <v>-2.451388724044024</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.187758959627653</v>
+        <v>2.169074327309729</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.141531060958527</v>
+        <v>1.230277239910821</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.928765468676167</v>
+        <v>3.888152585187578</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.300100549822897</v>
+        <v>3.206239958962933</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.763884339370801</v>
+        <v>-2.460829649932553</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.194190389760829</v>
+        <v>2.221551674676164</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.13017308275042</v>
+        <v>1.352704357454212</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.97820439947315</v>
+        <v>4.01786257343546</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.302991644368198</v>
+        <v>3.209131053508234</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.852760970539275</v>
+        <v>-2.549706281101027</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.16153083183874</v>
+        <v>2.188892116754075</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.041296451581946</v>
+        <v>1.263827726285738</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.927769515317366</v>
+        <v>3.967427689279677</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.301103457261974</v>
+        <v>3.207242866402009</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.929090948140181</v>
+        <v>-2.626036258701933</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.129110653692153</v>
+        <v>2.156471938607488</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.041296451581946</v>
+        <v>1.263827726285738</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.925881328211141</v>
+        <v>3.965539502173452</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.295923686864836</v>
+        <v>3.202063096004871</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.08404773354031</v>
+        <v>-2.780993044102062</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.061948169134964</v>
+        <v>2.089309454050299</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8863396661818166</v>
+        <v>1.108870940885609</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.827727486573926</v>
+        <v>3.867385660536237</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343062</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.294357697074988</v>
+        <v>3.200497106215023</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.245616159067565</v>
+        <v>-2.942561469629318</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.995754809134214</v>
+        <v>2.023116094049549</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7595567423839372</v>
+        <v>0.9820880170877296</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.750091742505351</v>
+        <v>3.789749916467661</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.307431103940907</v>
+        <v>3.213570513080942</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.353916820937685</v>
+        <v>-3.050862131499437</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.965507951252085</v>
+        <v>1.99286923616742</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7595567423839372</v>
+        <v>0.9820880170877296</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.763165149371269</v>
+        <v>3.80282332333358</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.299436300723847</v>
+        <v>3.205575709863882</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.371720792658429</v>
+        <v>-3.068666103220181</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.950391559346727</v>
+        <v>1.977752844262062</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.689022119478736</v>
+        <v>0.9115533941825285</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.712849572411089</v>
+        <v>3.752507746373399</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.297960341850849</v>
+        <v>3.204099750990884</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.399621579767902</v>
+        <v>-3.096566890329654</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.93775528562994</v>
+        <v>1.965116570545275</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6544251953358012</v>
+        <v>0.8769564700395936</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.69061545905233</v>
+        <v>3.73027363301464</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.294724785828048</v>
+        <v>3.200864194968083</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.522147682470796</v>
+        <v>-3.219092993032548</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.885509288525981</v>
+        <v>1.912870573441316</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5318990926329074</v>
+        <v>0.7544303673366998</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.613864241407792</v>
+        <v>3.653522415370103</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585935</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.361430745418551</v>
+        <v>3.267570154558586</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.752662178656385</v>
+        <v>-3.449607489218137</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.860009449642249</v>
+        <v>1.887370734557585</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3013845964473186</v>
+        <v>0.523915871151111</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.542261503286943</v>
+        <v>3.581919677249253</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814667</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.501742464420398</v>
+        <v>3.407881873560433</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.101407263880828</v>
+        <v>-3.79835257444258</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.860823134554319</v>
+        <v>1.888184419469654</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1926366425284208</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.617324449937451</v>
+        <v>3.656982623899762</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237096</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.570722733566038</v>
+        <v>3.476862142706073</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.255393681656969</v>
+        <v>-3.952338992218721</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.868208836589503</v>
+        <v>1.895570121504838</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1926366425284208</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.686304719083091</v>
+        <v>3.725962893045402</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423389</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.556773935686159</v>
+        <v>3.462913344826194</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.459993116519978</v>
+        <v>-4.156938427081729</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.77242026476442</v>
+        <v>1.799781549679755</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1926366425284208</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.672355921203212</v>
+        <v>3.712014095165522</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.568644424741573</v>
+        <v>3.474783833881608</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.712468270527702</v>
+        <v>-4.409413581089454</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.683300692216744</v>
+        <v>1.710661977132079</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1926366425284208</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.684226410258626</v>
+        <v>3.723884584220936</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.569854959260517</v>
+        <v>3.475994368400552</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.005364027007114</v>
+        <v>-4.702309337568866</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.567352924143923</v>
+        <v>1.594714209059258</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1926366425284208</v>
+        <v>0.4151679172322132</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.685436944777569</v>
+        <v>3.72509511873988</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251943</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.573976701487838</v>
+        <v>3.480116110627873</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.192028155141922</v>
+        <v>-4.888973465703674</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.496809015117321</v>
+        <v>1.524170300032657</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1658976717038609</v>
+        <v>0.3884289464076534</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.673515304510155</v>
+        <v>3.713173478472465</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.569054554224028</v>
+        <v>3.475193963364063</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.338048842055884</v>
+        <v>-5.034994152617636</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.433478593087926</v>
+        <v>1.460839878003261</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.156814579910004</v>
+        <v>0.3793458546137964</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.66314330217003</v>
+        <v>3.702801476132341</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830326</v>
+        <v>3.667962306830328</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.731258610923072</v>
+        <v>3.637398020063107</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.429762851165469</v>
+        <v>-5.126708161727221</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.558997046143136</v>
+        <v>1.586358331058471</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.156814579910004</v>
+        <v>0.3793458546137964</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.825347358869074</v>
+        <v>3.865005532831385</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071548</v>
+        <v>3.69653946807155</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.726105248886886</v>
+        <v>3.632244658026921</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.461414510225438</v>
+        <v>-5.15835982078719</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.541183020482963</v>
+        <v>1.568544305398297</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1516461226655638</v>
+        <v>0.3741773973693562</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.817092922486224</v>
+        <v>3.856751096448535</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.736334666455377</v>
+        <v>3.642474075595412</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.530480564798375</v>
+        <v>-5.227425875360127</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.523786016222279</v>
+        <v>1.551147301137614</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.08927524517195373</v>
+        <v>0.3118065198757461</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.78989981355855</v>
+        <v>3.82955798752086</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332688</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.745260304911279</v>
+        <v>3.651399714051315</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.632456687046782</v>
+        <v>-5.329401997608534</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.491921205778818</v>
+        <v>1.519282490694154</v>
       </c>
       <c r="F2026" t="n">
-        <v>-0.01270087707645384</v>
+        <v>0.2098303976273386</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.737639778665407</v>
+        <v>3.777297952627718</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.737413192155455</v>
+        <v>3.64355260129549</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.522450403569561</v>
+        <v>-5.219395714131313</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.528076606413882</v>
+        <v>1.555437891329218</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.01050369484082136</v>
+        <v>0.2330349695446138</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.743715409059948</v>
+        <v>3.783373583022259</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.741663202877429</v>
+        <v>3.647802612017464</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.379390827828635</v>
+        <v>-5.076336138390387</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.589550447432227</v>
+        <v>1.616911732347562</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.01851712143080064</v>
+        <v>0.2410483961345931</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.75277347573591</v>
+        <v>3.79243164969822</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.748924085759965</v>
+        <v>3.6550634949</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.077944102356797</v>
+        <v>-4.774889412918549</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.717390020503498</v>
+        <v>1.744751305418833</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3199638469026379</v>
+        <v>0.5424951216064303</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.940902393901548</v>
+        <v>3.980560567863859</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679624</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.749895263512676</v>
+        <v>3.656034672652711</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.102534346591981</v>
+        <v>-4.799479657153733</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.708525100562135</v>
+        <v>1.73588638547747</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3199638469026379</v>
+        <v>0.5424951216064303</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.941873571654258</v>
+        <v>3.98153174561657</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.82118418247416</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.750738167892431</v>
+        <v>3.656877577032466</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.051495970585461</v>
+        <v>-4.748441281147213</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.729783355344499</v>
+        <v>1.757144640259834</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3199638469026379</v>
+        <v>0.5424951216064303</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.942716476034014</v>
+        <v>3.982374649996325</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.831734516969543</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.769776266766577</v>
+        <v>3.675915675906612</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.01035667571883</v>
+        <v>-4.707301986280582</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.765277172165296</v>
+        <v>1.792638457080632</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3611031417692687</v>
+        <v>0.5836344164730611</v>
       </c>
       <c r="G2032" t="n">
-        <v>3.986438151828138</v>
+        <v>4.026096325790449</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.585960262890511</v>
+        <v>3.492099672030546</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.91372176370019</v>
+        <v>-4.610667074261942</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.620115133096687</v>
+        <v>1.647476418012022</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4577380537879087</v>
+        <v>0.6802693284917011</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.860603095163257</v>
+        <v>3.900261269125567</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.589462306964475</v>
+        <v>3.495601716104511</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.844683752751722</v>
+        <v>-4.541629063313474</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.651232381550038</v>
+        <v>1.678593666465374</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.5267760647363767</v>
+        <v>0.7493073394401691</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.905527945806301</v>
+        <v>3.945186119768612</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.573889126040558</v>
+        <v>3.480028535180593</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.68018741856076</v>
+        <v>-4.377132729122512</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.701457734302506</v>
+        <v>1.728819019217841</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6912723989273386</v>
+        <v>0.913803673631131</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.988652565396961</v>
+        <v>4.028310739359272</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.573076836476988</v>
+        <v>3.479216245617023</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.603088817018888</v>
+        <v>-4.30003412758064</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.731484885355685</v>
+        <v>1.75884617027102</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6912723989273386</v>
+        <v>0.913803673631131</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.987840275833391</v>
+        <v>4.027498449795702</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.58294561560206</v>
+        <v>3.489085024742095</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.613474011908777</v>
+        <v>-4.310419322470529</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.737199586524801</v>
+        <v>1.764560871440136</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6808872040374493</v>
+        <v>0.9034184787412417</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.99147793802453</v>
+        <v>4.03113611198684</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.653782621378485</v>
+        <v>3.55992203051852</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.632062170631002</v>
+        <v>-4.329007481192754</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.800601328812336</v>
+        <v>1.827962613727672</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.662299045315224</v>
+        <v>0.8848303200190164</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.05116204856762</v>
+        <v>4.09082022252993</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496554</v>
+        <v>3.855120535496556</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.650651632196784</v>
+        <v>3.556791041336819</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.632360717327038</v>
+        <v>-4.32930602788879</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.79735092095222</v>
+        <v>1.824712205867556</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6620004986191881</v>
+        <v>0.8845317733229805</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.047851931368297</v>
+        <v>4.087510105330607</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.655182527136175</v>
+        <v>3.56132193627621</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.53153758363661</v>
+        <v>-4.228482894198362</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.842211069367783</v>
+        <v>1.869572354283118</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6744647141035419</v>
+        <v>0.8969959888073343</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.059861355598301</v>
+        <v>4.099519529560611</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.655311780614718</v>
+        <v>3.561451189754754</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.340756222884202</v>
+        <v>-4.037701533445954</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.918652867147289</v>
+        <v>1.946014152062625</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8652460748559493</v>
+        <v>1.087777349559742</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.174459425528288</v>
+        <v>4.214117599490599</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.635148626352315</v>
+        <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.233792865034781</v>
+        <v>-3.930738175596533</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.941275056024654</v>
+        <v>1.96863634093999</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.9237106828157507</v>
+        <v>1.146241957519543</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.189375036041765</v>
+        <v>4.229033210004077</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.670115562964373</v>
+        <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.178462277133018</v>
+        <v>-3.875407587694771</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.998374227797418</v>
+        <v>2.025735512712753</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9790412707175129</v>
+        <v>1.201572545421305</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.257540325394881</v>
+        <v>4.297198499357192</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.663802130865811</v>
+        <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.166408150220056</v>
+        <v>-3.863353460781808</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.996882446464041</v>
+        <v>2.024243731379376</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9910953976304757</v>
+        <v>1.213626672334268</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.258459369444097</v>
+        <v>4.298117543406407</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.665682761049947</v>
+        <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.207563269788277</v>
+        <v>-3.904508580350029</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.982301028820888</v>
+        <v>2.009662313736223</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9499402780622548</v>
+        <v>1.172471552766047</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.2356469278873</v>
+        <v>4.275305101849611</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.678533786927829</v>
+        <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.139514707096747</v>
+        <v>-3.836460017658499</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.022371479775383</v>
+        <v>2.049732764690718</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.017988840753785</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.2893270913801</v>
+        <v>4.328985265342411</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013425</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.698736457101424</v>
+        <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.371115100266247</v>
+        <v>-4.068060410828</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.949933992681177</v>
+        <v>1.977295277596512</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.017988840753785</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.309529761553694</v>
+        <v>4.349187935516005</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.66674720149897</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.682342693168306</v>
+        <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.421166645795466</v>
+        <v>-4.11811195635722</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.913519610536371</v>
+        <v>1.940880895451706</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.017988840753785</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.293135997620577</v>
+        <v>4.332794171582887</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.642594606761772</v>
+        <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.596273478371911</v>
+        <v>-4.293218788933665</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.80372879109926</v>
+        <v>1.831090076014594</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.017988840753785</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.253387911214043</v>
+        <v>4.293046085176353</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.649617225758712</v>
+        <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.400173324941388</v>
+        <v>-4.097118635503142</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.889191471468409</v>
+        <v>1.916552756383743</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.214088994184308</v>
+        <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.378070622269297</v>
+        <v>4.417728796231607</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.748788225331617</v>
+        <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.247147932828104</v>
+        <v>-3.966632476488474</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.049572627886628</v>
+        <v>2.067918219562515</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.367114386297592</v>
+        <v>1.567106427902768</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.569056857110172</v>
+        <v>4.595191491213312</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.936254450239909</v>
+        <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.275455246701374</v>
+        <v>-3.994939790361744</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.225715927245612</v>
+        <v>2.2440615189215</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.367114386297592</v>
+        <v>1.567106427902768</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.756523082018465</v>
+        <v>4.782657716121605</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620436</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.905657401593992</v>
+        <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.442048471814896</v>
+        <v>-4.161533015475266</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.128481588554286</v>
+        <v>2.146827180230173</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.200521161184069</v>
+        <v>1.400513202789245</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.625970098304434</v>
+        <v>4.652104732407574</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285649</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.90933380425571</v>
+        <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.41901267845333</v>
+        <v>-4.1384972221137</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.14137230856063</v>
+        <v>2.159717900236518</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.200521161184069</v>
+        <v>1.400513202789245</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.629646500966151</v>
+        <v>4.655781135069292</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.906951859379205</v>
+        <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.389766697997634</v>
+        <v>-4.109251241658003</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.150688755866403</v>
+        <v>2.169034347542292</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.200521161184069</v>
+        <v>1.400513202789245</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.627264556089647</v>
+        <v>4.653399190192788</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.90424509853684</v>
+        <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.496692245875485</v>
+        <v>-4.216176789535854</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.105211775872898</v>
+        <v>2.123557367548786</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.093595613306218</v>
+        <v>1.293587654911394</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.560402466520571</v>
+        <v>4.586537100623712</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600701002</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.905673900680074</v>
+        <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.641710804382734</v>
+        <v>-4.361195348043103</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.048633154613233</v>
+        <v>2.066978746289121</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.9485770547989694</v>
+        <v>1.148569096404146</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.474820133559456</v>
+        <v>4.500954767662597</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.005605139937827</v>
+        <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.760052570167451</v>
+        <v>-4.479537113827821</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.101227687557098</v>
+        <v>2.119573279232987</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.9592630933618594</v>
+        <v>1.159255134967036</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.581162995954942</v>
+        <v>4.607297630058084</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.003390837063765</v>
+        <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.811462992488159</v>
+        <v>-4.530947536148529</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.078449215754754</v>
+        <v>2.096794807430643</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.9592630933618594</v>
+        <v>1.159255134967036</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.578948693080881</v>
+        <v>4.605083327184023</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.003293965138055</v>
+        <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.890882443695911</v>
+        <v>-4.61036698735628</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.046584563345943</v>
+        <v>2.064930155021831</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.9592630933618594</v>
+        <v>1.159255134967036</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.578851821155171</v>
+        <v>4.604986455258312</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298398</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.003287858696098</v>
+        <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.986345441613128</v>
+        <v>-4.705829985273498</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.008393257737099</v>
+        <v>2.026738849412987</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.9592630933618594</v>
+        <v>1.159255134967036</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.578845714713214</v>
+        <v>4.604980348816356</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960218</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.001384255258709</v>
+        <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.921969530762413</v>
+        <v>-4.641454074422783</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.032240018639996</v>
+        <v>2.050585610315884</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.023639004212574</v>
+        <v>1.223631045817751</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.615567657786254</v>
+        <v>4.641702291889395</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353535</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.007118073006436</v>
+        <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.977338692894607</v>
+        <v>-4.696823236554977</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.015826171534845</v>
+        <v>2.034171763210733</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.023639004212574</v>
+        <v>1.223631045817751</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.621301475533981</v>
+        <v>4.647436109637122</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.006656436349369</v>
+        <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.995557159892216</v>
+        <v>-4.715041703552585</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.008077148078734</v>
+        <v>2.026422739754622</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.9985325669567322</v>
+        <v>1.198524608561909</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.605775976523408</v>
+        <v>4.631910610626549</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113687</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.026530829199688</v>
+        <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.907350325744638</v>
+        <v>-4.626834869405007</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.063234274588085</v>
+        <v>2.081579866263972</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.9985325669567322</v>
+        <v>1.198524608561909</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.625650369373727</v>
+        <v>4.651785003476868</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.010231529724416</v>
+        <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.801315330539328</v>
+        <v>-4.520799874199698</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.089348973194936</v>
+        <v>2.107694564870823</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.9985325669567322</v>
+        <v>1.198524608561909</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.609351069898455</v>
+        <v>4.635485704001596</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.012662479188461</v>
+        <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.618103667406233</v>
+        <v>-4.337588211066603</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.16506458791222</v>
+        <v>2.183410179588107</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.9985325669567322</v>
+        <v>1.198524608561909</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.611782019362501</v>
+        <v>4.637916653465641</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.97845366503635</v>
+        <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.546382220392382</v>
+        <v>-4.265866764052752</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.15954435256565</v>
+        <v>2.177889944241537</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.070254013970583</v>
+        <v>1.270246055575759</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.6206060734187</v>
+        <v>4.646740707521841</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394113</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.925369410957522</v>
+        <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.524009194784676</v>
+        <v>-4.243493738445046</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.115409308729904</v>
+        <v>2.133754900405791</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.081509765083484</v>
+        <v>1.281501806688661</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.574275270007613</v>
+        <v>4.600409904110753</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.71560744645673</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.110567615842878</v>
+        <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.557025490695421</v>
+        <v>-4.27651003435579</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.287400995250962</v>
+        <v>2.305746586926849</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.012072388416733</v>
+        <v>1.212064430021909</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.717811048892917</v>
+        <v>4.743945682996058</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.102488841671127</v>
+        <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.545497855045812</v>
+        <v>-4.264982398706182</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.283933275339054</v>
+        <v>2.302278867014941</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.071073046618095</v>
+        <v>1.271065088223272</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.745132669641984</v>
+        <v>4.771267303745124</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236297</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.106156954192915</v>
+        <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.642839356388181</v>
+        <v>-4.36232390004855</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.248664787323895</v>
+        <v>2.267010378999782</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.026652864452607</v>
+        <v>1.226644906057783</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.722148672864479</v>
+        <v>4.74828330696762</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427683</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.107408036385753</v>
+        <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.728695385728147</v>
+        <v>-4.448179929388517</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.215573457780747</v>
+        <v>2.233919049456634</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.9842767952264717</v>
+        <v>1.184268836831648</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.697974113521637</v>
+        <v>4.724108747624777</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.089827238206255</v>
+        <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.737532183144267</v>
+        <v>-4.457016726804636</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.194457940634801</v>
+        <v>2.212803532310688</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.976834622585121</v>
+        <v>1.176826664190298</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.675928011757328</v>
+        <v>4.702062645860469</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667454</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.099991749251305</v>
+        <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.828914745709725</v>
+        <v>-4.548399289370095</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.168069426653667</v>
+        <v>2.186415018329554</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9402697378657763</v>
+        <v>1.140261779470953</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.664153591970771</v>
+        <v>4.690288226073911</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.67397837488919</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.202120007075573</v>
+        <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.817208027722719</v>
+        <v>-4.536692571383089</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.274880371672737</v>
+        <v>2.293225963348624</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.9519764558527827</v>
+        <v>1.151968497457959</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.773305880587243</v>
+        <v>4.799440514690382</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.205152345806978</v>
+        <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.888120101464997</v>
+        <v>-4.607604645125367</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.249547880907231</v>
+        <v>2.267893472583117</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.9519764558527827</v>
+        <v>1.151968497457959</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.776338219318648</v>
+        <v>4.802472853421787</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.672895177452572</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.418057179085036</v>
+        <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.898436199631349</v>
+        <v>-4.617920743291719</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.458326274918748</v>
+        <v>2.476671866594635</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.9519764558527827</v>
+        <v>1.151968497457959</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.989243052596706</v>
+        <v>5.015377686699845</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.417235845997125</v>
+        <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.898342231613976</v>
+        <v>-4.617826775274346</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.457542529037787</v>
+        <v>2.475888120713673</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.9523463172001007</v>
+        <v>1.152338358805277</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.988643636317186</v>
+        <v>5.014778270420326</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.411467831941479</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.046708459270121</v>
+        <v>-4.766193002930491</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.392428023919683</v>
+        <v>2.410773615595569</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.9523463172001007</v>
+        <v>1.152338358805277</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.98287562226154</v>
+        <v>5.00901025636468</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.411467831941479</v>
+        <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.045760036152083</v>
+        <v>-4.765244579812452</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.392807393166898</v>
+        <v>2.411152984842785</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.9523463172001007</v>
+        <v>1.152338358805277</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.98287562226154</v>
+        <v>5.00901025636468</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.424195439922571</v>
+        <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.146029854111104</v>
+        <v>-4.865514397771474</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.365427073964382</v>
+        <v>2.383772665640268</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.9523463172001007</v>
+        <v>1.152338358805277</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.995603230242632</v>
+        <v>5.021737864345772</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.71707115842477</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.426141438346959</v>
+        <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.140037607322292</v>
+        <v>-4.859522150982662</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.369769971104294</v>
+        <v>2.388115562780181</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.9523463172001007</v>
+        <v>1.152338358805277</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.99754922866702</v>
+        <v>5.023683862770159</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149219</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.419795574364728</v>
+        <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.051479646191525</v>
+        <v>-4.963620728407371</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.39884729157437</v>
+        <v>2.340130267828066</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.9523463172001007</v>
+        <v>1.152338358805277</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.991203364684789</v>
+        <v>5.017337998787928</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.73530072138309</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.419104251803724</v>
+        <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.033720568688451</v>
+        <v>-4.945861650904297</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.405259600014595</v>
+        <v>2.346542576268291</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.9523463172001007</v>
+        <v>1.152338358805277</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.990512042123784</v>
+        <v>5.016646676226924</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720996</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.43188643771231</v>
+        <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.934090417639383</v>
+        <v>-4.846231499855229</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.457893846342809</v>
+        <v>2.399176822596505</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.051976468249168</v>
+        <v>1.251968509854345</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.063072318661812</v>
+        <v>5.089206952764951</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
-        <v>4.621040703211037</v>
+        <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.983489926328394</v>
+        <v>-4.89563100854424</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.627288308365931</v>
+        <v>2.568571284619627</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.062235301680913</v>
+        <v>1.26222734328609</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.258381884219585</v>
+        <v>5.284516518322724</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963131</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
-        <v>4.608229376313899</v>
+        <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.776805452686018</v>
+        <v>-4.688946534901865</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.697150770925743</v>
+        <v>2.638433747179439</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.268919775323289</v>
+        <v>1.468911816928465</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.369581241507873</v>
+        <v>5.395715875611011</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162541</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
-        <v>4.610230889968004</v>
+        <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.810962347683544</v>
+        <v>-4.723103429899391</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.685489526580838</v>
+        <v>2.626772502834534</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.185336005782476</v>
+        <v>1.385328047387653</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.32143249343749</v>
+        <v>5.347567127540629</v>
       </c>
     </row>
     <row r="2090">
@@ -49618,19 +49618,19 @@
         <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
-        <v>4.963728003957671</v>
+        <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.718372868622088</v>
+        <v>-4.630513950837934</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.076022432195088</v>
+        <v>3.017305408448784</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.185336005782476</v>
+        <v>1.385328047387653</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.674929607427157</v>
+        <v>5.701064241530297</v>
       </c>
     </row>
     <row r="2091">
@@ -49641,19 +49641,19 @@
         <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
-        <v>4.968291115524774</v>
+        <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.778261496445638</v>
+        <v>-4.690402578661485</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.056630092632771</v>
+        <v>2.997913068886467</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.171214091095012</v>
+        <v>1.371206132700188</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.671019570181782</v>
+        <v>5.697154204284921</v>
       </c>
     </row>
     <row r="2092">
@@ -49664,19 +49664,19 @@
         <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
-        <v>5.018121056848302</v>
+        <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.726045186649296</v>
+        <v>-4.638186268865143</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.127346557874835</v>
+        <v>3.068629534128531</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.171214091095012</v>
+        <v>1.371206132700188</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.720849511505309</v>
+        <v>5.746984145608448</v>
       </c>
     </row>
     <row r="2093">
@@ -49687,19 +49687,19 @@
         <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
-        <v>5.026935027058313</v>
+        <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.69414766956405</v>
+        <v>-4.606288751779897</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.148919534918945</v>
+        <v>3.09020251117264</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.203111608180257</v>
+        <v>1.403103649785434</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.748801991966467</v>
+        <v>5.774936626069607</v>
       </c>
     </row>
     <row r="2094">
@@ -49710,19 +49710,19 @@
         <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
-        <v>5.02257261109751</v>
+        <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.708902993764191</v>
+        <v>-4.621044075980038</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.138654989278085</v>
+        <v>3.079937965531781</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.203111608180257</v>
+        <v>1.403103649785434</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.744439576005664</v>
+        <v>5.770574210108804</v>
       </c>
     </row>
     <row r="2095">
@@ -49733,19 +49733,19 @@
         <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
-        <v>5.01349711451379</v>
+        <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.659438370394279</v>
+        <v>-4.571579452610126</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.14936534204233</v>
+        <v>3.090648318296025</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.252576231550169</v>
+        <v>1.452568273155346</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.765042853443891</v>
+        <v>5.791177487547031</v>
       </c>
     </row>
     <row r="2096">
@@ -49756,19 +49756,19 @@
         <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
-        <v>5.009904782228724</v>
+        <v>4.916044191368758</v>
       </c>
       <c r="D2096" t="n">
-        <v>-4.496330378240664</v>
+        <v>-4.408471460456511</v>
       </c>
       <c r="E2096" t="n">
-        <v>3.21101620661871</v>
+        <v>3.152299182872406</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.415684223703784</v>
+        <v>1.615676265308961</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.859315316450995</v>
+        <v>5.885449950554134</v>
       </c>
     </row>
     <row r="2097">
@@ -49779,19 +49779,19 @@
         <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
-        <v>5.018951818919852</v>
+        <v>4.925091228059886</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.363522752743497</v>
+        <v>-4.275663834959344</v>
       </c>
       <c r="E2097" t="n">
-        <v>3.273186293508705</v>
+        <v>3.214469269762401</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.415684223703784</v>
+        <v>1.615676265308961</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.868362353142123</v>
+        <v>5.894496987245263</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790952</v>
+        <v>3.832425987790951</v>
       </c>
       <c r="C2098" t="n">
-        <v>5.019809283905974</v>
+        <v>4.925948693046007</v>
       </c>
       <c r="D2098" t="n">
-        <v>-4.179862536414437</v>
+        <v>-4.338371751433902</v>
       </c>
       <c r="E2098" t="n">
-        <v>3.347507845026451</v>
+        <v>3.190243568158699</v>
       </c>
       <c r="F2098" t="n">
-        <v>1.599344440032844</v>
+        <v>1.552968348834403</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.979415947925681</v>
+        <v>5.857729702346649</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.803639579680029</v>
+        <v>3.843535918066549</v>
       </c>
       <c r="C2099" t="n">
-        <v>5.018816867454944</v>
+        <v>4.924956276594978</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.176262764434139</v>
+        <v>-4.340257025505295</v>
       </c>
       <c r="E2099" t="n">
-        <v>3.347955337367541</v>
+        <v>3.188497042079113</v>
       </c>
       <c r="F2099" t="n">
-        <v>1.57759795162533</v>
+        <v>1.55108307476301</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.965375638430142</v>
+        <v>5.855606121452784</v>
       </c>
     </row>
   </sheetData>
